--- a/docs/EAA_Nghiep_vu_Agent.xlsx
+++ b/docs/EAA_Nghiep_vu_Agent.xlsx
@@ -11,9 +11,11 @@
     <sheet name="Nghiệp vụ" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Câu hỏi phải biết hỏi" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Thống kê" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Đối chiếu" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Nghiệp vụ'!$A$1:$I$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Đối chiếu'!$A$1:$I$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,8 +56,24 @@
     <font>
       <i val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C5700"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -97,6 +115,26 @@
         <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -124,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -182,6 +220,43 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4618,7 +4693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4999,7 +5074,3801 @@
         <v>13</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="22" t="n"/>
+      <c r="B16" s="22" t="n"/>
+      <c r="C16" s="22" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="22" t="n"/>
+      <c r="F16" s="22" t="n"/>
+      <c r="G16" s="22" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>Đối chiếu với mã hiện có</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="n"/>
+      <c r="C17" s="22" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="22" t="n"/>
+      <c r="F17" s="22" t="n"/>
+      <c r="G17" s="22" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>Giai đoạn</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>Việc</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Cố ý không</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Có khoảng cách tự chủ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>GĐ0 · Tiếp nhận &amp; phạm vi</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>GĐ1 · Phân tích &amp; đặc tả</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>GĐ2 · Môi trường &amp; công cụ</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>GĐ3 · Tri thức phần cứng</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>GĐ4 · Thiết kế &amp; phân rã</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="22" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>GĐ5 · Sinh mã &amp; kiểm chứng tĩnh</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>GĐ6 · Mô phỏng</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>GĐ7 · Ráp &amp; nạp</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>GĐ8 · Đưa lên mạch &amp; đo</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>GĐ9 · Nghiệm thu &amp; phát hành</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>GĐ10 · Vận hành &amp; bảo trì</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="n">
+        <v>74</v>
+      </c>
+      <c r="C31" s="25" t="n">
+        <v>36</v>
+      </c>
+      <c r="D31" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="E31" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="F31" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="25" t="n">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="66" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Giai đoạn</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>Nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>Tự chủ
+ĐỀ XUẤT</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>Tự chủ
+ĐẠT</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>Khoảng
+cách</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>Bằng chứng trong mã</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
+        <is>
+          <t>Còn thiếu gì</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>N-001</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>GĐ0 · Tiếp nhận &amp; phạm vi</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Tiếp nhận yêu cầu bằng lời của người dùng</t>
+        </is>
+      </c>
+      <c r="D2" s="26" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E2" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G2" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Không có lệnh nào tiếp nhận yêu cầu. Người tự viết constraints.yaml.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>N-002</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>GĐ0 · Tiếp nhận &amp; phạm vi</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Dò phần cứng đang cắm vào máy</t>
+        </is>
+      </c>
+      <c r="D3" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E3" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F3" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G3" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>eaa/serialport.py + eaa ports · TC-42a</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Chưa đọc ổ mass-storage của mạch nạp; chưa có danh mục bo để tra VID/PID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>N-003</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>GĐ0 · Tiếp nhận &amp; phạm vi</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Nhận dạng bo/MCU từ dấu hiệu dò được</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F4" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G4" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Chỉ so với VID/PID mà DỰ ÁN tự khai. Không có danh mục bo, không đề xuất ứng viên, không hỏi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>N-004</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>GĐ0 · Tiếp nhận &amp; phạm vi</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Thu thập tài liệu gốc</t>
+        </is>
+      </c>
+      <c r="D5" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G5" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>eaa/ingest.py (PdfIngestor, check_web_source) · TC-22</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Không liệt kê đích danh tài liệu cần; không hỏi rev silicon; không hỏi errata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>N-005</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>GĐ0 · Tiếp nhận &amp; phạm vi</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Lập danh mục giả định ban đầu</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E6" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G6" s="29" t="inlineStr">
+        <is>
+          <t>−3</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>eaa/ingest.py AssumptionLog · TC-22</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Có kho giả định, nhưng danh mục ban đầu do người viết tay (hồ sơ DISCO là tôi gõ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>N-006</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>GĐ0 · Tiếp nhận &amp; phạm vi</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Xác định phạm vi và cái KHÔNG làm</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G7" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Không có bước chốt phạm vi và cái không làm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>N-010</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>GĐ1 · Phân tích &amp; đặc tả</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Chốt ràng buộc cứng</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G8" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>eaa/kb.py Constraints + G1 · TC-04</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Đọc/kiểm/duyệt được, nhưng Agent KHÔNG đề xuất bộ ràng buộc — người viết trước.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>N-011</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>GĐ1 · Phân tích &amp; đặc tả</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Định nghĩa tiêu chí nghiệm thu ĐO ĐƯỢC</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>eaa/acceptance.py · TC-45</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Đối chiếu tiêu chí thì đủ; Agent không đề xuất tiêu chí và không ép 'phải đo được'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>N-012</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>GĐ1 · Phân tích &amp; đặc tả</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Chọn kiến trúc phần mềm</t>
+        </is>
+      </c>
+      <c r="D10" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G10" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>eaa/options.py + eaa decide · TC-46</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>N-013</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>GĐ1 · Phân tích &amp; đặc tả</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Phân bổ tài nguyên phần cứng</t>
+        </is>
+      </c>
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G11" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>eaa/graph.py check_module · TC-18</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>N-014</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>GĐ1 · Phân tích &amp; đặc tả</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Chốt sơ đồ chân</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G12" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>hardware_profile.yaml → graph · TC-18</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Đọc được pin_map; không trích từ schematic, không đề xuất, không kiểm chân có hỗ trợ chức năng cần.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>N-015</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>GĐ1 · Phân tích &amp; đặc tả</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Lập ngân sách tài nguyên</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G13" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>constraints.limits + SizeGate · TC-40d</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Kiểm được TỔNG; không chia ngân sách theo module, không cảnh báo module ăn quá phần.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>N-016</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>GĐ1 · Phân tích &amp; đặc tả</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Phân tích hỏng hóc và hệ quả</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G14" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Không có phân tích hỏng hóc–hệ quả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>N-017</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>GĐ1 · Phân tích &amp; đặc tả</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Xác định chế độ an toàn</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G15" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Không có định nghĩa chế độ an toàn. (safety_checklist chỉ dành cho kịch bản chẩn đoán, khác việc này.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>N-020</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>GĐ2 · Môi trường &amp; công cụ</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Kiểm công cụ đã có trên máy</t>
+        </is>
+      </c>
+      <c r="D16" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E16" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G16" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>eaa/doctor.py + toolsearch.derive_requirements · TC-34, TC-39</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>N-021</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>GĐ2 · Môi trường &amp; công cụ</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Tìm công cụ chưa biết cách cài</t>
+        </is>
+      </c>
+      <c r="D17" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G17" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>eaa/toolsearch.py · TC-39</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>N-022</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>GĐ2 · Môi trường &amp; công cụ</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Cài công cụ</t>
+        </is>
+      </c>
+      <c r="D18" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E18" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F18" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G18" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>eaa doctor --fix · TC-34, TC-37</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>N-023</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>GĐ2 · Môi trường &amp; công cụ</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Khóa phiên bản môi trường</t>
+        </is>
+      </c>
+      <c r="D19" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E19" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F19" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G19" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>eaa/doctor.py EnvLock · TC-36</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>N-024</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>GĐ2 · Môi trường &amp; công cụ</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Dựng kho mã và quy ước commit</t>
+        </is>
+      </c>
+      <c r="D20" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E20" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F20" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G20" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>eaa/vcs.py · TC-01</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>N-030</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>GĐ3 · Tri thức phần cứng</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Chọn trang tài liệu cần trích</t>
+        </is>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G21" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>eaa datasheet ingest · TC-22</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Người chọn trang (đúng thiết kế), nhưng Agent không nêu ĐÍCH DANH trang cần trích.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>N-031</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>GĐ3 · Tri thức phần cứng</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Chưng cất trích đoạn thành bảng thanh ghi–bit</t>
+        </is>
+      </c>
+      <c r="D22" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E22" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G22" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>eaa/ingest.py → G2 · TC-22</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>N-032</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>GĐ3 · Tri thức phần cứng</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Dựng đồ thị tri thức</t>
+        </is>
+      </c>
+      <c r="D23" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G23" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>eaa/graph.py · TC-18</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>N-033</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>GĐ3 · Tri thức phần cứng</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Phát hiện mâu thuẫn nguồn</t>
+        </is>
+      </c>
+      <c r="D24" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E24" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G24" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>eaa/readiness.py conflict + chuẩn hóa số · TC-26</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>N-034</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>GĐ3 · Tri thức phần cứng</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Tự đánh giá đủ thông tin trước khi sinh mã</t>
+        </is>
+      </c>
+      <c r="D25" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E25" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F25" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G25" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>eaa/readiness.py · TC-24</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>N-035</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>GĐ3 · Tri thức phần cứng</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Đi tìm thứ còn thiếu (leo thang 3 bậc)</t>
+        </is>
+      </c>
+      <c r="D26" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F26" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G26" s="29" t="inlineStr">
+        <is>
+          <t>−2</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>eaa/gapsearch.py (WIP, chưa nối CLI, chưa test)</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Hiện hành: chỉ IN GỢI Ý ba bậc rồi dừng. search_rounds không ai tăng. Chưa đi tìm thật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>N-036</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>GĐ3 · Tri thức phần cứng</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Quản lý vòng đời tri thức</t>
+        </is>
+      </c>
+      <c r="D27" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E27" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F27" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G27" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>eaa/lifecycle.py (3 đường truy ngược) · TC-29</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>N-037</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>GĐ3 · Tri thức phần cứng</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Theo dõi errata của nhà sản xuất</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E28" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F28" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G28" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Không hỏi rev silicon, không tra errata, không đối chiếu với ngoại vi đang dùng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>N-040</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>GĐ4 · Thiết kế &amp; phân rã</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Phân rã bài toán thành module</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E29" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F29" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G29" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>eaa plan add (thủ công)</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Agent không đề xuất phân rã. Người tự liệt kê module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>N-041</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>GĐ4 · Thiết kế &amp; phân rã</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Định nghĩa giao diện giữa module</t>
+        </is>
+      </c>
+      <c r="D30" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F30" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G30" s="29" t="inlineStr">
+        <is>
+          <t>−2</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>eaa/composer.py lớp K3</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Đọc được tệp tiêu đề module đã merge; KHÔNG sinh interface trước khi sinh thân.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>N-042</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>GĐ4 · Thiết kế &amp; phân rã</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Xếp thứ tự làm theo phụ thuộc</t>
+        </is>
+      </c>
+      <c r="D31" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E31" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F31" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G31" s="29" t="inlineStr">
+        <is>
+          <t>−3</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>state.BacklogItem.depends_on · TC-18</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Dùng để nạp interface và kiểm xung đột; không sắp thứ tự topo, không tự chọn module kế tiếp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>N-043</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>GĐ4 · Thiết kế &amp; phân rã</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Thiết kế lịch chạy</t>
+        </is>
+      </c>
+      <c r="D32" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E32" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F32" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G32" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>projects/*/firmware.yaml · TC-41a</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Kiểm được chu kỳ hợp lệ; Agent không đề xuất chu kỳ, không ước lượng tải CPU, không cảnh báo quá tải.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>N-050</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>GĐ5 · Sinh mã &amp; kiểm chứng tĩnh</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Sinh mã một module</t>
+        </is>
+      </c>
+      <c r="D33" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E33" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F33" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G33" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>eaa/composer.py + orchestrator · TC-04, TC-17</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>N-051</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>GĐ5 · Sinh mã &amp; kiểm chứng tĩnh</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Biên dịch</t>
+        </is>
+      </c>
+      <c r="D34" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F34" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G34" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>eaa/tools/compile.py CompileGate · TC-40</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>N-052</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>GĐ5 · Sinh mã &amp; kiểm chứng tĩnh</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Phân tích tĩnh theo ràng buộc dự án</t>
+        </is>
+      </c>
+      <c r="D35" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E35" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F35" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G35" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>eaa/tools/static.py · TC-07</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>N-053</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>GĐ5 · Sinh mã &amp; kiểm chứng tĩnh</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị trên máy chủ</t>
+        </is>
+      </c>
+      <c r="D36" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F36" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G36" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>eaa/tools/unittests.py · TC-07</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>Chạy được; không nêu rõ phần nào KHÔNG kiểm được trên máy chủ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>N-054</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>GĐ5 · Sinh mã &amp; kiểm chứng tĩnh</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Đo chiếm dụng bộ nhớ</t>
+        </is>
+      </c>
+      <c r="D37" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E37" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F37" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G37" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>eaa/tools/compile.py SizeGate + size_scope · TC-40d</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>N-055</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>GĐ5 · Sinh mã &amp; kiểm chứng tĩnh</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Vòng tự sửa khi cổng không đạt</t>
+        </is>
+      </c>
+      <c r="D38" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E38" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F38" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G38" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>eaa/orchestrator.py · TC-06, TC-19</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>N-056</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>GĐ5 · Sinh mã &amp; kiểm chứng tĩnh</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Review và hợp nhất</t>
+        </is>
+      </c>
+      <c r="D39" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E39" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F39" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G39" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>eaa/gates.py + vcs.py content_digest · TC-01</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>N-057</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>GĐ5 · Sinh mã &amp; kiểm chứng tĩnh</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Ghi nhận lỗi mô hình bịa ra</t>
+        </is>
+      </c>
+      <c r="D40" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E40" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F40" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G40" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>eaa/ledger.py · TC-10</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>N-060</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>GĐ6 · Mô phỏng</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Dựng mô hình đối tượng điều khiển</t>
+        </is>
+      </c>
+      <c r="D41" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E41" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F41" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G41" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>projects/robot_balance/sim/</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Dự án mẫu có mô hình con lắc; Agent không đề xuất mô hình cho đối tượng mới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>N-061</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>GĐ6 · Mô phỏng</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Chạy mô phỏng vòng kín</t>
+        </is>
+      </c>
+      <c r="D42" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E42" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F42" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G42" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>eaa/tools/sim.py, sim_runner.py · TC-12</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>N-062</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>GĐ6 · Mô phỏng</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Quét tham số và đề xuất bộ tham số</t>
+        </is>
+      </c>
+      <c r="D43" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E43" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F43" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G43" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>eaa sim --sweep · TC-12</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>N-063</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>GĐ6 · Mô phỏng</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Tiêm lỗi trong mô phỏng</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E44" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F44" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G44" s="29" t="inlineStr">
+        <is>
+          <t>−3</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>Không tiêm lỗi trong mô phỏng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>N-064</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>GĐ6 · Mô phỏng</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Chạy chính mã C sinh ra trong mô phỏng</t>
+        </is>
+      </c>
+      <c r="D45" s="36" t="inlineStr">
+        <is>
+          <t>Cố ý không làm</t>
+        </is>
+      </c>
+      <c r="E45" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F45" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G45" s="29" t="inlineStr">
+        <is>
+          <t>−3</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>Cố ý để ngoài chuỗi tự động: nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>N-070</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>GĐ7 · Ráp &amp; nạp</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Ráp firmware hoàn chỉnh</t>
+        </is>
+      </c>
+      <c r="D46" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E46" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F46" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G46" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>eaa/firmware.py + eaa build · TC-41</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>N-071</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>GĐ7 · Ráp &amp; nạp</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Kiểm bộ nhớ ở tầm firmware</t>
+        </is>
+      </c>
+      <c r="D47" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E47" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F47" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G47" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>SizeGate scope=firmware · TC-41e</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>Đo được flash/RAM ở tầm firmware; KHÔNG kiểm khoảng trống ngăn xếp còn lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>N-072</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>GĐ7 · Ráp &amp; nạp</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Kiểm trước khi nạp</t>
+        </is>
+      </c>
+      <c r="D48" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E48" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F48" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G48" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>eaa/flash.py preflight · TC-42b</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>N-073</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>GĐ7 · Ráp &amp; nạp</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Chọn đúng thiết bị để nạp</t>
+        </is>
+      </c>
+      <c r="D49" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E49" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F49" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G49" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>eaa/serialport.py match_confirmed · TC-47d</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>N-074</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>GĐ7 · Ráp &amp; nạp</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Nạp và ghi nhật ký</t>
+        </is>
+      </c>
+      <c r="D50" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E50" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F50" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G50" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>eaa/flash.py + FlashLog · TC-42d</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>N-075</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>GĐ7 · Ráp &amp; nạp</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Kiểm sau khi nạp</t>
+        </is>
+      </c>
+      <c r="D51" s="26" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E51" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F51" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G51" s="29" t="inlineStr">
+        <is>
+          <t>−3</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>Không đọc ngược/so kiểm tổng sau khi nạp. 'Nạp không báo lỗi' đang bị ngầm hiểu là 'nạp đúng'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>N-080</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>GĐ8 · Đưa lên mạch &amp; đo</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Thiết lập kênh đo</t>
+        </is>
+      </c>
+      <c r="D52" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E52" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F52" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G52" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>eaa/telemetry.py + eaa telemetry · TC-43</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>N-081</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>GĐ8 · Đưa lên mạch &amp; đo</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Sinh firmware đo cho từng kịch bản chẩn đoán</t>
+        </is>
+      </c>
+      <c r="D53" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E53" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F53" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G53" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>eaa/firmware.py DiagnosticFirmwareBuilder · TC-44</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>Cơ chế đủ; mới 2/6 kịch bản có phần đo (DS-01, DS-04).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>N-082</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>GĐ8 · Đưa lên mạch &amp; đo</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Chẩn đoán hai kênh</t>
+        </is>
+      </c>
+      <c r="D54" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E54" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F54" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G54" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>eaa/diagnostics.py · TC-27</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>N-083</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>GĐ8 · Đưa lên mạch &amp; đo</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Đo đặc tính thời gian thực</t>
+        </is>
+      </c>
+      <c r="D55" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E55" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F55" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G55" s="29" t="inlineStr">
+        <is>
+          <t>−3</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>acceptance loop_period_ms + telemetry</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>Có kênh và có tiêu chí; CHƯA có firmware đo dao động chu kỳ và tải CPU, chưa báo trường hợp xấu nhất.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>N-084</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>GĐ8 · Đưa lên mạch &amp; đo</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Đo điện và nhiệt</t>
+        </is>
+      </c>
+      <c r="D56" s="26" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E56" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="F56" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G56" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>diagnostics.yaml DS-05 (mới khai, chưa có phần đo)</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>Không có hướng dẫn đo đích danh, không có chỗ nhập số đo tay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>N-085</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>GĐ8 · Đưa lên mạch &amp; đo</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Chẩn đoán sâu bằng công cụ gỡ lỗi</t>
+        </is>
+      </c>
+      <c r="D57" s="26" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E57" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F57" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G57" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>Ngoài phạm vi đề án (đã ghi từ trước).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>N-086</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>GĐ8 · Đưa lên mạch &amp; đo</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Kiểm độ bền dài hạn</t>
+        </is>
+      </c>
+      <c r="D58" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E58" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F58" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G58" s="29" t="inlineStr">
+        <is>
+          <t>−3</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>acceptance uptime_s ≥ 600 · TC-45</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>Có tiêu chí; không có cơ chế chạy dài, không phát hiện reset qua bộ đếm thời gian chạy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>N-090</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>GĐ9 · Nghiệm thu &amp; phát hành</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Đối chiếu tiêu chí nghiệm thu</t>
+        </is>
+      </c>
+      <c r="D59" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E59" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F59" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G59" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>eaa/acceptance.py · TC-45</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>N-091</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>GĐ9 · Nghiệm thu &amp; phát hành</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Phong hạng chất lượng bản mã</t>
+        </is>
+      </c>
+      <c r="D60" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E60" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F60" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G60" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>eaa/versions.py + check_device_commit · TC-30, TC-45a</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>N-092</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>GĐ9 · Nghiệm thu &amp; phát hành</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Giữ bản chạy tốt và quay lui</t>
+        </is>
+      </c>
+      <c r="D61" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E61" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F61" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G61" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>eaa/versions.py + eaa rollback · TC-30</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>N-093</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>GĐ9 · Nghiệm thu &amp; phát hành</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Xuất báo cáo và dấu vết</t>
+        </is>
+      </c>
+      <c r="D62" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E62" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F62" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>eaa/kpi.py + llm/calllog.py + registry.py · TC-09, TC-15</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>N-094</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>GĐ9 · Nghiệm thu &amp; phát hành</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Bàn giao tài liệu vận hành</t>
+        </is>
+      </c>
+      <c r="D63" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E63" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F63" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G63" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>eaa/registry.py (kho phẩm xuất) · TC-32</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>Lưu/gửi lại phẩm xuất được; KHÔNG sinh tài liệu vận hành từ dữ liệu dự án.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>N-100</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>GĐ10 · Vận hành &amp; bảo trì</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
+        </is>
+      </c>
+      <c r="D64" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E64" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F64" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>eaa/lifecycle.py · TC-29</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>N-101</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>GĐ10 · Vận hành &amp; bảo trì</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Đánh giá ảnh hưởng khi linh kiện đổi</t>
+        </is>
+      </c>
+      <c r="D65" s="26" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E65" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F65" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G65" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>Không so sánh linh kiện thay thế.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>N-102</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>GĐ10 · Vận hành &amp; bảo trì</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Chẩn đoán sự cố ngoài hiện trường</t>
+        </is>
+      </c>
+      <c r="D66" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E66" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F66" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>eaa diagnose select + hai kênh · TC-27</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>Chọn kịch bản từ triệu chứng được; không dựng lại điều kiện sự cố, không xử lý ca không tái hiện.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>N-103</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>GĐ10 · Vận hành &amp; bảo trì</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Cập nhật firmware cho thiết bị đã triển khai</t>
+        </is>
+      </c>
+      <c r="D67" s="26" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E67" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F67" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G67" s="29" t="inlineStr">
+        <is>
+          <t>−2</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>Không có cập nhật firmware cho thiết bị đã triển khai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>N-900</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Giữ ranh giới tổng quát / nền tảng / dự án</t>
+        </is>
+      </c>
+      <c r="D68" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E68" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F68" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>TC-38 (quét mỗi commit) + TC-47a (không rẽ nhánh theo pack)</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>N-901</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Bảo vệ khóa và bí mật</t>
+        </is>
+      </c>
+      <c r="D69" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E69" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F69" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>eaa/llm/base.py mask_secrets · TC-14 + tests/conftest.py</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>N-902</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Không bao giờ hành động ngoài ý muốn người</t>
+        </is>
+      </c>
+      <c r="D70" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E70" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F70" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>eaa/gates.py, doctor, flash — không cờ bỏ qua · TC-01, TC-42c</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>N-903</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Nói rõ mức tin cậy của mọi điều mình nói</t>
+        </is>
+      </c>
+      <c r="D71" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F71" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G71" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>serialport.match_confirmed, telemetry.bad_ratio, AssumptionLog</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>Có ở vài chỗ; CHƯA nhất quán toàn hệ — nhiều đầu ra không nói mức tin cậy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>N-904</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Quản lý chi phí gọi mô hình</t>
+        </is>
+      </c>
+      <c r="D72" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E72" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F72" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>eaa/kpi.py (tokens_in/out) · TC-09</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>Ghi được token; không có trần theo module, không quy ra chi phí, không cảnh báo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>N-905</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Ghi nhận mọi sai lệch so với thiết kế</t>
+        </is>
+      </c>
+      <c r="D73" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E73" s="33" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F73" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G73" s="29" t="inlineStr">
+        <is>
+          <t>−3</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>docs/SAI_LECH_THIET_KE.md (40 mục)</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>Nhật ký đầy đủ, nhưng do TÔI ghi tay — Agent không tự phát hiện và không tự ghi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>N-906</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Tự đánh giá và cải tiến quy trình</t>
+        </is>
+      </c>
+      <c r="D74" s="30" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E74" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F74" s="28" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G74" s="29" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>eaa report + kpi.summary · TC-09</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>Tổng hợp được chỉ số; không chỉ ra khâu hay hỏng, không đề xuất sửa prompt/quy tắc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>N-907</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Khôi phục sau gián đoạn</t>
+        </is>
+      </c>
+      <c r="D75" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E75" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F75" s="31" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>eaa/state.py ghi nguyên tử + eaa resume · TC-03</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I75"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/EAA_Nghiep_vu_Agent.xlsx
+++ b/docs/EAA_Nghiep_vu_Agent.xlsx
@@ -5218,10 +5218,10 @@
         <v>8</v>
       </c>
       <c r="C22" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="22" t="n">
         <v>1</v>
@@ -5230,7 +5230,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -5443,10 +5443,10 @@
         <v>74</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E31" s="25" t="n">
         <v>13</v>
@@ -5455,7 +5455,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -6633,9 +6633,9 @@
           <t>Đi tìm thứ còn thiếu (leo thang 3 bậc)</t>
         </is>
       </c>
-      <c r="D26" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D26" s="34" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E26" s="35" t="inlineStr">
@@ -6643,26 +6643,22 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="F26" s="28" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G26" s="29" t="inlineStr">
-        <is>
-          <t>−2</t>
+      <c r="F26" s="35" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G26" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>eaa/gapsearch.py (WIP, chưa nối CLI, chưa test)</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>Hiện hành: chỉ IN GỢI Ý ba bậc rồi dừng. search_rounds không ai tăng. Chưa đi tìm thật.</t>
-        </is>
-      </c>
+          <t>eaa/gapsearch.py + eaa resolve · TC-48 (26 test)</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">

--- a/docs/EAA_Nghiep_vu_Agent.xlsx
+++ b/docs/EAA_Nghiep_vu_Agent.xlsx
@@ -58,7 +58,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00006100"/>
     </font>
     <font>
       <b val="1"/>
@@ -66,7 +66,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
@@ -117,7 +117,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -127,7 +127,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -231,26 +231,26 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -5143,19 +5143,19 @@
         <v>6</v>
       </c>
       <c r="C19" s="22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D19" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -5443,19 +5443,19 @@
         <v>74</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E31" s="25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D2" s="26" t="inlineStr">
         <is>
-          <t>Chưa có</t>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E2" s="27" t="inlineStr">
@@ -5559,26 +5559,22 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F2" s="28" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G2" s="29" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F2" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G2" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>Không có lệnh nào tiếp nhận yêu cầu. Người tự viết constraints.yaml.</t>
-        </is>
-      </c>
+          <t>eaa/brief.py QUESTIONS + eaa brief · TC-49c</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
@@ -5596,36 +5592,32 @@
           <t>Dò phần cứng đang cắm vào máy</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
-        </is>
-      </c>
-      <c r="E3" s="31" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="F3" s="31" t="inlineStr">
+      <c r="F3" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="G3" s="32" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>eaa/serialport.py + eaa ports · TC-42a</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>Chưa đọc ổ mass-storage của mạch nạp; chưa có danh mục bo để tra VID/PID.</t>
-        </is>
-      </c>
+          <t>eaa/brief.py probe_hardware · TC-49a</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -5645,7 +5637,7 @@
       </c>
       <c r="D4" s="26" t="inlineStr">
         <is>
-          <t>Chưa có</t>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E4" s="27" t="inlineStr">
@@ -5653,26 +5645,22 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F4" s="28" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G4" s="29" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G4" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Chỉ so với VID/PID mà DỰ ÁN tự khai. Không có danh mục bo, không đề xuất ứng viên, không hỏi.</t>
-        </is>
-      </c>
+          <t>eaa/brief.py identify_board · TC-49b</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -5705,7 +5693,7 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="G5" s="32" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5737,36 +5725,32 @@
           <t>Lập danh mục giả định ban đầu</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
-        </is>
-      </c>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F6" s="28" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G6" s="29" t="inlineStr">
-        <is>
-          <t>−3</t>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>eaa/ingest.py AssumptionLog · TC-22</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Có kho giả định, nhưng danh mục ban đầu do người viết tay (hồ sơ DISCO là tôi gõ).</t>
-        </is>
-      </c>
+          <t>eaa/brief.py ProjectDraft.gia_dinh · TC-49d</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
@@ -5784,7 +5768,7 @@
           <t>Xác định phạm vi và cái KHÔNG làm</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>Chưa có</t>
         </is>
@@ -5794,12 +5778,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F7" s="28" t="inlineStr">
+      <c r="F7" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="G7" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -5841,12 +5825,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="F8" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G8" s="29" t="inlineStr">
+      <c r="G8" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -5888,12 +5872,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F9" s="28" t="inlineStr">
+      <c r="F9" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G9" s="29" t="inlineStr">
+      <c r="G9" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -5925,7 +5909,7 @@
           <t>Chọn kiến trúc phần mềm</t>
         </is>
       </c>
-      <c r="D10" s="34" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
@@ -5940,7 +5924,7 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="G10" s="32" t="inlineStr">
+      <c r="G10" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5968,22 +5952,22 @@
           <t>Phân bổ tài nguyên phần cứng</t>
         </is>
       </c>
-      <c r="D11" s="34" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E11" s="33" t="inlineStr">
+      <c r="E11" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F11" s="33" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="G11" s="32" t="inlineStr">
+      <c r="G11" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6021,12 +6005,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F12" s="28" t="inlineStr">
+      <c r="F12" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G12" s="29" t="inlineStr">
+      <c r="G12" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -6068,12 +6052,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F13" s="33" t="inlineStr">
+      <c r="F13" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="G13" s="32" t="inlineStr">
+      <c r="G13" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6105,7 +6089,7 @@
           <t>Phân tích hỏng hóc và hệ quả</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="32" t="inlineStr">
         <is>
           <t>Chưa có</t>
         </is>
@@ -6115,12 +6099,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F14" s="28" t="inlineStr">
+      <c r="F14" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G14" s="29" t="inlineStr">
+      <c r="G14" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -6152,7 +6136,7 @@
           <t>Xác định chế độ an toàn</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="32" t="inlineStr">
         <is>
           <t>Chưa có</t>
         </is>
@@ -6162,12 +6146,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F15" s="28" t="inlineStr">
+      <c r="F15" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G15" s="29" t="inlineStr">
+      <c r="G15" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -6199,22 +6183,22 @@
           <t>Kiểm công cụ đã có trên máy</t>
         </is>
       </c>
-      <c r="D16" s="34" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E16" s="31" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="F16" s="31" t="inlineStr">
+      <c r="F16" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="G16" s="32" t="inlineStr">
+      <c r="G16" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6242,7 +6226,7 @@
           <t>Tìm công cụ chưa biết cách cài</t>
         </is>
       </c>
-      <c r="D17" s="34" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
@@ -6257,7 +6241,7 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="G17" s="32" t="inlineStr">
+      <c r="G17" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6285,7 +6269,7 @@
           <t>Cài công cụ</t>
         </is>
       </c>
-      <c r="D18" s="34" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
@@ -6300,7 +6284,7 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="G18" s="32" t="inlineStr">
+      <c r="G18" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6328,22 +6312,22 @@
           <t>Khóa phiên bản môi trường</t>
         </is>
       </c>
-      <c r="D19" s="34" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E19" s="33" t="inlineStr">
+      <c r="E19" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F19" s="33" t="inlineStr">
+      <c r="F19" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="G19" s="32" t="inlineStr">
+      <c r="G19" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6371,22 +6355,22 @@
           <t>Dựng kho mã và quy ước commit</t>
         </is>
       </c>
-      <c r="D20" s="34" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E20" s="33" t="inlineStr">
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F20" s="33" t="inlineStr">
+      <c r="F20" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="G20" s="32" t="inlineStr">
+      <c r="G20" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6424,12 +6408,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F21" s="28" t="inlineStr">
+      <c r="F21" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G21" s="29" t="inlineStr">
+      <c r="G21" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -6461,7 +6445,7 @@
           <t>Chưng cất trích đoạn thành bảng thanh ghi–bit</t>
         </is>
       </c>
-      <c r="D22" s="34" t="inlineStr">
+      <c r="D22" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
@@ -6476,7 +6460,7 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="G22" s="32" t="inlineStr">
+      <c r="G22" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6504,22 +6488,22 @@
           <t>Dựng đồ thị tri thức</t>
         </is>
       </c>
-      <c r="D23" s="34" t="inlineStr">
+      <c r="D23" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E23" s="31" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="F23" s="31" t="inlineStr">
+      <c r="F23" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="G23" s="32" t="inlineStr">
+      <c r="G23" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6547,7 +6531,7 @@
           <t>Phát hiện mâu thuẫn nguồn</t>
         </is>
       </c>
-      <c r="D24" s="34" t="inlineStr">
+      <c r="D24" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
@@ -6562,7 +6546,7 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="G24" s="32" t="inlineStr">
+      <c r="G24" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6590,22 +6574,22 @@
           <t>Tự đánh giá đủ thông tin trước khi sinh mã</t>
         </is>
       </c>
-      <c r="D25" s="34" t="inlineStr">
+      <c r="D25" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E25" s="33" t="inlineStr">
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F25" s="33" t="inlineStr">
+      <c r="F25" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="G25" s="32" t="inlineStr">
+      <c r="G25" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6633,7 +6617,7 @@
           <t>Đi tìm thứ còn thiếu (leo thang 3 bậc)</t>
         </is>
       </c>
-      <c r="D26" s="34" t="inlineStr">
+      <c r="D26" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
@@ -6648,7 +6632,7 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="G26" s="32" t="inlineStr">
+      <c r="G26" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6676,22 +6660,22 @@
           <t>Quản lý vòng đời tri thức</t>
         </is>
       </c>
-      <c r="D27" s="34" t="inlineStr">
+      <c r="D27" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E27" s="33" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F27" s="33" t="inlineStr">
+      <c r="F27" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="G27" s="32" t="inlineStr">
+      <c r="G27" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6719,7 +6703,7 @@
           <t>Theo dõi errata của nhà sản xuất</t>
         </is>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D28" s="32" t="inlineStr">
         <is>
           <t>Chưa có</t>
         </is>
@@ -6729,12 +6713,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F28" s="28" t="inlineStr">
+      <c r="F28" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G28" s="29" t="inlineStr">
+      <c r="G28" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -6766,7 +6750,7 @@
           <t>Phân rã bài toán thành module</t>
         </is>
       </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="D29" s="32" t="inlineStr">
         <is>
           <t>Chưa có</t>
         </is>
@@ -6776,12 +6760,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F29" s="28" t="inlineStr">
+      <c r="F29" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G29" s="29" t="inlineStr">
+      <c r="G29" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -6823,12 +6807,12 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="F30" s="28" t="inlineStr">
+      <c r="F30" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G30" s="29" t="inlineStr">
+      <c r="G30" s="34" t="inlineStr">
         <is>
           <t>−2</t>
         </is>
@@ -6865,17 +6849,17 @@
           <t>Một phần</t>
         </is>
       </c>
-      <c r="E31" s="33" t="inlineStr">
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F31" s="28" t="inlineStr">
+      <c r="F31" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G31" s="29" t="inlineStr">
+      <c r="G31" s="34" t="inlineStr">
         <is>
           <t>−3</t>
         </is>
@@ -6917,12 +6901,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F32" s="28" t="inlineStr">
+      <c r="F32" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G32" s="29" t="inlineStr">
+      <c r="G32" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -6954,7 +6938,7 @@
           <t>Sinh mã một module</t>
         </is>
       </c>
-      <c r="D33" s="34" t="inlineStr">
+      <c r="D33" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
@@ -6969,7 +6953,7 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="G33" s="32" t="inlineStr">
+      <c r="G33" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6997,22 +6981,22 @@
           <t>Biên dịch</t>
         </is>
       </c>
-      <c r="D34" s="34" t="inlineStr">
+      <c r="D34" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E34" s="31" t="inlineStr">
+      <c r="E34" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="F34" s="31" t="inlineStr">
+      <c r="F34" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="G34" s="32" t="inlineStr">
+      <c r="G34" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7040,22 +7024,22 @@
           <t>Phân tích tĩnh theo ràng buộc dự án</t>
         </is>
       </c>
-      <c r="D35" s="34" t="inlineStr">
+      <c r="D35" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E35" s="31" t="inlineStr">
+      <c r="E35" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="F35" s="31" t="inlineStr">
+      <c r="F35" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="G35" s="32" t="inlineStr">
+      <c r="G35" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7088,17 +7072,17 @@
           <t>Một phần</t>
         </is>
       </c>
-      <c r="E36" s="31" t="inlineStr">
+      <c r="E36" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="F36" s="31" t="inlineStr">
+      <c r="F36" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="G36" s="32" t="inlineStr">
+      <c r="G36" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7130,22 +7114,22 @@
           <t>Đo chiếm dụng bộ nhớ</t>
         </is>
       </c>
-      <c r="D37" s="34" t="inlineStr">
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E37" s="31" t="inlineStr">
+      <c r="E37" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="F37" s="31" t="inlineStr">
+      <c r="F37" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="G37" s="32" t="inlineStr">
+      <c r="G37" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7173,22 +7157,22 @@
           <t>Vòng tự sửa khi cổng không đạt</t>
         </is>
       </c>
-      <c r="D38" s="34" t="inlineStr">
+      <c r="D38" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E38" s="33" t="inlineStr">
+      <c r="E38" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F38" s="33" t="inlineStr">
+      <c r="F38" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="G38" s="32" t="inlineStr">
+      <c r="G38" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7216,7 +7200,7 @@
           <t>Review và hợp nhất</t>
         </is>
       </c>
-      <c r="D39" s="34" t="inlineStr">
+      <c r="D39" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
@@ -7231,7 +7215,7 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="G39" s="32" t="inlineStr">
+      <c r="G39" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7259,22 +7243,22 @@
           <t>Ghi nhận lỗi mô hình bịa ra</t>
         </is>
       </c>
-      <c r="D40" s="34" t="inlineStr">
+      <c r="D40" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E40" s="33" t="inlineStr">
+      <c r="E40" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F40" s="33" t="inlineStr">
+      <c r="F40" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="G40" s="32" t="inlineStr">
+      <c r="G40" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7312,12 +7296,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F41" s="28" t="inlineStr">
+      <c r="F41" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G41" s="29" t="inlineStr">
+      <c r="G41" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -7349,22 +7333,22 @@
           <t>Chạy mô phỏng vòng kín</t>
         </is>
       </c>
-      <c r="D42" s="34" t="inlineStr">
+      <c r="D42" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E42" s="31" t="inlineStr">
+      <c r="E42" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="F42" s="31" t="inlineStr">
+      <c r="F42" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="G42" s="32" t="inlineStr">
+      <c r="G42" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7392,7 +7376,7 @@
           <t>Quét tham số và đề xuất bộ tham số</t>
         </is>
       </c>
-      <c r="D43" s="34" t="inlineStr">
+      <c r="D43" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
@@ -7407,7 +7391,7 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="G43" s="32" t="inlineStr">
+      <c r="G43" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7435,22 +7419,22 @@
           <t>Tiêm lỗi trong mô phỏng</t>
         </is>
       </c>
-      <c r="D44" s="26" t="inlineStr">
+      <c r="D44" s="32" t="inlineStr">
         <is>
           <t>Chưa có</t>
         </is>
       </c>
-      <c r="E44" s="33" t="inlineStr">
+      <c r="E44" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F44" s="28" t="inlineStr">
+      <c r="F44" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G44" s="29" t="inlineStr">
+      <c r="G44" s="34" t="inlineStr">
         <is>
           <t>−3</t>
         </is>
@@ -7487,17 +7471,17 @@
           <t>Cố ý không làm</t>
         </is>
       </c>
-      <c r="E45" s="33" t="inlineStr">
+      <c r="E45" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F45" s="28" t="inlineStr">
+      <c r="F45" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G45" s="29" t="inlineStr">
+      <c r="G45" s="34" t="inlineStr">
         <is>
           <t>−3</t>
         </is>
@@ -7529,7 +7513,7 @@
           <t>Ráp firmware hoàn chỉnh</t>
         </is>
       </c>
-      <c r="D46" s="34" t="inlineStr">
+      <c r="D46" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
@@ -7544,7 +7528,7 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="G46" s="32" t="inlineStr">
+      <c r="G46" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7577,17 +7561,17 @@
           <t>Một phần</t>
         </is>
       </c>
-      <c r="E47" s="31" t="inlineStr">
+      <c r="E47" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="F47" s="31" t="inlineStr">
+      <c r="F47" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="G47" s="32" t="inlineStr">
+      <c r="G47" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7619,7 +7603,7 @@
           <t>Kiểm trước khi nạp</t>
         </is>
       </c>
-      <c r="D48" s="34" t="inlineStr">
+      <c r="D48" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
@@ -7634,7 +7618,7 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="G48" s="32" t="inlineStr">
+      <c r="G48" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7662,22 +7646,22 @@
           <t>Chọn đúng thiết bị để nạp</t>
         </is>
       </c>
-      <c r="D49" s="34" t="inlineStr">
+      <c r="D49" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E49" s="33" t="inlineStr">
+      <c r="E49" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F49" s="33" t="inlineStr">
+      <c r="F49" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="G49" s="32" t="inlineStr">
+      <c r="G49" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7705,7 +7689,7 @@
           <t>Nạp và ghi nhật ký</t>
         </is>
       </c>
-      <c r="D50" s="34" t="inlineStr">
+      <c r="D50" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
@@ -7720,7 +7704,7 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="G50" s="32" t="inlineStr">
+      <c r="G50" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7748,22 +7732,22 @@
           <t>Kiểm sau khi nạp</t>
         </is>
       </c>
-      <c r="D51" s="26" t="inlineStr">
+      <c r="D51" s="32" t="inlineStr">
         <is>
           <t>Chưa có</t>
         </is>
       </c>
-      <c r="E51" s="33" t="inlineStr">
+      <c r="E51" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F51" s="28" t="inlineStr">
+      <c r="F51" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G51" s="29" t="inlineStr">
+      <c r="G51" s="34" t="inlineStr">
         <is>
           <t>−3</t>
         </is>
@@ -7795,22 +7779,22 @@
           <t>Thiết lập kênh đo</t>
         </is>
       </c>
-      <c r="D52" s="34" t="inlineStr">
+      <c r="D52" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E52" s="33" t="inlineStr">
+      <c r="E52" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F52" s="33" t="inlineStr">
+      <c r="F52" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="G52" s="32" t="inlineStr">
+      <c r="G52" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7853,7 +7837,7 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="G53" s="32" t="inlineStr">
+      <c r="G53" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7885,7 +7869,7 @@
           <t>Chẩn đoán hai kênh</t>
         </is>
       </c>
-      <c r="D54" s="34" t="inlineStr">
+      <c r="D54" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
@@ -7900,7 +7884,7 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="G54" s="32" t="inlineStr">
+      <c r="G54" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7933,17 +7917,17 @@
           <t>Một phần</t>
         </is>
       </c>
-      <c r="E55" s="33" t="inlineStr">
+      <c r="E55" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F55" s="28" t="inlineStr">
+      <c r="F55" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G55" s="29" t="inlineStr">
+      <c r="G55" s="34" t="inlineStr">
         <is>
           <t>−3</t>
         </is>
@@ -7975,22 +7959,22 @@
           <t>Đo điện và nhiệt</t>
         </is>
       </c>
-      <c r="D56" s="26" t="inlineStr">
+      <c r="D56" s="32" t="inlineStr">
         <is>
           <t>Chưa có</t>
         </is>
       </c>
-      <c r="E56" s="28" t="inlineStr">
+      <c r="E56" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="F56" s="28" t="inlineStr">
+      <c r="F56" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G56" s="32" t="inlineStr">
+      <c r="G56" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8022,7 +8006,7 @@
           <t>Chẩn đoán sâu bằng công cụ gỡ lỗi</t>
         </is>
       </c>
-      <c r="D57" s="26" t="inlineStr">
+      <c r="D57" s="32" t="inlineStr">
         <is>
           <t>Chưa có</t>
         </is>
@@ -8032,12 +8016,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F57" s="28" t="inlineStr">
+      <c r="F57" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G57" s="29" t="inlineStr">
+      <c r="G57" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -8074,17 +8058,17 @@
           <t>Một phần</t>
         </is>
       </c>
-      <c r="E58" s="33" t="inlineStr">
+      <c r="E58" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F58" s="28" t="inlineStr">
+      <c r="F58" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G58" s="29" t="inlineStr">
+      <c r="G58" s="34" t="inlineStr">
         <is>
           <t>−3</t>
         </is>
@@ -8116,7 +8100,7 @@
           <t>Đối chiếu tiêu chí nghiệm thu</t>
         </is>
       </c>
-      <c r="D59" s="34" t="inlineStr">
+      <c r="D59" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
@@ -8131,7 +8115,7 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="G59" s="32" t="inlineStr">
+      <c r="G59" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8159,7 +8143,7 @@
           <t>Phong hạng chất lượng bản mã</t>
         </is>
       </c>
-      <c r="D60" s="34" t="inlineStr">
+      <c r="D60" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
@@ -8174,7 +8158,7 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="G60" s="32" t="inlineStr">
+      <c r="G60" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8202,22 +8186,22 @@
           <t>Giữ bản chạy tốt và quay lui</t>
         </is>
       </c>
-      <c r="D61" s="34" t="inlineStr">
+      <c r="D61" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E61" s="33" t="inlineStr">
+      <c r="E61" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F61" s="33" t="inlineStr">
+      <c r="F61" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="G61" s="32" t="inlineStr">
+      <c r="G61" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8245,22 +8229,22 @@
           <t>Xuất báo cáo và dấu vết</t>
         </is>
       </c>
-      <c r="D62" s="34" t="inlineStr">
+      <c r="D62" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E62" s="33" t="inlineStr">
+      <c r="E62" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F62" s="33" t="inlineStr">
+      <c r="F62" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="G62" s="32" t="inlineStr">
+      <c r="G62" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8298,12 +8282,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F63" s="28" t="inlineStr">
+      <c r="F63" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G63" s="29" t="inlineStr">
+      <c r="G63" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -8335,7 +8319,7 @@
           <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
         </is>
       </c>
-      <c r="D64" s="34" t="inlineStr">
+      <c r="D64" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
@@ -8350,7 +8334,7 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="G64" s="32" t="inlineStr">
+      <c r="G64" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8378,7 +8362,7 @@
           <t>Đánh giá ảnh hưởng khi linh kiện đổi</t>
         </is>
       </c>
-      <c r="D65" s="26" t="inlineStr">
+      <c r="D65" s="32" t="inlineStr">
         <is>
           <t>Chưa có</t>
         </is>
@@ -8388,12 +8372,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F65" s="28" t="inlineStr">
+      <c r="F65" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G65" s="29" t="inlineStr">
+      <c r="G65" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -8440,7 +8424,7 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="G66" s="32" t="inlineStr">
+      <c r="G66" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8472,7 +8456,7 @@
           <t>Cập nhật firmware cho thiết bị đã triển khai</t>
         </is>
       </c>
-      <c r="D67" s="26" t="inlineStr">
+      <c r="D67" s="32" t="inlineStr">
         <is>
           <t>Chưa có</t>
         </is>
@@ -8482,12 +8466,12 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="F67" s="28" t="inlineStr">
+      <c r="F67" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G67" s="29" t="inlineStr">
+      <c r="G67" s="34" t="inlineStr">
         <is>
           <t>−2</t>
         </is>
@@ -8519,22 +8503,22 @@
           <t>Giữ ranh giới tổng quát / nền tảng / dự án</t>
         </is>
       </c>
-      <c r="D68" s="34" t="inlineStr">
+      <c r="D68" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E68" s="31" t="inlineStr">
+      <c r="E68" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="F68" s="31" t="inlineStr">
+      <c r="F68" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="G68" s="32" t="inlineStr">
+      <c r="G68" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8562,22 +8546,22 @@
           <t>Bảo vệ khóa và bí mật</t>
         </is>
       </c>
-      <c r="D69" s="34" t="inlineStr">
+      <c r="D69" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E69" s="31" t="inlineStr">
+      <c r="E69" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="F69" s="31" t="inlineStr">
+      <c r="F69" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="G69" s="32" t="inlineStr">
+      <c r="G69" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8605,7 +8589,7 @@
           <t>Không bao giờ hành động ngoài ý muốn người</t>
         </is>
       </c>
-      <c r="D70" s="34" t="inlineStr">
+      <c r="D70" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
@@ -8620,7 +8604,7 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="G70" s="32" t="inlineStr">
+      <c r="G70" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8653,17 +8637,17 @@
           <t>Một phần</t>
         </is>
       </c>
-      <c r="E71" s="31" t="inlineStr">
+      <c r="E71" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="F71" s="33" t="inlineStr">
+      <c r="F71" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="G71" s="29" t="inlineStr">
+      <c r="G71" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -8700,17 +8684,17 @@
           <t>Một phần</t>
         </is>
       </c>
-      <c r="E72" s="33" t="inlineStr">
+      <c r="E72" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F72" s="33" t="inlineStr">
+      <c r="F72" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="G72" s="32" t="inlineStr">
+      <c r="G72" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8747,17 +8731,17 @@
           <t>Một phần</t>
         </is>
       </c>
-      <c r="E73" s="33" t="inlineStr">
+      <c r="E73" s="31" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F73" s="28" t="inlineStr">
+      <c r="F73" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G73" s="29" t="inlineStr">
+      <c r="G73" s="34" t="inlineStr">
         <is>
           <t>−3</t>
         </is>
@@ -8799,12 +8783,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F74" s="28" t="inlineStr">
+      <c r="F74" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G74" s="29" t="inlineStr">
+      <c r="G74" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -8836,22 +8820,22 @@
           <t>Khôi phục sau gián đoạn</t>
         </is>
       </c>
-      <c r="D75" s="34" t="inlineStr">
+      <c r="D75" s="26" t="inlineStr">
         <is>
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E75" s="31" t="inlineStr">
+      <c r="E75" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="F75" s="31" t="inlineStr">
+      <c r="F75" s="29" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="G75" s="32" t="inlineStr">
+      <c r="G75" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/docs/EAA_Nghiep_vu_Agent.xlsx
+++ b/docs/EAA_Nghiep_vu_Agent.xlsx
@@ -5243,19 +5243,19 @@
         <v>4</v>
       </c>
       <c r="C23" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="D23" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" s="22" t="n">
-        <v>1</v>
       </c>
       <c r="F23" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -5443,19 +5443,19 @@
         <v>74</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E31" s="25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -6750,9 +6750,9 @@
           <t>Phân rã bài toán thành module</t>
         </is>
       </c>
-      <c r="D29" s="32" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E29" s="27" t="inlineStr">
@@ -6760,26 +6760,22 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F29" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G29" s="34" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F29" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G29" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>eaa plan add (thủ công)</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>Agent không đề xuất phân rã. Người tự liệt kê module.</t>
-        </is>
-      </c>
+          <t>eaa/decompose.py + eaa plan propose · TC-50 (32 test)</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
@@ -6807,24 +6803,24 @@
           <t>T2</t>
         </is>
       </c>
-      <c r="F30" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
+      <c r="F30" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="G30" s="34" t="inlineStr">
         <is>
-          <t>−2</t>
+          <t>−1</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>eaa/composer.py lớp K3</t>
+          <t>decompose.ModuleProposal.provides + composer K3 · TC-50a</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>Đọc được tệp tiêu đề module đã merge; KHÔNG sinh interface trước khi sinh thân.</t>
+          <t>Đề xuất được DANH SÁCH hàm mỗi module cung cấp; chưa SINH tệp tiêu đề trước khi sinh thân.</t>
         </is>
       </c>
     </row>
@@ -6844,9 +6840,9 @@
           <t>Xếp thứ tự làm theo phụ thuộc</t>
         </is>
       </c>
-      <c r="D31" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D31" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E31" s="31" t="inlineStr">
@@ -6854,26 +6850,22 @@
           <t>T3</t>
         </is>
       </c>
-      <c r="F31" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G31" s="34" t="inlineStr">
-        <is>
-          <t>−3</t>
+      <c r="F31" s="31" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G31" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>state.BacklogItem.depends_on · TC-18</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>Dùng để nạp interface và kiểm xung đột; không sắp thứ tự topo, không tự chọn module kế tiếp.</t>
-        </is>
-      </c>
+          <t>decompose.order()/parallel_groups() · TC-50b</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
@@ -6891,9 +6883,9 @@
           <t>Thiết kế lịch chạy</t>
         </is>
       </c>
-      <c r="D32" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D32" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E32" s="27" t="inlineStr">
@@ -6901,26 +6893,22 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F32" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G32" s="34" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F32" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G32" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>projects/*/firmware.yaml · TC-41a</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>Kiểm được chu kỳ hợp lệ; Agent không đề xuất chu kỳ, không ước lượng tải CPU, không cảnh báo quá tải.</t>
-        </is>
-      </c>
+          <t>decompose: chu kỳ + tải CPU + 3 phép kiểm · TC-50c</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">

--- a/docs/EAA_Nghiep_vu_Agent.xlsx
+++ b/docs/EAA_Nghiep_vu_Agent.xlsx
@@ -5168,19 +5168,19 @@
         <v>8</v>
       </c>
       <c r="C20" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="22" t="n">
         <v>4</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -5443,19 +5443,19 @@
         <v>74</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D31" s="25" t="n">
         <v>19</v>
       </c>
       <c r="E31" s="25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -6089,9 +6089,9 @@
           <t>Phân tích hỏng hóc và hệ quả</t>
         </is>
       </c>
-      <c r="D14" s="32" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E14" s="27" t="inlineStr">
@@ -6099,26 +6099,22 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F14" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G14" s="34" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F14" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Không có phân tích hỏng hóc–hệ quả.</t>
-        </is>
-      </c>
+          <t>eaa/safety.py + eaa safety propose · TC-51 (29 test)</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
@@ -6136,9 +6132,9 @@
           <t>Xác định chế độ an toàn</t>
         </is>
       </c>
-      <c r="D15" s="32" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E15" s="27" t="inlineStr">
@@ -6146,26 +6142,22 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F15" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G15" s="34" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F15" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G15" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>Không có định nghĩa chế độ an toàn. (safety_checklist chỉ dành cho kịch bản chẩn đoán, khác việc này.)</t>
-        </is>
-      </c>
+          <t>eaa/safety.py SafeState · TC-51c, TC-51d</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">

--- a/docs/EAA_Nghiep_vu_Agent.xlsx
+++ b/docs/EAA_Nghiep_vu_Agent.xlsx
@@ -62,7 +62,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C5700"/>
+      <color rgb="001F4E79"/>
     </font>
     <font>
       <b val="1"/>
@@ -70,7 +70,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E79"/>
+      <color rgb="009C5700"/>
     </font>
   </fonts>
   <fills count="13">
@@ -122,7 +122,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -132,7 +132,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -237,13 +237,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -252,8 +252,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -623,7 +623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -645,159 +645,166 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Đề án Thạc sĩ Kỹ thuật (Kỹ thuật Điện tử, PTIT) · Học viên: Vũ Trí Công · Giảng viên hướng dẫn: TS. Nguyễn Trung Hiếu</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Thang mức tự chủ — cột quan trọng nhất của bảng</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Mức</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Nghĩa</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Khi nào dùng</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Người làm, Agent ghi vết</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Agent không làm được việc này. Nó chỉ ghi lại ai làm, làm lúc nào, kết quả ra sao. Dùng cho việc đòi tay người hoặc phán đoán vật lý.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Agent đề xuất, người quyết</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Agent dựng phương án/dữ kiện ở trạng thái ĐỀ XUẤT. Không có hiệu lực cho tới khi người chọn. Dùng khi có nhiều cách đều đúng, hoặc khi sai thì tốn kém.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Agent làm, người duyệt trước khi có hiệu lực</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Agent làm trọn việc và trình kết quả; kết quả chỉ vào hệ thống sau khi người duyệt tại một gate. Dùng cho thứ khó hoàn tác.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Agent tự làm, báo lại</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Agent làm và có hiệu lực ngay, nhưng để lại bằng chứng đầy đủ và báo cáo. Dùng khi việc hoàn tác được và sai thì phát hiện được.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Agent tự làm, không cần báo</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Chỉ dành cho việc đọc, việc tính, việc không đổi trạng thái gì. Mọi việc GHI ra ngoài đều không thuộc mức này.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Cách dùng bảng</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1. Đọc sheet 'Nghiệp vụ' — soát xem thiếu việc nào, hoặc việc nào không cần.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2. Soát cột 'Mức tự chủ' — chỗ nào bạn muốn Agent tự chủ hơn (hoặc ít hơn) mức đề xuất.</t>
+          <t>1. Đọc sheet 'Nghiệp vụ' — soát xem thiếu việc nào, hoặc việc nào không cần.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3. Soát cột 'Cách Agent làm' — đây là chỗ quyết định Agent thông minh tới đâu.</t>
+          <t>2. Soát cột 'Mức tự chủ' — chỗ nào bạn muốn Agent tự chủ hơn (hoặc ít hơn) mức đề xuất.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4. Sheet 'Câu hỏi phải biết hỏi' — danh mục khai thác yêu cầu; thiếu câu nào thì bổ sung.</t>
+          <t>3. Soát cột 'Cách Agent làm' — đây là chỗ quyết định Agent thông minh tới đâu.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>4. Sheet 'Câu hỏi phải biết hỏi' — danh mục khai thác yêu cầu; thiếu câu nào thì bổ sung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>5. Sau khi bạn duyệt, mới đối chiếu với mã hiện có để biết đã làm được bao nhiêu.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Ghi chú: mức tự chủ ở đây là ĐỀ XUẤT của tôi, không phải kết luận. Nguyên tắc dùng để đề xuất: việc nào sai thì hỏng thật (nạp, cài, xóa, phong hạng) đều không quá T2.</t>
         </is>
@@ -5143,19 +5150,19 @@
         <v>6</v>
       </c>
       <c r="C19" s="22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -5168,10 +5175,10 @@
         <v>8</v>
       </c>
       <c r="C20" s="22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D20" s="22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E20" s="22" t="n">
         <v>0</v>
@@ -5180,7 +5187,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -5218,19 +5225,19 @@
         <v>8</v>
       </c>
       <c r="C22" s="22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D22" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -5243,10 +5250,10 @@
         <v>4</v>
       </c>
       <c r="C23" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="22" t="n">
         <v>0</v>
@@ -5255,7 +5262,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -5268,10 +5275,10 @@
         <v>8</v>
       </c>
       <c r="C24" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="22" t="n">
         <v>0</v>
@@ -5293,19 +5300,19 @@
         <v>5</v>
       </c>
       <c r="C25" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="22" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -5318,19 +5325,19 @@
         <v>6</v>
       </c>
       <c r="C26" s="22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D26" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G26" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -5343,19 +5350,19 @@
         <v>7</v>
       </c>
       <c r="C27" s="22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D27" s="22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E27" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -5368,10 +5375,10 @@
         <v>5</v>
       </c>
       <c r="C28" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="22" t="n">
         <v>0</v>
@@ -5380,7 +5387,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -5393,19 +5400,19 @@
         <v>4</v>
       </c>
       <c r="C29" s="22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D29" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F29" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -5418,10 +5425,10 @@
         <v>8</v>
       </c>
       <c r="C30" s="22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D30" s="22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E30" s="22" t="n">
         <v>0</v>
@@ -5430,7 +5437,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -5443,19 +5450,19 @@
         <v>74</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E31" s="25" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5678,9 +5685,9 @@
           <t>Thu thập tài liệu gốc</t>
         </is>
       </c>
-      <c r="D5" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E5" s="27" t="inlineStr">
@@ -5700,14 +5707,10 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>eaa/ingest.py (PdfIngestor, check_web_source) · TC-22</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Không liệt kê đích danh tài liệu cần; không hỏi rev silicon; không hỏi errata.</t>
-        </is>
-      </c>
+          <t>eaa/docplan.py plan_documents · TC-55a,b</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -5730,12 +5733,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F6" s="31" t="inlineStr">
+      <c r="F6" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -5768,9 +5771,9 @@
           <t>Xác định phạm vi và cái KHÔNG làm</t>
         </is>
       </c>
-      <c r="D7" s="32" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E7" s="27" t="inlineStr">
@@ -5778,26 +5781,22 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F7" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G7" s="34" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F7" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Không có bước chốt phạm vi và cái không làm.</t>
-        </is>
-      </c>
+          <t>eaa/propose.py ScopeProposal · TC-54a</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -5815,9 +5814,9 @@
           <t>Chốt ràng buộc cứng</t>
         </is>
       </c>
-      <c r="D8" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E8" s="27" t="inlineStr">
@@ -5825,26 +5824,22 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F8" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G8" s="34" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F8" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>eaa/kb.py Constraints + G1 · TC-04</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Đọc/kiểm/duyệt được, nhưng Agent KHÔNG đề xuất bộ ràng buộc — người viết trước.</t>
-        </is>
-      </c>
+          <t>eaa/propose.py ConstraintProposal · TC-54b</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -5862,9 +5857,9 @@
           <t>Định nghĩa tiêu chí nghiệm thu ĐO ĐƯỢC</t>
         </is>
       </c>
-      <c r="D9" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E9" s="27" t="inlineStr">
@@ -5872,26 +5867,22 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F9" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G9" s="34" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F9" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G9" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>eaa/acceptance.py · TC-45</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>Đối chiếu tiêu chí thì đủ; Agent không đề xuất tiêu chí và không ép 'phải đo được'.</t>
-        </is>
-      </c>
+          <t>eaa/propose.py AcceptanceProposal · TC-54c,d</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -5957,12 +5948,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E11" s="31" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F11" s="31" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -5995,9 +5986,9 @@
           <t>Chốt sơ đồ chân</t>
         </is>
       </c>
-      <c r="D12" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -6005,26 +5996,22 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F12" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G12" s="34" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F12" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>hardware_profile.yaml → graph · TC-18</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Đọc được pin_map; không trích từ schematic, không đề xuất, không kiểm chân có hỗ trợ chức năng cần.</t>
-        </is>
-      </c>
+          <t>eaa/propose.py PinMapProposal + pin_functions · TC-54e,f</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
@@ -6042,9 +6029,9 @@
           <t>Lập ngân sách tài nguyên</t>
         </is>
       </c>
-      <c r="D13" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E13" s="27" t="inlineStr">
@@ -6052,9 +6039,9 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F13" s="31" t="inlineStr">
-        <is>
-          <t>T3</t>
+      <c r="F13" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="G13" s="28" t="inlineStr">
@@ -6064,14 +6051,10 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>constraints.limits + SizeGate · TC-40d</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>Kiểm được TỔNG; không chia ngân sách theo module, không cảnh báo module ăn quá phần.</t>
-        </is>
-      </c>
+          <t>eaa/budget.py ResourceBudget · TC-53a,b,c,g</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -6266,12 +6249,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E18" s="35" t="inlineStr">
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="F18" s="35" t="inlineStr">
+      <c r="F18" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -6309,12 +6292,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E19" s="31" t="inlineStr">
+      <c r="E19" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F19" s="31" t="inlineStr">
+      <c r="F19" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -6352,12 +6335,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E20" s="31" t="inlineStr">
+      <c r="E20" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F20" s="31" t="inlineStr">
+      <c r="F20" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -6390,9 +6373,9 @@
           <t>Chọn trang tài liệu cần trích</t>
         </is>
       </c>
-      <c r="D21" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D21" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E21" s="27" t="inlineStr">
@@ -6400,26 +6383,22 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F21" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G21" s="34" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F21" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G21" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>eaa datasheet ingest · TC-22</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>Người chọn trang (đúng thiết kế), nhưng Agent không nêu ĐÍCH DANH trang cần trích.</t>
-        </is>
-      </c>
+          <t>eaa/docplan.py plan_pages · TC-55d,e</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -6442,12 +6421,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E22" s="35" t="inlineStr">
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="F22" s="35" t="inlineStr">
+      <c r="F22" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -6571,12 +6550,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E25" s="31" t="inlineStr">
+      <c r="E25" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F25" s="31" t="inlineStr">
+      <c r="F25" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -6614,12 +6593,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E26" s="35" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="F26" s="35" t="inlineStr">
+      <c r="F26" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -6657,12 +6636,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E27" s="31" t="inlineStr">
+      <c r="E27" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F27" s="31" t="inlineStr">
+      <c r="F27" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -6695,9 +6674,9 @@
           <t>Theo dõi errata của nhà sản xuất</t>
         </is>
       </c>
-      <c r="D28" s="32" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E28" s="27" t="inlineStr">
@@ -6705,26 +6684,22 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F28" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G28" s="34" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F28" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G28" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>Không hỏi rev silicon, không tra errata, không đối chiếu với ngoại vi đang dùng.</t>
-        </is>
-      </c>
+          <t>eaa/docplan.py ErrataAnalysis · TC-55f,g,h</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
@@ -6785,36 +6760,32 @@
           <t>Định nghĩa giao diện giữa module</t>
         </is>
       </c>
-      <c r="D30" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
-        </is>
-      </c>
-      <c r="E30" s="35" t="inlineStr">
+      <c r="D30" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E30" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="F30" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="G30" s="34" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F30" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G30" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>decompose.ModuleProposal.provides + composer K3 · TC-50a</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>Đề xuất được DANH SÁCH hàm mỗi module cung cấp; chưa SINH tệp tiêu đề trước khi sinh thân.</t>
-        </is>
-      </c>
+          <t>eaa/interfaces.py + khuôn interfaces của pack · TC-56a..e</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
@@ -6837,12 +6808,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E31" s="31" t="inlineStr">
+      <c r="E31" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F31" s="31" t="inlineStr">
+      <c r="F31" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -6923,12 +6894,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E33" s="35" t="inlineStr">
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="F33" s="35" t="inlineStr">
+      <c r="F33" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -7047,9 +7018,9 @@
           <t>Kiểm thử đơn vị trên máy chủ</t>
         </is>
       </c>
-      <c r="D36" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D36" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E36" s="29" t="inlineStr">
@@ -7069,14 +7040,10 @@
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>eaa/tools/unittests.py · TC-07</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>Chạy được; không nêu rõ phần nào KHÔNG kiểm được trên máy chủ.</t>
-        </is>
-      </c>
+          <t>eaa/tools/unittests.py host_gaps · TC-56f,g</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
@@ -7142,12 +7109,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E38" s="31" t="inlineStr">
+      <c r="E38" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F38" s="31" t="inlineStr">
+      <c r="F38" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -7185,12 +7152,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E39" s="35" t="inlineStr">
+      <c r="E39" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="F39" s="35" t="inlineStr">
+      <c r="F39" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -7228,12 +7195,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E40" s="31" t="inlineStr">
+      <c r="E40" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F40" s="31" t="inlineStr">
+      <c r="F40" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -7266,9 +7233,9 @@
           <t>Dựng mô hình đối tượng điều khiển</t>
         </is>
       </c>
-      <c r="D41" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D41" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E41" s="27" t="inlineStr">
@@ -7276,26 +7243,22 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F41" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G41" s="34" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F41" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G41" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>projects/robot_balance/sim/</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>Dự án mẫu có mô hình con lắc; Agent không đề xuất mô hình cho đối tượng mới.</t>
-        </is>
-      </c>
+          <t>eaa/propose.py PlantModelProposal · TC-57f,g</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
@@ -7399,36 +7362,32 @@
           <t>Tiêm lỗi trong mô phỏng</t>
         </is>
       </c>
-      <c r="D44" s="32" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
-        </is>
-      </c>
-      <c r="E44" s="31" t="inlineStr">
+      <c r="D44" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E44" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F44" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G44" s="34" t="inlineStr">
-        <is>
-          <t>−3</t>
+      <c r="F44" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G44" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>Không tiêm lỗi trong mô phỏng.</t>
-        </is>
-      </c>
+          <t>sim_runner FaultSpec + require_safe_state · TC-57a..e</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
@@ -7446,12 +7405,12 @@
           <t>Chạy chính mã C sinh ra trong mô phỏng</t>
         </is>
       </c>
-      <c r="D45" s="36" t="inlineStr">
+      <c r="D45" s="32" t="inlineStr">
         <is>
           <t>Cố ý không làm</t>
         </is>
       </c>
-      <c r="E45" s="31" t="inlineStr">
+      <c r="E45" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -7498,12 +7457,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E46" s="35" t="inlineStr">
+      <c r="E46" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="F46" s="35" t="inlineStr">
+      <c r="F46" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -7536,9 +7495,9 @@
           <t>Kiểm bộ nhớ ở tầm firmware</t>
         </is>
       </c>
-      <c r="D47" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E47" s="29" t="inlineStr">
@@ -7558,14 +7517,10 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>SizeGate scope=firmware · TC-41e</t>
-        </is>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>Đo được flash/RAM ở tầm firmware; KHÔNG kiểm khoảng trống ngăn xếp còn lại.</t>
-        </is>
-      </c>
+          <t>budget.derived + stack_headroom_bytes_min · TC-53d</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
@@ -7588,12 +7543,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E48" s="35" t="inlineStr">
+      <c r="E48" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="F48" s="35" t="inlineStr">
+      <c r="F48" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -7631,12 +7586,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E49" s="31" t="inlineStr">
+      <c r="E49" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F49" s="31" t="inlineStr">
+      <c r="F49" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -7674,12 +7629,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E50" s="35" t="inlineStr">
+      <c r="E50" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="F50" s="35" t="inlineStr">
+      <c r="F50" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -7712,36 +7667,32 @@
           <t>Kiểm sau khi nạp</t>
         </is>
       </c>
-      <c r="D51" s="32" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
-        </is>
-      </c>
-      <c r="E51" s="31" t="inlineStr">
+      <c r="D51" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E51" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F51" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G51" s="34" t="inlineStr">
-        <is>
-          <t>−3</t>
+      <c r="F51" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G51" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>Không đọc ngược/so kiểm tổng sau khi nạp. 'Nạp không báo lỗi' đang bị ngầm hiểu là 'nạp đúng'.</t>
-        </is>
-      </c>
+          <t>eaa/flash.py VerifyResult + năng lực flash_verify · TC-52</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
@@ -7764,12 +7715,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E52" s="31" t="inlineStr">
+      <c r="E52" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F52" s="31" t="inlineStr">
+      <c r="F52" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -7802,17 +7753,17 @@
           <t>Sinh firmware đo cho từng kịch bản chẩn đoán</t>
         </is>
       </c>
-      <c r="D53" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
-        </is>
-      </c>
-      <c r="E53" s="35" t="inlineStr">
+      <c r="D53" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E53" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="F53" s="35" t="inlineStr">
+      <c r="F53" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -7824,14 +7775,10 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>eaa/firmware.py DiagnosticFirmwareBuilder · TC-44</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>Cơ chế đủ; mới 2/6 kịch bản có phần đo (DS-01, DS-04).</t>
-        </is>
-      </c>
+          <t>đủ 6 kịch bản khai firmware_template · TC-58a</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
@@ -7892,36 +7839,32 @@
           <t>Đo đặc tính thời gian thực</t>
         </is>
       </c>
-      <c r="D55" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
-        </is>
-      </c>
-      <c r="E55" s="31" t="inlineStr">
+      <c r="D55" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E55" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F55" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G55" s="34" t="inlineStr">
-        <is>
-          <t>−3</t>
+      <c r="F55" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G55" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>acceptance loop_period_ms + telemetry</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>Có kênh và có tiêu chí; CHƯA có firmware đo dao động chu kỳ và tải CPU, chưa báo trường hợp xấu nhất.</t>
-        </is>
-      </c>
+          <t>DS-06 đo cả trường hợp xấu nhất và tải CPU · TC-58b</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
@@ -7939,9 +7882,9 @@
           <t>Đo điện và nhiệt</t>
         </is>
       </c>
-      <c r="D56" s="32" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
+      <c r="D56" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E56" s="33" t="inlineStr">
@@ -7961,14 +7904,10 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>diagnostics.yaml DS-05 (mới khai, chưa có phần đo)</t>
-        </is>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>Không có hướng dẫn đo đích danh, không có chỗ nhập số đo tay.</t>
-        </is>
-      </c>
+          <t>ManualMeasurement + eaa diagnose measure · TC-58c,d</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
@@ -7986,7 +7925,7 @@
           <t>Chẩn đoán sâu bằng công cụ gỡ lỗi</t>
         </is>
       </c>
-      <c r="D57" s="32" t="inlineStr">
+      <c r="D57" s="35" t="inlineStr">
         <is>
           <t>Chưa có</t>
         </is>
@@ -8033,36 +7972,32 @@
           <t>Kiểm độ bền dài hạn</t>
         </is>
       </c>
-      <c r="D58" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
-        </is>
-      </c>
-      <c r="E58" s="31" t="inlineStr">
+      <c r="D58" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E58" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F58" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G58" s="34" t="inlineStr">
-        <is>
-          <t>−3</t>
+      <c r="F58" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G58" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>acceptance uptime_s ≥ 600 · TC-45</t>
-        </is>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>Có tiêu chí; không có cơ chế chạy dài, không phát hiện reset qua bộ đếm thời gian chạy.</t>
-        </is>
-      </c>
+          <t>eaa/endurance.py + eaa endurance · TC-58e,f,g</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
@@ -8085,12 +8020,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E59" s="35" t="inlineStr">
+      <c r="E59" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="F59" s="35" t="inlineStr">
+      <c r="F59" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -8128,12 +8063,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E60" s="35" t="inlineStr">
+      <c r="E60" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="F60" s="35" t="inlineStr">
+      <c r="F60" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -8171,12 +8106,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E61" s="31" t="inlineStr">
+      <c r="E61" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F61" s="31" t="inlineStr">
+      <c r="F61" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -8214,12 +8149,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E62" s="31" t="inlineStr">
+      <c r="E62" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F62" s="31" t="inlineStr">
+      <c r="F62" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -8252,9 +8187,9 @@
           <t>Bàn giao tài liệu vận hành</t>
         </is>
       </c>
-      <c r="D63" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D63" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E63" s="27" t="inlineStr">
@@ -8262,26 +8197,22 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F63" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G63" s="34" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F63" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G63" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>eaa/registry.py (kho phẩm xuất) · TC-32</t>
-        </is>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>Lưu/gửi lại phẩm xuất được; KHÔNG sinh tài liệu vận hành từ dữ liệu dự án.</t>
-        </is>
-      </c>
+          <t>eaa/handover.py OperationsHandbook · TC-59a,b</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
@@ -8342,9 +8273,9 @@
           <t>Đánh giá ảnh hưởng khi linh kiện đổi</t>
         </is>
       </c>
-      <c r="D65" s="32" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
+      <c r="D65" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E65" s="27" t="inlineStr">
@@ -8352,26 +8283,22 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F65" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G65" s="34" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F65" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G65" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>Không so sánh linh kiện thay thế.</t>
-        </is>
-      </c>
+          <t>eaa/handover.py SwapAnalysis · TC-59c,d</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
@@ -8389,9 +8316,9 @@
           <t>Chẩn đoán sự cố ngoài hiện trường</t>
         </is>
       </c>
-      <c r="D66" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D66" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E66" s="27" t="inlineStr">
@@ -8411,14 +8338,10 @@
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>eaa diagnose select + hai kênh · TC-27</t>
-        </is>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>Chọn kịch bản từ triệu chứng được; không dựng lại điều kiện sự cố, không xử lý ca không tái hiện.</t>
-        </is>
-      </c>
+          <t>eaa/diagnostics.py FieldCase · TC-59e,f</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
@@ -8436,36 +8359,32 @@
           <t>Cập nhật firmware cho thiết bị đã triển khai</t>
         </is>
       </c>
-      <c r="D67" s="32" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
-        </is>
-      </c>
-      <c r="E67" s="35" t="inlineStr">
+      <c r="D67" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E67" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="F67" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G67" s="34" t="inlineStr">
-        <is>
-          <t>−2</t>
+      <c r="F67" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G67" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>Không có cập nhật firmware cho thiết bị đã triển khai.</t>
-        </is>
-      </c>
+          <t>eaa/handover.py RolloutPlan · TC-59g,h</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
@@ -8574,12 +8493,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E70" s="35" t="inlineStr">
+      <c r="E70" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="F70" s="35" t="inlineStr">
+      <c r="F70" s="31" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -8612,7 +8531,7 @@
           <t>Nói rõ mức tin cậy của mọi điều mình nói</t>
         </is>
       </c>
-      <c r="D71" s="30" t="inlineStr">
+      <c r="D71" s="36" t="inlineStr">
         <is>
           <t>Một phần</t>
         </is>
@@ -8622,7 +8541,7 @@
           <t>T4</t>
         </is>
       </c>
-      <c r="F71" s="31" t="inlineStr">
+      <c r="F71" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -8634,12 +8553,12 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>serialport.match_confirmed, telemetry.bad_ratio, AssumptionLog</t>
+          <t>eaa/confidence.py — bộ từ vựng chung · TC-60a,b,c</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>Có ở vài chỗ; CHƯA nhất quán toàn hệ — nhiều đầu ra không nói mức tin cậy.</t>
+          <t>Đã có MỘT bộ từ vựng và năm chỗ quy về nó (kiểm sau nạp, errata, tham số mô hình, bảng chân, chạy dài); các đầu ra còn lại vẫn chưa gắn nhãn.</t>
         </is>
       </c>
     </row>
@@ -8659,17 +8578,17 @@
           <t>Quản lý chi phí gọi mô hình</t>
         </is>
       </c>
-      <c r="D72" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
-        </is>
-      </c>
-      <c r="E72" s="31" t="inlineStr">
+      <c r="D72" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E72" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F72" s="31" t="inlineStr">
+      <c r="F72" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -8681,14 +8600,10 @@
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>eaa/kpi.py (tokens_in/out) · TC-09</t>
-        </is>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>Ghi được token; không có trần theo module, không quy ra chi phí, không cảnh báo.</t>
-        </is>
-      </c>
+          <t>eaa/budget.py TokenBudget · TC-53e,f</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
@@ -8706,36 +8621,32 @@
           <t>Ghi nhận mọi sai lệch so với thiết kế</t>
         </is>
       </c>
-      <c r="D73" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
-        </is>
-      </c>
-      <c r="E73" s="31" t="inlineStr">
+      <c r="D73" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E73" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F73" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G73" s="34" t="inlineStr">
-        <is>
-          <t>−3</t>
+      <c r="F73" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G73" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>docs/SAI_LECH_THIET_KE.md (40 mục)</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>Nhật ký đầy đủ, nhưng do TÔI ghi tay — Agent không tự phát hiện và không tự ghi.</t>
-        </is>
-      </c>
+          <t>eaa/deviation.py + eaa deviations · TC-60d,e,f</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
@@ -8753,9 +8664,9 @@
           <t>Tự đánh giá và cải tiến quy trình</t>
         </is>
       </c>
-      <c r="D74" s="30" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D74" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E74" s="27" t="inlineStr">
@@ -8763,26 +8674,22 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F74" s="33" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G74" s="34" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F74" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G74" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>eaa report + kpi.summary · TC-09</t>
-        </is>
-      </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>Tổng hợp được chỉ số; không chỉ ra khâu hay hỏng, không đề xuất sửa prompt/quy tắc.</t>
-        </is>
-      </c>
+          <t>kpi.weak_points + eaa report review · TC-60g,h,i</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="13" t="inlineStr">

--- a/docs/EAA_Nghiep_vu_Agent.xlsx
+++ b/docs/EAA_Nghiep_vu_Agent.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,12 +68,8 @@
       <b val="1"/>
       <color rgb="009C0006"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C5700"/>
-    </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -130,11 +126,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -162,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -253,9 +244,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5425,10 +5413,10 @@
         <v>8</v>
       </c>
       <c r="C30" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D30" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="22" t="n">
         <v>0</v>
@@ -5450,10 +5438,10 @@
         <v>74</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="25" t="n">
         <v>1</v>
@@ -8531,9 +8519,9 @@
           <t>Nói rõ mức tin cậy của mọi điều mình nói</t>
         </is>
       </c>
-      <c r="D71" s="36" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D71" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E71" s="29" t="inlineStr">
@@ -8553,14 +8541,10 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>eaa/confidence.py — bộ từ vựng chung · TC-60a,b,c</t>
-        </is>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>Đã có MỘT bộ từ vựng và năm chỗ quy về nó (kiểm sau nạp, errata, tham số mô hình, bảng chân, chạy dài); các đầu ra còn lại vẫn chưa gắn nhãn.</t>
-        </is>
-      </c>
+          <t>eaa/confidence.py + Judged · TC-60a-c, TC-63a-e</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="13" t="inlineStr">

--- a/docs/EAA_Nghiep_vu_Agent.xlsx
+++ b/docs/EAA_Nghiep_vu_Agent.xlsx
@@ -69,7 +69,7 @@
       <color rgb="009C0006"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -121,11 +121,6 @@
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -153,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -242,9 +237,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5338,13 +5330,13 @@
         <v>7</v>
       </c>
       <c r="C27" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="22" t="n">
         <v>0</v>
@@ -5438,13 +5430,13 @@
         <v>74</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D31" s="25" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="25" t="n">
         <v>1</v>
@@ -7913,9 +7905,9 @@
           <t>Chẩn đoán sâu bằng công cụ gỡ lỗi</t>
         </is>
       </c>
-      <c r="D57" s="35" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
+      <c r="D57" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E57" s="27" t="inlineStr">
@@ -7935,12 +7927,12 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>eaa/debugsession.py + eaa debug plan/log/record · TC-75</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>Ngoài phạm vi đề án (đã ghi từ trước).</t>
+          <t>Đủ Ở ĐÚNG MỨC T0 — 'người làm, Agent ghi vết'. Agent dò mạch gỡ lỗi, dựng kế hoạch phiên từ tiêu chí kịch bản đã duyệt (mỗi bước khai trước hai nhánh kết luận), và ghi lại ai làm gì. Nó KHÔNG chạy phiên gỡ lỗi — việc ấy đòi mạch cắm vào bo thật và vẫn ngoài phạm vi đề án. Tên trình gỡ lỗi nằm ở packs/*/pack.yaml, không ở engine.</t>
         </is>
       </c>
     </row>

--- a/docs/EAA_Nghiep_vu_Agent.xlsx
+++ b/docs/EAA_Nghiep_vu_Agent.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Đối chiếu" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Nghiệp vụ'!$A$1:$I$75</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Đối chiếu'!$A$1:$I$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Nghiệp vụ'!$A$1:$I$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Đối chiếu'!$A$1:$I$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="009C5700"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="001F4E79"/>
     </font>
     <font>
@@ -69,7 +73,7 @@
       <color rgb="009C0006"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -118,7 +122,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -148,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -232,11 +246,17 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -801,7 +821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4340,8 +4360,290 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>N-908</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Phân biệt 'mã tôi sai' với 'bài kiểm tôi sai'</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Khi cổng đỏ: một phán đoán có lý lẽ về việc nên sửa mã hay nên sửa bài kiểm</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>Đầu ra cổng + mã + bài kiểm</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>Trước khi vá: đối chiếu con số bài kiểm đòi với con số suy ra từ vật lý/toán của bài toán. Lệch thì bài kiểm là nghi phạm, không phải mã. Mọi lần vá chạm vào HẰNG SỐ của bài kiểm phải nêu lý do bằng đại lượng vật lý, không bằng 'để bài kiểm xanh'.</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>Phân xử khi hai bên không khớp</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>Ba trong 12 lần từ chối G3 là mã tự chỉnh cho vừa đồ đo của chính nó, và cả ba qua sạch bốn cổng</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>N-909</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Phát hiện bài kiểm KHÔNG chứng minh điều nó nhận là mình chứng minh</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Danh sách bài kiểm 'rỗng': xanh cả với mã sai</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>Bài kiểm mới sinh + mã nó canh</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Với mỗi bài kiểm mới: tính xem đầu vào của nó có đủ ĐẨY hệ tới chỗ lỗi sẽ hiện ra không (đủ số vòng, đủ biên độ, đúng trạng thái khởi động). Đưa phép tính ấy vào hồ sơ G3 chứ không chỉ đưa màu của bài kiểm.</t>
+        </is>
+      </c>
+      <c r="G77" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>Đọc lại phép tính ở G3</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>Bài kiểm đỏ đúng lúc rồi xanh đúng lúc — vì một lý do khác — nguy hiểm hơn bài kiểm đỏ, vì lần sau không ai đọc lại nó nữa (§3.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>N-910</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Canh thoái lui giữa các lượt sinh của cùng một module</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Cảnh báo khi lượt sinh mới đánh mất thứ lượt trước đã có</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Mã trên main + mã vừa sinh</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>So khai báo hàm (đã có: eaa/contract.py, SL-163) VÀ so tập lời gọi khởi tạo trong hàm vào (app_init, main) — mất một lời gọi là mất im lặng, không cổng nào đỏ.</t>
+        </is>
+      </c>
+      <c r="G78" s="15" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>app_init() mất bốn lời gọi khởi tạo driver sau một vòng vá → firmware câm, 33 bài kiểm vẫn xanh</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>N-911</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Cảnh báo khi một phép chia trong chú thích ghép hai đại lượng khác thứ nguyên</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>Mã sinh ra + bảng đại lượng của dự án</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>Rút các biểu thức số trong chú thích `// a / b = c`, tra đơn vị của a và b trong hồ sơ phần cứng, báo khi phép chia không ra đơn vị nó nhận.</t>
+        </is>
+      </c>
+      <c r="G79" s="15" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>'4ms per step / 0.000031s per sample = 129' chia chu kỳ cho một hệ số ĐỘ TRÊN LSB. Con số vô nghĩa, chú thích nghe hợp lý, và nó là nguyên nhân robot không lấy đủ mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>N-912</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Mỗi module có ít nhất một đường báo lỗi ra ngoài mà người quan sát được</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>Bản phân rã module + phương tiện báo có trên bo (LED, còi, UART)</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>Khi phân rã: mỗi module khai một 'dấu hiệu sống' và một 'dấu hiệu hỏng' quan sát được mà không cần máy đo. Đưa vào tiêu chí nghiệm thu của module, không để thành việc thêm sau.</t>
+        </is>
+      </c>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>Chốt dấu hiệu nào đủ rõ trên bo cụ thể</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>Ba lượt nạp đầu robot chỉ 'im' hoặc 'ngã', không phân biệt được với chip chết. Mọi cải tiến quan sát — nhịp bíp, nút thoát, watchdog mất mẫu — đều do người thêm</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>N-913</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Đưa số đo từ phần cứng ngược vào prompt</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Lớp ngữ cảnh chứa số đo thật của bo, không chỉ số trong tài liệu</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>measurements.jsonl + kết quả chẩn đoán DS-xx</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>Thêm một lớp vào bộ ghép prompt: số đo đã duyệt của chính bo này (trôi con quay, mốc gia tốc, tốc độ bootloader, nhịp đo được). Số đo phải qua gate mới vào, cùng đường với tri thức.</t>
+        </is>
+      </c>
+      <c r="G81" s="16" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>Duyệt số đo nào được coi là đã chốt</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>Bài học từ bo hiện chỉ tới mô hình qua LÝ DO TỪ CHỐI kỹ sư gõ tay — mất là mất hẳn</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I75"/>
+  <autoFilter ref="A1:I81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5018,22 +5320,22 @@
         </is>
       </c>
       <c r="B14" s="20" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C14" s="20" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -5043,22 +5345,22 @@
         </is>
       </c>
       <c r="B15" s="21" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C15" s="21" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -5205,10 +5507,10 @@
         <v>8</v>
       </c>
       <c r="C22" s="22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D22" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="22" t="n">
         <v>0</v>
@@ -5380,10 +5682,10 @@
         <v>4</v>
       </c>
       <c r="C29" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="22" t="n">
         <v>0</v>
@@ -5402,22 +5704,22 @@
         </is>
       </c>
       <c r="B30" s="22" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C30" s="22" t="n">
         <v>8</v>
       </c>
       <c r="D30" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F30" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -5427,22 +5729,22 @@
         </is>
       </c>
       <c r="B31" s="25" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E31" s="25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5456,7 +5758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6611,9 +6913,9 @@
           <t>Quản lý vòng đời tri thức</t>
         </is>
       </c>
-      <c r="D27" s="26" t="inlineStr">
-        <is>
-          <t>Đủ</t>
+      <c r="D27" s="32" t="inlineStr">
+        <is>
+          <t>Một phần</t>
         </is>
       </c>
       <c r="E27" s="30" t="inlineStr">
@@ -6633,10 +6935,14 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>eaa/lifecycle.py (3 đường truy ngược) · TC-29</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr"/>
+          <t>eaa/lifecycle.py KnowledgeLifecycle (3 đường truy ngược) · TC-29</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Rà soát 04/09: KHÔNG module nào trong eaa/ import lifecycle, và không lệnh CLI nào gọi tới. `eaa docs regen` đi qua registry, không qua vòng đời tri thức. Cơ chế đúng, đường chạy chưa có</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -7385,7 +7691,7 @@
           <t>Chạy chính mã C sinh ra trong mô phỏng</t>
         </is>
       </c>
-      <c r="D45" s="32" t="inlineStr">
+      <c r="D45" s="33" t="inlineStr">
         <is>
           <t>Cố ý không làm</t>
         </is>
@@ -7395,12 +7701,12 @@
           <t>T3</t>
         </is>
       </c>
-      <c r="F45" s="33" t="inlineStr">
+      <c r="F45" s="34" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G45" s="34" t="inlineStr">
+      <c r="G45" s="35" t="inlineStr">
         <is>
           <t>−3</t>
         </is>
@@ -7867,12 +8173,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E56" s="33" t="inlineStr">
+      <c r="E56" s="34" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="F56" s="33" t="inlineStr">
+      <c r="F56" s="34" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
@@ -7915,12 +8221,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F57" s="33" t="inlineStr">
+      <c r="F57" s="34" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G57" s="34" t="inlineStr">
+      <c r="G57" s="35" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -8210,9 +8516,9 @@
           <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
         </is>
       </c>
-      <c r="D64" s="26" t="inlineStr">
-        <is>
-          <t>Đủ</t>
+      <c r="D64" s="32" t="inlineStr">
+        <is>
+          <t>Một phần</t>
         </is>
       </c>
       <c r="E64" s="27" t="inlineStr">
@@ -8232,10 +8538,14 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>eaa/lifecycle.py · TC-29</t>
-        </is>
-      </c>
-      <c r="I64" s="6" t="inlineStr"/>
+          <t>eaa/lifecycle.py StaleSet · TC-29</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>Cùng gốc với N-036: sửa một datasheet hiện KHÔNG có lệnh nào trả lời 'mã nào bị ảnh hưởng'. Cần một lệnh (vd `eaa knowledge stale`) nối StaleSet vào đường người dùng</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
@@ -8526,7 +8836,7 @@
           <t>T3</t>
         </is>
       </c>
-      <c r="G71" s="34" t="inlineStr">
+      <c r="G71" s="35" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -8710,8 +9020,290 @@
       </c>
       <c r="I75" s="6" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>N-908</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Phân biệt 'mã tôi sai' với 'bài kiểm tôi sai'</t>
+        </is>
+      </c>
+      <c r="D76" s="36" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E76" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="35" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có gì. Bốn cổng đo mã CÓ CHẠY KHÔNG, không đo mã có ĐANG ĐO ĐÚNG THỨ nó nhận không. Bằng chứng: 3/12 lần từ chối G3 (drv_imu, logic_pid, app_balance) · §3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>N-909</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Phát hiện bài kiểm KHÔNG chứng minh điều nó nhận là mình chứng minh</t>
+        </is>
+      </c>
+      <c r="D77" s="36" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E77" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="35" t="inlineStr">
+        <is>
+          <t>−2</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có gì. Cần một phép kiểm ĐỘ NHẠY: chạy lại bài kiểm mới trên bản mã SAI đã biết, xanh thì bài kiểm ấy rỗng. Bằng chứng: test_deadband_keeps_setpoint_steady · §3.3, §3.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>N-910</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Canh thoái lui giữa các lượt sinh của cùng một module</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E78" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F78" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G78" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>eaa/contract.py so khai báo header với bản trên main · TC-124 (16 bài)</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>Nửa đã có là CHỮ KÝ HÀM (SL-163). Nửa còn thiếu là TẬP LỜI GỌI trong hàm vào — mất một lời gọi khởi tạo không cổng nào đỏ. Bằng chứng: app_init() · §3.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>N-911</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
+        </is>
+      </c>
+      <c r="D79" s="36" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E79" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="35" t="inlineStr">
+        <is>
+          <t>−4</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có gì. Hồ sơ phần cứng đã khai đơn vị của từng đại lượng, nên dữ liệu để làm thì có sẵn. Bằng chứng: chú thích '4ms / 0.000031s = 129' · §3.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>N-912</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
+        </is>
+      </c>
+      <c r="D80" s="36" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E80" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="35" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có gì. eaa/decompose.py chưa đòi module khai dấu hiệu sống/hỏng; eaa/propose.py AcceptanceProposal chưa sinh tiêu chí quan sát được bằng mắt/tai · §3.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>N-913</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Đưa số đo từ phần cứng ngược vào prompt</t>
+        </is>
+      </c>
+      <c r="D81" s="36" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E81" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="35" t="inlineStr">
+        <is>
+          <t>−3</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có gì. measurements.jsonl và kết quả DS-xx nằm NGOÀI eaa/composer.py. Đây là mục đắt nhất trong sáu mục, vì nó đụng vào bộ ghép prompt và vào gate tri thức · §3.7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I75"/>
+  <autoFilter ref="A1:I81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/EAA_Nghiep_vu_Agent.xlsx
+++ b/docs/EAA_Nghiep_vu_Agent.xlsx
@@ -5707,10 +5707,10 @@
         <v>14</v>
       </c>
       <c r="C30" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="22" t="n">
         <v>5</v>
@@ -5732,10 +5732,10 @@
         <v>80</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" s="25" t="n">
         <v>5</v>
@@ -9130,9 +9130,9 @@
           <t>Canh thoái lui giữa các lượt sinh của cùng một module</t>
         </is>
       </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D78" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E78" s="29" t="inlineStr">
@@ -9152,14 +9152,10 @@
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>eaa/contract.py so khai báo header với bản trên main · TC-124 (16 bài)</t>
-        </is>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>Nửa đã có là CHỮ KÝ HÀM (SL-163). Nửa còn thiếu là TẬP LỜI GỌI trong hàm vào — mất một lời gọi khởi tạo không cổng nào đỏ. Bằng chứng: app_init() · §3.2</t>
-        </is>
-      </c>
+          <t>eaa/contract.py: pha_vo_hop_dong so chữ ký header (SL-163, TC-124) + mat_loi_goi so tập lời gọi LIÊN MODULE của tệp .c với bản đã merge (SL-167, TC-127, 33 bài)</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="13" t="inlineStr">

--- a/docs/EAA_Nghiep_vu_Agent.xlsx
+++ b/docs/EAA_Nghiep_vu_Agent.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Đối chiếu" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Nghiệp vụ'!$A$1:$I$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Đối chiếu'!$A$1:$I$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Nghiệp vụ'!$A$1:$I$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Đối chiếu'!$A$1:$I$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -821,7 +821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2154,54 +2154,54 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>N-040</t>
+          <t>N-038</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>GĐ4 · Thiết kế &amp; phân rã</t>
+          <t>GĐ3 · Tri thức phần cứng</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Phân rã bài toán thành module</t>
+          <t>Trả lời câu hỏi kỹ thuật từ kho tri thức ĐÃ DUYỆT</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Danh sách module, mỗi module một trách nhiệm rõ</t>
+          <t>Trích đoạn đúng chỗ cho một câu hỏi tự do, kèm mã chunk để tra ngược</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Phát biểu bài toán, kiến trúc đã chọn</t>
+          <t>Câu hỏi bằng lời + kho trích đoạn đã qua G2</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Đề xuất phân rã theo ngoại vi và theo tầng (driver / logic / điều phối); mỗi module nêu rõ trách nhiệm, tài nguyên chiếm, và tiêu chí xong.</t>
-        </is>
-      </c>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>T1</t>
+          <t>Hai tầng, đúng thứ tự của đường sinh mã: đồ thị chỉ đích danh trước (chỉ khi câu hỏi gọi tên một module của dự án), BM25 lấp sau với ngưỡng độ phủ. CHỈ trả trích đoạn đã duyệt; chunk còn chờ được NÊU TÊN nhưng không tính vào kết quả. Chất lượng truy xuất đo được bằng bộ chuẩn, không bằng cảm giác.</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>T4</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Duyệt danh sách module</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>Phân rã sai làm module phụ thuộc chằng chịt, không kiểm chứng riêng được</t>
+          <t>Toàn bộ giá trị của G2 nằm ở chỗ một người đã đọc bản gốc. Đường hỏi-đáp không chạm được vào kết quả ấy thì câu trả lời tụt xuống hạng chưa kiểm mà không có gì nói ra điều đó</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>N-041</t>
+          <t>N-040</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -2211,44 +2211,44 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Định nghĩa giao diện giữa module</t>
+          <t>Phân rã bài toán thành module</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Tệp tiêu đề: hàm, kiểu dữ liệu, hợp đồng gọi</t>
+          <t>Danh sách module, mỗi module một trách nhiệm rõ</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Danh sách module</t>
+          <t>Phát biểu bài toán, kiến trúc đã chọn</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Sinh giao diện TRƯỚC khi sinh phần thân, để module phụ thuộc có thể làm song song. Nêu rõ hàm nào gọi trong ngắt được, hàm nào chặn, hàm nào tái nhập được.</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>T2</t>
+          <t>Đề xuất phân rã theo ngoại vi và theo tầng (driver / logic / điều phối); mỗi module nêu rõ trách nhiệm, tài nguyên chiếm, và tiêu chí xong.</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Duyệt giao diện</t>
+          <t>Duyệt danh sách module</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>Đổi giao diện sau khi đã viết thân là sửa lan ra mọi nơi gọi tới</t>
+          <t>Phân rã sai làm module phụ thuộc chằng chịt, không kiểm chứng riêng được</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>N-042</t>
+          <t>N-041</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -2258,44 +2258,44 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Xếp thứ tự làm theo phụ thuộc</t>
+          <t>Định nghĩa giao diện giữa module</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Thứ tự module, và cái nào làm song song được</t>
+          <t>Tệp tiêu đề: hàm, kiểu dữ liệu, hợp đồng gọi</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Đồ thị phụ thuộc</t>
+          <t>Danh sách module</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Sắp topo theo phụ thuộc; làm driver trước, logic sau; nêu rõ module nào chặn module nào để người biết đường ưu tiên.</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>T3</t>
+          <t>Sinh giao diện TRƯỚC khi sinh phần thân, để module phụ thuộc có thể làm song song. Nêu rõ hàm nào gọi trong ngắt được, hàm nào chặn, hàm nào tái nhập được.</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Duyệt giao diện</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>Làm sai thứ tự thì phải giả lập phụ thuộc, tốn công gấp đôi</t>
+          <t>Đổi giao diện sau khi đã viết thân là sửa lan ra mọi nơi gọi tới</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>N-043</t>
+          <t>N-042</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -2305,91 +2305,91 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Thiết kế lịch chạy</t>
+          <t>Xếp thứ tự làm theo phụ thuộc</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Bảng việc: module nào chạy mỗi bao nhiêu, ưu tiên ra sao</t>
+          <t>Thứ tự module, và cái nào làm song song được</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Ràng buộc thời gian, danh sách module</t>
+          <t>Đồ thị phụ thuộc</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>Đề xuất chu kỳ từ yêu cầu vật lý (chu kỳ điều khiển, tốc độ lấy mẫu); kiểm tổng tải CPU ước lượng; cảnh báo khi tổng vượt 100% hoặc khi một việc dài hơn chu kỳ của việc khác.</t>
-        </is>
-      </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>T1</t>
+          <t>Sắp topo theo phụ thuộc; làm driver trước, logic sau; nêu rõ module nào chặn module nào để người biết đường ưu tiên.</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Chốt chu kỳ từng việc</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>Chu kỳ là quyết định vật lý — máy đọc được tên hàm, không đọc được rằng con lắc cần 10 ms</t>
+          <t>Làm sai thứ tự thì phải giả lập phụ thuộc, tốn công gấp đôi</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>N-050</t>
+          <t>N-043</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>GĐ5 · Sinh mã &amp; kiểm chứng tĩnh</t>
+          <t>GĐ4 · Thiết kế &amp; phân rã</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Sinh mã một module</t>
+          <t>Thiết kế lịch chạy</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Mã nguồn + tệp tiêu đề của module</t>
+          <t>Bảng việc: module nào chạy mỗi bao nhiêu, ưu tiên ra sao</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Đặc tả module, tri thức đã duyệt, ràng buộc</t>
+          <t>Ràng buộc thời gian, danh sách module</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Nén ngữ cảnh có ngân sách: ràng buộc luôn có mặt, trích đoạn liên quan được chọn theo đồ thị, giao diện module phụ thuộc kèm theo. Mã cấu hình thanh ghi BẮT BUỘC trích dẫn nguồn.</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>T2</t>
+          <t>Đề xuất chu kỳ từ yêu cầu vật lý (chu kỳ điều khiển, tốc độ lấy mẫu); kiểm tổng tải CPU ước lượng; cảnh báo khi tổng vượt 100% hoặc khi một việc dài hơn chu kỳ của việc khác.</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Review diff trước khi hợp nhất</t>
+          <t>Chốt chu kỳ từng việc</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>Mã không trích dẫn nguồn thì không phân biệt được tra được với bịa ra</t>
+          <t>Chu kỳ là quyết định vật lý — máy đọc được tên hàm, không đọc được rằng con lắc cần 10 ms</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>N-051</t>
+          <t>N-050</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -2399,44 +2399,44 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Biên dịch</t>
+          <t>Sinh mã một module</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Tệp đối tượng, hoặc danh sách lỗi có vị trí</t>
+          <t>Mã nguồn + tệp tiêu đề của module</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Mã nguồn, toolchain</t>
+          <t>Đặc tả module, tri thức đã duyệt, ràng buộc</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>Dịch từng tệp riêng (không liên kết), vì một module driver không có hàm main và không cần có. Dịch hết mọi tệp rồi mới kết luận, để lượt sửa thấy đủ lỗi.</t>
-        </is>
-      </c>
-      <c r="G34" s="15" t="inlineStr">
-        <is>
-          <t>T4</t>
+          <t>Nén ngữ cảnh có ngân sách: ràng buộc luôn có mặt, trích đoạn liên quan được chọn theo đồ thị, giao diện module phụ thuộc kèm theo. Mã cấu hình thanh ghi BẮT BUỘC trích dẫn nguồn.</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Review diff trước khi hợp nhất</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>Gộp dịch với liên kết làm mọi module trượt vì lý do chẳng liên quan tới chất lượng mã</t>
+          <t>Mã không trích dẫn nguồn thì không phân biệt được tra được với bịa ra</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>N-052</t>
+          <t>N-051</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -2446,22 +2446,22 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Phân tích tĩnh theo ràng buộc dự án</t>
+          <t>Biên dịch</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Danh sách vi phạm, có vị trí và mã quy tắc</t>
+          <t>Tệp đối tượng, hoặc danh sách lỗi có vị trí</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Mã nguồn, bộ quy tắc nền tảng + ràng buộc dự án</t>
+          <t>Mã nguồn, toolchain</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Hợp nhất quy tắc của nền tảng với điều cấm của dự án. Dự án khai Ý ĐỊNH ('cấm hàm chặn'), nền tảng lo cách phát hiện ý định ấy. Thiếu quy tắc cho một điều cấm là LỖI CẤU HÌNH, không phải đạt.</t>
+          <t>Dịch từng tệp riêng (không liên kết), vì một module driver không có hàm main và không cần có. Dịch hết mọi tệp rồi mới kết luận, để lượt sửa thấy đủ lỗi.</t>
         </is>
       </c>
       <c r="G35" s="15" t="inlineStr">
@@ -2476,14 +2476,14 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>Cổng chỉ chặn được thứ nó ĐƯỢC BẢO là cấm; im lặng ở đây là cho qua</t>
+          <t>Gộp dịch với liên kết làm mọi module trượt vì lý do chẳng liên quan tới chất lượng mã</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>N-053</t>
+          <t>N-052</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Kiểm thử đơn vị trên máy chủ</t>
+          <t>Phân tích tĩnh theo ràng buộc dự án</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Kết quả test, độ phủ</t>
+          <t>Danh sách vi phạm, có vị trí và mã quy tắc</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Mã nguồn, lớp trừu tượng phần cứng giả</t>
+          <t>Mã nguồn, bộ quy tắc nền tảng + ràng buộc dự án</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Chạy logic thuần trên máy chủ qua lớp phần cứng giả; tập trung vào tính toán và máy trạng thái. Nêu rõ phần nào KHÔNG kiểm được trên máy chủ.</t>
+          <t>Hợp nhất quy tắc của nền tảng với điều cấm của dự án. Dự án khai Ý ĐỊNH ('cấm hàm chặn'), nền tảng lo cách phát hiện ý định ấy. Thiếu quy tắc cho một điều cấm là LỖI CẤU HÌNH, không phải đạt.</t>
         </is>
       </c>
       <c r="G36" s="15" t="inlineStr">
@@ -2523,14 +2523,14 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>Nhầm 'qua test trên máy chủ' với 'chạy đúng trên chip' là ngộ nhận tốn kém nhất</t>
+          <t>Cổng chỉ chặn được thứ nó ĐƯỢC BẢO là cấm; im lặng ở đây là cho qua</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>N-054</t>
+          <t>N-053</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -2540,22 +2540,22 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Đo chiếm dụng bộ nhớ</t>
+          <t>Kiểm thử đơn vị trên máy chủ</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Số byte flash/RAM, đối chiếu ngân sách</t>
+          <t>Kết quả test, độ phủ</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Tệp đối tượng hoặc ảnh liên kết</t>
+          <t>Mã nguồn, lớp trừu tượng phần cứng giả</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Đo và so với ngân sách đã chia. Nói rõ đang đo tầm MODULE hay tầm FIRMWARE — trần của cả firmware áp lên một module lẻ là phép kiểm dễ dãi hơn nó trông.</t>
+          <t>Chạy logic thuần trên máy chủ qua lớp phần cứng giả; tập trung vào tính toán và máy trạng thái. Nêu rõ phần nào KHÔNG kiểm được trên máy chủ.</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr">
@@ -2570,14 +2570,14 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>Đo nhầm tầm làm ngân sách mất tác dụng đúng lúc cần nhất</t>
+          <t>Nhầm 'qua test trên máy chủ' với 'chạy đúng trên chip' là ngộ nhận tốn kém nhất</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>N-055</t>
+          <t>N-054</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -2587,44 +2587,44 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Vòng tự sửa khi cổng không đạt</t>
+          <t>Đo chiếm dụng bộ nhớ</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Mã đã sửa, hoặc bàn giao người sau N lần</t>
+          <t>Số byte flash/RAM, đối chiếu ngân sách</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Báo cáo cổng hỏng</t>
+          <t>Tệp đối tượng hoặc ảnh liên kết</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Gửi bản vá kèm ĐÚNG lỗi và hàm liên quan, không gửi lại cả tệp. Tối đa N lần rồi dừng. Lỗi môi trường và lỗi cấu hình KHÔNG vào vòng này — mô hình không sửa được chúng.</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="inlineStr">
-        <is>
-          <t>T3</t>
+          <t>Đo và so với ngân sách đã chia. Nói rõ đang đo tầm MODULE hay tầm FIRMWARE — trần của cả firmware áp lên một module lẻ là phép kiểm dễ dãi hơn nó trông.</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>T4</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Nhận bàn giao khi quá N lần</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>Đốt lượt sửa vào lỗi môi trường làm mất luôn cơ hội sửa lỗi thật</t>
+          <t>Đo nhầm tầm làm ngân sách mất tác dụng đúng lúc cần nhất</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>N-056</t>
+          <t>N-055</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -2634,44 +2634,44 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Review và hợp nhất</t>
+          <t>Vòng tự sửa khi cổng không đạt</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Mã vào nhánh chính, kèm dấu vết đầy đủ</t>
+          <t>Mã đã sửa, hoặc bàn giao người sau N lần</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Toàn bộ báo cáo cổng đều đạt</t>
+          <t>Báo cáo cổng hỏng</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Trình diff kèm bảng kiểm sinh từ đồ thị tri thức (thanh ghi nào phải đối chiếu). Hợp nhất CHỈ khi mọi cổng đạt VÀ người duyệt; băm nội dung nối liền 'thứ đã duyệt' với 'thứ được hợp nhất'.</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
-        <is>
-          <t>T2</t>
+          <t>Gửi bản vá kèm ĐÚNG lỗi và hàm liên quan, không gửi lại cả tệp. Tối đa N lần rồi dừng. Lỗi môi trường và lỗi cấu hình KHÔNG vào vòng này — mô hình không sửa được chúng.</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Duyệt diff</t>
+          <t>Nhận bàn giao khi quá N lần</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>Một nhánh thứ hai dẫn tới hợp nhất là chỗ mọi bất biến bị vô hiệu</t>
+          <t>Đốt lượt sửa vào lỗi môi trường làm mất luôn cơ hội sửa lỗi thật</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>N-057</t>
+          <t>N-056</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -2681,91 +2681,91 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Ghi nhận lỗi mô hình bịa ra</t>
+          <t>Review và hợp nhất</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Nhật ký: bịa cái gì, phát hiện ở cổng nào, sửa ra sao</t>
+          <t>Mã vào nhánh chính, kèm dấu vết đầy đủ</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Kết quả các cổng</t>
+          <t>Toàn bộ báo cáo cổng đều đạt</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Mỗi lần mã dùng thanh ghi không có thật, hoặc giá trị không khớp nguồn, thì ghi lại. Nhật ký này là dữ liệu cho chương đánh giá, và là đầu vào cải tiến prompt.</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr">
-        <is>
-          <t>T3</t>
+          <t>Trình diff kèm bảng kiểm sinh từ đồ thị tri thức (thanh ghi nào phải đối chiếu). Hợp nhất CHỈ khi mọi cổng đạt VÀ người duyệt; băm nội dung nối liền 'thứ đã duyệt' với 'thứ được hợp nhất'.</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Duyệt diff</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>Không đo được tỉ lệ bịa thì không chứng minh được quy trình có tác dụng</t>
+          <t>Một nhánh thứ hai dẫn tới hợp nhất là chỗ mọi bất biến bị vô hiệu</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>N-060</t>
+          <t>N-057</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>GĐ6 · Mô phỏng</t>
+          <t>GĐ5 · Sinh mã &amp; kiểm chứng tĩnh</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Dựng mô hình đối tượng điều khiển</t>
+          <t>Ghi nhận lỗi mô hình bịa ra</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Mô hình toán của đối tượng, có tham số vật lý</t>
+          <t>Nhật ký: bịa cái gì, phát hiện ở cổng nào, sửa ra sao</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Thông số cơ khí, điện</t>
+          <t>Kết quả các cổng</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>Đề xuất mô hình từ loại đối tượng (con lắc ngược, động cơ, nhiệt); tham số chưa đo được thì vào danh mục giả định. Nêu rõ mô hình bỏ qua hiện tượng nào.</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>T1</t>
+          <t>Mỗi lần mã dùng thanh ghi không có thật, hoặc giá trị không khớp nguồn, thì ghi lại. Nhật ký này là dữ liệu cho chương đánh giá, và là đầu vào cải tiến prompt.</t>
+        </is>
+      </c>
+      <c r="G41" s="16" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Duyệt mô hình và tham số</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>Mô hình sai làm mọi kết quả mô phỏng thành vô nghĩa mà vẫn trông thuyết phục</t>
+          <t>Không đo được tỉ lệ bịa thì không chứng minh được quy trình có tác dụng</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>N-061</t>
+          <t>N-060</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -2775,44 +2775,44 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Chạy mô phỏng vòng kín</t>
+          <t>Dựng mô hình đối tượng điều khiển</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Quỹ đạo, các chỉ số chất lượng điều khiển</t>
+          <t>Mô hình toán của đối tượng, có tham số vật lý</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Mô hình, mã điều khiển, kịch bản</t>
+          <t>Thông số cơ khí, điện</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>Chạy các kịch bản đã khai (khởi động, nhiễu, tải nặng); tính chỉ số theo định nghĩa viết ra được (thời gian ổn định đo từ đâu tới đâu).</t>
-        </is>
-      </c>
-      <c r="G42" s="15" t="inlineStr">
-        <is>
-          <t>T4</t>
+          <t>Đề xuất mô hình từ loại đối tượng (con lắc ngược, động cơ, nhiệt); tham số chưa đo được thì vào danh mục giả định. Nêu rõ mô hình bỏ qua hiện tượng nào.</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Duyệt mô hình và tham số</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>Chỉ số định nghĩa mơ hồ thì hai lần đo không so được với nhau</t>
+          <t>Mô hình sai làm mọi kết quả mô phỏng thành vô nghĩa mà vẫn trông thuyết phục</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>N-062</t>
+          <t>N-061</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -2822,44 +2822,44 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Quét tham số và đề xuất bộ tham số</t>
+          <t>Chạy mô phỏng vòng kín</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Bảng kết quả theo tham số, và bộ được gợi ý</t>
+          <t>Quỹ đạo, các chỉ số chất lượng điều khiển</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Mô hình, dải tham số</t>
+          <t>Mô hình, mã điều khiển, kịch bản</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Quét lưới, xếp hạng theo chỉ số, nêu rõ tham số nào thật sự quyết định kết quả. Gợi ý một bộ kèm lý do; không tự chốt.</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>T1</t>
+          <t>Chạy các kịch bản đã khai (khởi động, nhiễu, tải nặng); tính chỉ số theo định nghĩa viết ra được (thời gian ổn định đo từ đâu tới đâu).</t>
+        </is>
+      </c>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>T4</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Chọn bộ tham số</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>Tự chốt tham số là quyết định thay người ở chỗ ảnh hưởng trực tiếp tới an toàn</t>
+          <t>Chỉ số định nghĩa mơ hồ thì hai lần đo không so được với nhau</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>N-063</t>
+          <t>N-062</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -2869,44 +2869,44 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Tiêm lỗi trong mô phỏng</t>
+          <t>Quét tham số và đề xuất bộ tham số</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Hành vi hệ thống khi cảm biến hỏng/trôi/mất</t>
+          <t>Bảng kết quả theo tham số, và bộ được gợi ý</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Mô hình, phân tích hỏng hóc</t>
+          <t>Mô hình, dải tham số</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Tiêm từng lỗi đã liệt kê ở N-016: cảm biến trả rác, mất mẫu, trôi điểm không, nguồn sụt. Kiểm hệ có vào chế độ an toàn không.</t>
-        </is>
-      </c>
-      <c r="G44" s="16" t="inlineStr">
-        <is>
-          <t>T3</t>
+          <t>Quét lưới, xếp hạng theo chỉ số, nêu rõ tham số nào thật sự quyết định kết quả. Gợi ý một bộ kèm lý do; không tự chốt.</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Chọn bộ tham số</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>Chỉ thử đường đi thuận là chỉ chứng minh hệ chạy khi không có gì hỏng</t>
+          <t>Tự chốt tham số là quyết định thay người ở chỗ ảnh hưởng trực tiếp tới an toàn</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>N-064</t>
+          <t>N-063</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Chạy chính mã C sinh ra trong mô phỏng</t>
+          <t>Tiêm lỗi trong mô phỏng</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Kết quả mô phỏng dùng artifact thật, không phải bản chép tay</t>
+          <t>Hành vi hệ thống khi cảm biến hỏng/trôi/mất</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Mã đã dịch, mô hình</t>
+          <t>Mô hình, phân tích hỏng hóc</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Nối mã nguồn thật vào mô hình qua lớp phần cứng giả. Nếu chưa làm được thì phải nói rõ mô phỏng đang chạy MÔ HÌNH của thuật toán chứ không phải mã sẽ nạp.</t>
+          <t>Tiêm từng lỗi đã liệt kê ở N-016: cảm biến trả rác, mất mẫu, trôi điểm không, nguồn sụt. Kiểm hệ có vào chế độ an toàn không.</t>
         </is>
       </c>
       <c r="G45" s="16" t="inlineStr">
@@ -2946,61 +2946,61 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>Mô phỏng một bản chép tay rồi kết luận cho bản sẽ nạp là ngộ nhận âm thầm</t>
+          <t>Chỉ thử đường đi thuận là chỉ chứng minh hệ chạy khi không có gì hỏng</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>N-070</t>
+          <t>N-064</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>GĐ7 · Ráp &amp; nạp</t>
+          <t>GĐ6 · Mô phỏng</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Ráp firmware hoàn chỉnh</t>
+          <t>Chạy chính mã C sinh ra trong mô phỏng</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Ảnh liên kết từ mọi module đã hợp nhất + vòng lặp chính</t>
+          <t>Kết quả mô phỏng dùng artifact thật, không phải bản chép tay</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Module đã merge, bản thiết kế ráp</t>
+          <t>Mã đã dịch, mô hình</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>Sinh vòng lặp chính từ khuôn của nền tảng và bảng việc của dự án. MỌI module đã merge phải có mặt trong bản thiết kế ráp — bỏ quên là LỖI, không phải cảnh báo.</t>
-        </is>
-      </c>
-      <c r="G46" s="17" t="inlineStr">
-        <is>
-          <t>T2</t>
+          <t>Nối mã nguồn thật vào mô hình qua lớp phần cứng giả. Nếu chưa làm được thì phải nói rõ mô phỏng đang chạy MÔ HÌNH của thuật toán chứ không phải mã sẽ nạp.</t>
+        </is>
+      </c>
+      <c r="G46" s="16" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>Duyệt bản thiết kế ráp</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>Firmware thiếu một module đã qua kiểm chứng là thứ mà mọi bằng chứng đều nói là có</t>
+          <t>Mô phỏng một bản chép tay rồi kết luận cho bản sẽ nạp là ngộ nhận âm thầm</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>N-071</t>
+          <t>N-070</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -3010,44 +3010,44 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Kiểm bộ nhớ ở tầm firmware</t>
+          <t>Ráp firmware hoàn chỉnh</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Số byte thật của ảnh sẽ nạp, đối chiếu ngân sách</t>
+          <t>Ảnh liên kết từ mọi module đã hợp nhất + vòng lặp chính</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Ảnh liên kết</t>
+          <t>Module đã merge, bản thiết kế ráp</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Đây là lần đầu ngưỡng bộ nhớ áp lên thứ sẽ thật sự chạy. Kiểm cả khoảng trống ngăn xếp còn lại, không chỉ tổng flash.</t>
-        </is>
-      </c>
-      <c r="G47" s="15" t="inlineStr">
-        <is>
-          <t>T4</t>
+          <t>Sinh vòng lặp chính từ khuôn của nền tảng và bảng việc của dự án. MỌI module đã merge phải có mặt trong bản thiết kế ráp — bỏ quên là LỖI, không phải cảnh báo.</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Duyệt bản thiết kế ráp</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>Tràn ngăn xếp là lỗi hiện ra ngẫu nhiên, rất khó lần ra nguyên nhân</t>
+          <t>Firmware thiếu một module đã qua kiểm chứng là thứ mà mọi bằng chứng đều nói là có</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>N-072</t>
+          <t>N-071</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -3057,44 +3057,44 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Kiểm trước khi nạp</t>
+          <t>Kiểm bộ nhớ ở tầm firmware</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Kết luận: được nạp hay không, kèm lý do</t>
+          <t>Số byte thật của ảnh sẽ nạp, đối chiếu ngân sách</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Ảnh, kho mã, nhật ký nạp</t>
+          <t>Ảnh liên kết</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>Bốn phép kiểm đều là 'không' chứ không phải cảnh báo: có ảnh · kho mã sạch · ảnh mới hơn nguồn · người xác nhận.</t>
-        </is>
-      </c>
-      <c r="G48" s="17" t="inlineStr">
-        <is>
-          <t>T2</t>
+          <t>Đây là lần đầu ngưỡng bộ nhớ áp lên thứ sẽ thật sự chạy. Kiểm cả khoảng trống ngăn xếp còn lại, không chỉ tổng flash.</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>T4</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Xác nhận nạp</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>Nạp ảnh cũ là cách hỏng âm thầm nhất: mạch chạy mã cũ, người đọc mã mới</t>
+          <t>Tràn ngăn xếp là lỗi hiện ra ngẫu nhiên, rất khó lần ra nguyên nhân</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>N-073</t>
+          <t>N-072</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -3104,44 +3104,44 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Chọn đúng thiết bị để nạp</t>
+          <t>Kiểm trước khi nạp</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Cổng/mạch nạp đã xác định chắc chắn</t>
+          <t>Kết luận: được nạp hay không, kèm lý do</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Danh sách thiết bị dò được, hồ sơ bo</t>
+          <t>Ảnh, kho mã, nhật ký nạp</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Tự chọn CHỈ khi danh tính xác nhận bằng VID/PID. Khớp theo tên cổng là phỏng đoán — cắm hai bo cùng lúc thì gợi ý tên rất dễ trúng nhầm.</t>
-        </is>
-      </c>
-      <c r="G49" s="16" t="inlineStr">
-        <is>
-          <t>T3</t>
+          <t>Bốn phép kiểm đều là 'không' chứ không phải cảnh báo: có ảnh · kho mã sạch · ảnh mới hơn nguồn · người xác nhận.</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>Chỉ định cổng khi mơ hồ</t>
+          <t>Xác nhận nạp</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>Nạp nhầm thiết bị là hỏng thật, không phải một lượt chạy lại</t>
+          <t>Nạp ảnh cũ là cách hỏng âm thầm nhất: mạch chạy mã cũ, người đọc mã mới</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>N-074</t>
+          <t>N-073</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -3151,44 +3151,44 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Nạp và ghi nhật ký</t>
+          <t>Chọn đúng thiết bị để nạp</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Firmware trên chip; bản ghi: commit nào, ảnh nào, cổng nào, ai, lúc nào</t>
+          <t>Cổng/mạch nạp đã xác định chắc chắn</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Ảnh đã kiểm, xác nhận của người</t>
+          <t>Danh sách thiết bị dò được, hồ sơ bo</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Nạp qua công cụ của nền tảng; ghi cả lần TRƯỢT, vì 'đã thử và trượt' là dữ kiện chẩn đoán y như 'đã nạp xong'.</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="inlineStr">
-        <is>
-          <t>T2</t>
+          <t>Tự chọn CHỈ khi danh tính xác nhận bằng VID/PID. Khớp theo tên cổng là phỏng đoán — cắm hai bo cùng lúc thì gợi ý tên rất dễ trúng nhầm.</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Xác nhận</t>
+          <t>Chỉ định cổng khi mơ hồ</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>Không biết bản nào đang trên chip thì mọi số đo về sau đều mất neo</t>
+          <t>Nạp nhầm thiết bị là hỏng thật, không phải một lượt chạy lại</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>N-075</t>
+          <t>N-074</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -3198,69 +3198,69 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Kiểm sau khi nạp</t>
+          <t>Nạp và ghi nhật ký</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Xác nhận thứ trên chip đúng là thứ vừa gửi đi</t>
+          <t>Firmware trên chip; bản ghi: commit nào, ảnh nào, cổng nào, ai, lúc nào</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Ảnh, thiết bị</t>
+          <t>Ảnh đã kiểm, xác nhận của người</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>Đọc ngược bộ nhớ hoặc so kiểm tổng nếu mạch nạp hỗ trợ; nếu không hỗ trợ thì nói rõ là không kiểm được, đừng ngầm coi 'nạp không báo lỗi' là 'nạp đúng'.</t>
-        </is>
-      </c>
-      <c r="G51" s="16" t="inlineStr">
-        <is>
-          <t>T3</t>
+          <t>Nạp qua công cụ của nền tảng; ghi cả lần TRƯỢT, vì 'đã thử và trượt' là dữ kiện chẩn đoán y như 'đã nạp xong'.</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Xác nhận</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>Nạp lỗi một phần tạo ra hành vi kỳ quái không thể lần theo mã nguồn</t>
+          <t>Không biết bản nào đang trên chip thì mọi số đo về sau đều mất neo</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>N-080</t>
+          <t>N-075</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>GĐ8 · Đưa lên mạch &amp; đo</t>
+          <t>GĐ7 · Ráp &amp; nạp</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Thiết lập kênh đo</t>
+          <t>Kiểm sau khi nạp</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Kênh telemetry thông, khung tin kiểm được</t>
+          <t>Xác nhận thứ trên chip đúng là thứ vừa gửi đi</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Bo đã nạp, cổng nối tiếp</t>
+          <t>Ảnh, thiết bị</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>Khung tin có checksum và nhãn thời gian; luôn có hạn thời gian chờ; khung hỏng được ĐẾM chứ không nuốt; giữ bản ghi nguyên văn.</t>
+          <t>Đọc ngược bộ nhớ hoặc so kiểm tổng nếu mạch nạp hỗ trợ; nếu không hỗ trợ thì nói rõ là không kiểm được, đừng ngầm coi 'nạp không báo lỗi' là 'nạp đúng'.</t>
         </is>
       </c>
       <c r="G52" s="16" t="inlineStr">
@@ -3275,14 +3275,14 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>Phiên đo nhiều khung hỏng vẫn cho ra vài con số trông hợp lý</t>
+          <t>Nạp lỗi một phần tạo ra hành vi kỳ quái không thể lần theo mã nguồn</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>N-081</t>
+          <t>N-080</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -3292,44 +3292,44 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Sinh firmware đo cho từng kịch bản chẩn đoán</t>
+          <t>Thiết lập kênh đo</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Ảnh firmware đo riêng cho mỗi kịch bản</t>
+          <t>Kênh telemetry thông, khung tin kiểm được</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Kịch bản chẩn đoán, khuôn của nền tảng</t>
+          <t>Bo đã nạp, cổng nối tiếp</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>Ghép khung của nền tảng với phần đo của dự án bằng LIÊN KẾT, không dán chuỗi. Kịch bản chưa khai phần đo thì DỪNG, không dựng firmware rỗng.</t>
-        </is>
-      </c>
-      <c r="G53" s="17" t="inlineStr">
-        <is>
-          <t>T2</t>
+          <t>Khung tin có checksum và nhãn thời gian; luôn có hạn thời gian chờ; khung hỏng được ĐẾM chứ không nuốt; giữ bản ghi nguyên văn.</t>
+        </is>
+      </c>
+      <c r="G53" s="16" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Duyệt trước khi nạp</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>Firmware đo im lặng không phân biệt được với mạch hỏng</t>
+          <t>Phiên đo nhiều khung hỏng vẫn cho ra vài con số trông hợp lý</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>N-082</t>
+          <t>N-081</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -3339,44 +3339,44 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Chẩn đoán hai kênh</t>
+          <t>Sinh firmware đo cho từng kịch bản chẩn đoán</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Kết luận nguyên nhân, có bằng chứng cả máy lẫn người</t>
+          <t>Ảnh firmware đo riêng cho mỗi kịch bản</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Telemetry, quan sát của người</t>
+          <t>Kịch bản chẩn đoán, khuôn của nền tảng</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Lấy GIAO của thứ máy đo được và thứ người quan sát được. Thiếu một kênh thì TỪ CHỐI kết luận. Kịch bản gây chuyển động đòi xác nhận đủ checklist an toàn.</t>
-        </is>
-      </c>
-      <c r="G54" s="14" t="inlineStr">
-        <is>
-          <t>T1</t>
+          <t>Ghép khung của nền tảng với phần đo của dự án bằng LIÊN KẾT, không dán chuỗi. Kịch bản chưa khai phần đo thì DỪNG, không dựng firmware rỗng.</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Trả lời quan sát; xác nhận an toàn</t>
+          <t>Duyệt trước khi nạp</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>Kết luận chỉ từ một kênh là đoán mò có vẻ khoa học</t>
+          <t>Firmware đo im lặng không phân biệt được với mạch hỏng</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>N-083</t>
+          <t>N-082</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -3386,44 +3386,44 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Đo đặc tính thời gian thực</t>
+          <t>Chẩn đoán hai kênh</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Chu kỳ thật, độ trễ, dao động chu kỳ, tải CPU</t>
+          <t>Kết luận nguyên nhân, có bằng chứng cả máy lẫn người</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Firmware đo, kênh telemetry</t>
+          <t>Telemetry, quan sát của người</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Đo trên thiết bị thật, không suy từ mô phỏng. So với ràng buộc thời gian đã chốt; nêu rõ trường hợp xấu nhất chứ không chỉ trung bình.</t>
-        </is>
-      </c>
-      <c r="G55" s="16" t="inlineStr">
-        <is>
-          <t>T3</t>
+          <t>Lấy GIAO của thứ máy đo được và thứ người quan sát được. Thiếu một kênh thì TỪ CHỐI kết luận. Kịch bản gây chuyển động đòi xác nhận đủ checklist an toàn.</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Trả lời quan sát; xác nhận an toàn</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>Trung bình đạt mà đỉnh trượt là lỗi chỉ xuất hiện lúc tải nặng</t>
+          <t>Kết luận chỉ từ một kênh là đoán mò có vẻ khoa học</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>N-084</t>
+          <t>N-083</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -3433,44 +3433,44 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Đo điện và nhiệt</t>
+          <t>Đo đặc tính thời gian thực</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Dòng tiêu thụ, sụt áp khi tải, nhiệt độ linh kiện</t>
+          <t>Chu kỳ thật, độ trễ, dao động chu kỳ, tải CPU</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Đồng hồ đo, thiết bị chạy</t>
+          <t>Firmware đo, kênh telemetry</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>Hướng dẫn người đo đích danh: đo ở điểm nào, trong điều kiện nào, giá trị chờ đợi bao nhiêu. Agent ghi lại và đối chiếu ngưỡng.</t>
-        </is>
-      </c>
-      <c r="G56" s="18" t="inlineStr">
-        <is>
-          <t>T0</t>
+          <t>Đo trên thiết bị thật, không suy từ mô phỏng. So với ràng buộc thời gian đã chốt; nêu rõ trường hợp xấu nhất chứ không chỉ trung bình.</t>
+        </is>
+      </c>
+      <c r="G56" s="16" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Thực hiện phép đo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>Sụt áp khi động cơ tăng tốc là nguyên nhân reset ngẫu nhiên rất hay bị bỏ sót</t>
+          <t>Trung bình đạt mà đỉnh trượt là lỗi chỉ xuất hiện lúc tải nặng</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>N-085</t>
+          <t>N-084</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -3480,44 +3480,44 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Chẩn đoán sâu bằng công cụ gỡ lỗi</t>
+          <t>Đo điện và nhiệt</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Trạng thái thanh ghi/bộ nhớ tại điểm dừng; vết thực thi</t>
+          <t>Dòng tiêu thụ, sụt áp khi tải, nhiệt độ linh kiện</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Mạch nạp có hỗ trợ gỡ lỗi</t>
+          <t>Đồng hồ đo, thiết bị chạy</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy, lấy vết. Chỉ cần khi hai kênh không đủ kết luận — nên xếp sau, không phải công cụ đầu tiên.</t>
-        </is>
-      </c>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>T1</t>
+          <t>Hướng dẫn người đo đích danh: đo ở điểm nào, trong điều kiện nào, giá trị chờ đợi bao nhiêu. Agent ghi lại và đối chiếu ngưỡng.</t>
+        </is>
+      </c>
+      <c r="G57" s="18" t="inlineStr">
+        <is>
+          <t>T0</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Điều khiển phiên gỡ lỗi</t>
+          <t>Thực hiện phép đo</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>Nhảy vào gỡ lỗi quá sớm tốn thời gian hơn đọc kỹ telemetry</t>
+          <t>Sụt áp khi động cơ tăng tốc là nguyên nhân reset ngẫu nhiên rất hay bị bỏ sót</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>N-086</t>
+          <t>N-085</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -3527,91 +3527,91 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Kiểm độ bền dài hạn</t>
+          <t>Chẩn đoán sâu bằng công cụ gỡ lỗi</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Kết quả chạy liên tục nhiều giờ: có reset không, có trôi không</t>
+          <t>Trạng thái thanh ghi/bộ nhớ tại điểm dừng; vết thực thi</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Thiết bị, kênh đo</t>
+          <t>Mạch nạp có hỗ trợ gỡ lỗi</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>Chạy dài, ghi liên tục, phát hiện reset (bộ đếm thời gian chạy nhảy về 0), trôi giá trị, rò bộ nhớ. Nêu rõ đã chạy bao lâu — 10 phút không kết luận được cho 10 giờ.</t>
-        </is>
-      </c>
-      <c r="G58" s="16" t="inlineStr">
-        <is>
-          <t>T3</t>
+          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy, lấy vết. Chỉ cần khi hai kênh không đủ kết luận — nên xếp sau, không phải công cụ đầu tiên.</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Bố trí điều kiện chạy dài</t>
+          <t>Điều khiển phiên gỡ lỗi</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>Lỗi tích lũy (trôi, tràn bộ đếm) chỉ lộ ra sau thời gian dài</t>
+          <t>Nhảy vào gỡ lỗi quá sớm tốn thời gian hơn đọc kỹ telemetry</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>N-090</t>
+          <t>N-086</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>GĐ9 · Nghiệm thu &amp; phát hành</t>
+          <t>GĐ8 · Đưa lên mạch &amp; đo</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Đối chiếu tiêu chí nghiệm thu</t>
+          <t>Kiểm độ bền dài hạn</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Bảng: tiêu chí — số đo — đạt/không</t>
+          <t>Kết quả chạy liên tục nhiều giờ: có reset không, có trôi không</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Số đo thật, tiêu chí đã chốt</t>
+          <t>Thiết bị, kênh đo</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>Rút số đo từ telemetry theo tiêu chí đã khai TỪ TRƯỚC. Thiếu một số đo đã khai là LỖI. Vượt ngưỡng thì không phong hạng.</t>
-        </is>
-      </c>
-      <c r="G59" s="17" t="inlineStr">
-        <is>
-          <t>T2</t>
+          <t>Chạy dài, ghi liên tục, phát hiện reset (bộ đếm thời gian chạy nhảy về 0), trôi giá trị, rò bộ nhớ. Nêu rõ đã chạy bao lâu — 10 phút không kết luận được cho 10 giờ.</t>
+        </is>
+      </c>
+      <c r="G59" s="16" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Nghiệm thu tại gate</t>
+          <t>Bố trí điều kiện chạy dài</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>Tiêu chí viết sau khi nhìn số thì phép đối chiếu không còn nghĩa gì</t>
+          <t>Lỗi tích lũy (trôi, tràn bộ đếm) chỉ lộ ra sau thời gian dài</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>N-091</t>
+          <t>N-090</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -3621,22 +3621,22 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Phong hạng chất lượng bản mã</t>
+          <t>Đối chiếu tiêu chí nghiệm thu</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>Hạng: dịch được / kiểm bằng mô phỏng / kiểm trên phần cứng</t>
+          <t>Bảng: tiêu chí — số đo — đạt/không</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Bằng chứng tương ứng từng hạng</t>
+          <t>Số đo thật, tiêu chí đã chốt</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>Hạng cao nhất đòi người duyệt VÀ số đo thật VÀ bản đang phong hạng phải là bản ĐANG CHẠY trên thiết bị (đối chiếu nhật ký nạp).</t>
+          <t>Rút số đo từ telemetry theo tiêu chí đã khai TỪ TRƯỚC. Thiếu một số đo đã khai là LỖI. Vượt ngưỡng thì không phong hạng.</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Duyệt phong hạng</t>
+          <t>Nghiệm thu tại gate</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>Phong hạng cho bản chưa từng chạy trên chip làm hỏng mọi lần quay lui về sau</t>
+          <t>Tiêu chí viết sau khi nhìn số thì phép đối chiếu không còn nghĩa gì</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>N-092</t>
+          <t>N-091</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -3668,44 +3668,44 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Giữ bản chạy tốt và quay lui</t>
+          <t>Phong hạng chất lượng bản mã</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Bản known-good; khả năng quay về nó</t>
+          <t>Hạng: dịch được / kiểm bằng mô phỏng / kiểm trên phần cứng</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Lịch sử phong hạng</t>
+          <t>Bằng chứng tương ứng từng hạng</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>Chỉ cập nhật bản known-good tại gate nghiệm thu. Quay lui không được làm mất bản known-good đang giữ.</t>
-        </is>
-      </c>
-      <c r="G61" s="16" t="inlineStr">
-        <is>
-          <t>T3</t>
+          <t>Hạng cao nhất đòi người duyệt VÀ số đo thật VÀ bản đang phong hạng phải là bản ĐANG CHẠY trên thiết bị (đối chiếu nhật ký nạp).</t>
+        </is>
+      </c>
+      <c r="G61" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Quyết định quay lui</t>
+          <t>Duyệt phong hạng</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>Không có đường lui thì một bản hỏng làm dừng cả kỳ thực nghiệm</t>
+          <t>Phong hạng cho bản chưa từng chạy trên chip làm hỏng mọi lần quay lui về sau</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>N-093</t>
+          <t>N-092</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -3715,22 +3715,22 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Xuất báo cáo và dấu vết</t>
+          <t>Giữ bản chạy tốt và quay lui</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Báo cáo: chỉ số, nhật ký quyết định, nguồn tri thức đã dùng</t>
+          <t>Bản known-good; khả năng quay về nó</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Toàn bộ nhật ký</t>
+          <t>Lịch sử phong hạng</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>Xuất bảng chỉ số cho báo cáo; mỗi kết quả truy được về prompt, model, phiên bản ràng buộc, trích đoạn đã dùng.</t>
+          <t>Chỉ cập nhật bản known-good tại gate nghiệm thu. Quay lui không được làm mất bản known-good đang giữ.</t>
         </is>
       </c>
       <c r="G62" s="16" t="inlineStr">
@@ -3740,19 +3740,19 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Quyết định quay lui</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>Kết quả không truy vết được thì không bảo vệ được</t>
+          <t>Không có đường lui thì một bản hỏng làm dừng cả kỳ thực nghiệm</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>N-094</t>
+          <t>N-093</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -3762,69 +3762,69 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Bàn giao tài liệu vận hành</t>
+          <t>Xuất báo cáo và dấu vết</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Hướng dẫn nạp, đo, chẩn đoán, và giới hạn đã biết</t>
+          <t>Báo cáo: chỉ số, nhật ký quyết định, nguồn tri thức đã dùng</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Toàn bộ dự án</t>
+          <t>Toàn bộ nhật ký</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Sinh tài liệu từ dữ liệu đã có (bảng chân, bảng việc, kịch bản chẩn đoán, giả định chưa kiểm). Nêu rõ điều hệ thống KHÔNG làm được.</t>
-        </is>
-      </c>
-      <c r="G63" s="14" t="inlineStr">
-        <is>
-          <t>T1</t>
+          <t>Xuất bảng chỉ số cho báo cáo; mỗi kết quả truy được về prompt, model, phiên bản ràng buộc, trích đoạn đã dùng.</t>
+        </is>
+      </c>
+      <c r="G63" s="16" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Duyệt tài liệu bàn giao</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>Bàn giao thiếu giới hạn đã biết là đẩy rủi ro sang người tiếp nhận</t>
+          <t>Kết quả không truy vết được thì không bảo vệ được</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>N-100</t>
+          <t>N-094</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>GĐ10 · Vận hành &amp; bảo trì</t>
+          <t>GĐ9 · Nghiệm thu &amp; phát hành</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
+          <t>Bàn giao tài liệu vận hành</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Danh sách module cần xem lại</t>
+          <t>Hướng dẫn nạp, đo, chẩn đoán, và giới hạn đã biết</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Trích đoạn mới, errata mới</t>
+          <t>Toàn bộ dự án</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Truy ngược từ trích đoạn ra mã theo ba đường: đồ thị, trích dẫn trong mã, dấu vết commit. Đánh dấu cần xem lại, không tự sửa.</t>
+          <t>Sinh tài liệu từ dữ liệu đã có (bảng chân, bảng việc, kịch bản chẩn đoán, giả định chưa kiểm). Nêu rõ điều hệ thống KHÔNG làm được.</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -3834,66 +3834,66 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Quyết định sửa hay không</t>
+          <t>Duyệt tài liệu bàn giao</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>Không truy ngược được thì tài liệu đổi mà mã đứng yên</t>
+          <t>Bàn giao thiếu giới hạn đã biết là đẩy rủi ro sang người tiếp nhận</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>N-101</t>
+          <t>N-095</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>GĐ10 · Vận hành &amp; bảo trì</t>
+          <t>GĐ9 · Nghiệm thu &amp; phát hành</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Đánh giá ảnh hưởng khi linh kiện đổi</t>
+          <t>Sinh tài liệu thiết kế của chính dự án</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>So sánh linh kiện cũ/mới, danh sách chỗ phải sửa</t>
+          <t>URD, SRS, SDD, bảng chức năng, sơ đồ luồng — xuất ra định dạng nộp được</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Mã linh kiện thay thế</t>
+          <t>Hồ sơ dự án: ràng buộc, hồ sơ phần cứng, bản phân rã, sổ module</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>So bảng thanh ghi, dải hoạt động, sơ đồ chân giữa hai linh kiện; nêu đích danh khác biệt chạm vào mã nào.</t>
-        </is>
-      </c>
-      <c r="G65" s="14" t="inlineStr">
-        <is>
-          <t>T1</t>
+          <t>Dựng MỘT mô hình tài liệu rồi xuất nhiều định dạng (md, docx, pptx, xlsx, pdf), thay vì viết mỗi định dạng một lần. Nội dung rút TỪ HỒ SƠ đang có, không hỏi mô hình — một tài liệu lệch khỏi dự án nó mô tả thì tệ hơn không có tài liệu.</t>
+        </is>
+      </c>
+      <c r="G65" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Chọn linh kiện thay thế</t>
+          <t>Đọc và chỉnh trước khi nộp</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>Linh kiện 'tương đương' thường khác ở đúng chỗ dự án đang dùng</t>
+          <t>Tài liệu viết tay tách khỏi mã ngay từ ngày thứ hai, và không ai biết bản nào đúng</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>N-102</t>
+          <t>N-100</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -3903,22 +3903,22 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Chẩn đoán sự cố ngoài hiện trường</t>
+          <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Nguyên nhân, và bản sửa</t>
+          <t>Danh sách module cần xem lại</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Mô tả triệu chứng, log nếu có</t>
+          <t>Trích đoạn mới, errata mới</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>Chọn kịch bản chẩn đoán từ mô tả triệu chứng; dựng lại điều kiện; dùng hai kênh. Nếu không dựng lại được thì nói rõ là chưa kết luận được.</t>
+          <t>Truy ngược từ trích đoạn ra mã theo ba đường: đồ thị, trích dẫn trong mã, dấu vết commit. Đánh dấu cần xem lại, không tự sửa.</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -3928,19 +3928,19 @@
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>Cung cấp quan sát hiện trường</t>
+          <t>Quyết định sửa hay không</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>Kết luận vội cho sự cố không dựng lại được thường sửa nhầm chỗ</t>
+          <t>Không truy ngược được thì tài liệu đổi mà mã đứng yên</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>N-103</t>
+          <t>N-101</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -3950,138 +3950,138 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Cập nhật firmware cho thiết bị đã triển khai</t>
+          <t>Đánh giá ảnh hưởng khi linh kiện đổi</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Quy trình cập nhật an toàn, có đường lui</t>
+          <t>So sánh linh kiện cũ/mới, danh sách chỗ phải sửa</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Bản mới đã nghiệm thu</t>
+          <t>Mã linh kiện thay thế</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Kiểm tương thích ngược; có cơ chế quay lui khi cập nhật hỏng; không cập nhật hàng loạt trước khi thử trên một thiết bị.</t>
-        </is>
-      </c>
-      <c r="G67" s="17" t="inlineStr">
-        <is>
-          <t>T2</t>
+          <t>So bảng thanh ghi, dải hoạt động, sơ đồ chân giữa hai linh kiện; nêu đích danh khác biệt chạm vào mã nào.</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>Duyệt triển khai</t>
+          <t>Chọn linh kiện thay thế</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>Cập nhật hỏng trên thiết bị ở xa là thiết bị mất luôn</t>
+          <t>Linh kiện 'tương đương' thường khác ở đúng chỗ dự án đang dùng</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>N-900</t>
+          <t>N-102</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>XS · Xuyên suốt</t>
+          <t>GĐ10 · Vận hành &amp; bảo trì</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Giữ ranh giới tổng quát / nền tảng / dự án</t>
+          <t>Chẩn đoán sự cố ngoài hiện trường</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Engine không chứa tri thức của một họ chip nào</t>
+          <t>Nguyên nhân, và bản sửa</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Toàn bộ mã</t>
+          <t>Mô tả triệu chứng, log nếu có</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>Quét tự động mỗi lần commit: tên chip, tên thanh ghi, tên công cụ của một hãng không được nằm trong lõi. Thiếu năng lực thì mở rộng interface, không thêm nhánh rẽ.</t>
-        </is>
-      </c>
-      <c r="G68" s="15" t="inlineStr">
-        <is>
-          <t>T4</t>
+          <t>Chọn kịch bản chẩn đoán từ mô tả triệu chứng; dựng lại điều kiện; dùng hai kênh. Nếu không dựng lại được thì nói rõ là chưa kết luận được.</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Cung cấp quan sát hiện trường</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>Mất ranh giới thì sản phẩm thành công cụ cho đúng một con chip</t>
+          <t>Kết luận vội cho sự cố không dựng lại được thường sửa nhầm chỗ</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>N-901</t>
+          <t>N-103</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>XS · Xuyên suốt</t>
+          <t>GĐ10 · Vận hành &amp; bảo trì</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Bảo vệ khóa và bí mật</t>
+          <t>Cập nhật firmware cho thiết bị đã triển khai</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Khóa không lọt vào log, commit, prompt, thông báo lỗi</t>
+          <t>Quy trình cập nhật an toàn, có đường lui</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Biến môi trường</t>
+          <t>Bản mới đã nghiệm thu</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>Khóa chỉ đọc từ biến môi trường; che ở mọi lối ra; test tự động kiểm điều này.</t>
-        </is>
-      </c>
-      <c r="G69" s="15" t="inlineStr">
-        <is>
-          <t>T4</t>
+          <t>Kiểm tương thích ngược; có cơ chế quay lui khi cập nhật hỏng; không cập nhật hàng loạt trước khi thử trên một thiết bị.</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Duyệt triển khai</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>Khóa lọt vào kho Git là sự cố không thu hồi được</t>
+          <t>Cập nhật hỏng trên thiết bị ở xa là thiết bị mất luôn</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>N-902</t>
+          <t>N-900</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -4091,44 +4091,44 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Không bao giờ hành động ngoài ý muốn người</t>
+          <t>Giữ ranh giới tổng quát / nền tảng / dự án</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Mọi việc chạm vào máy hoặc thiết bị đều có xác nhận</t>
+          <t>Engine không chứa tri thức của một họ chip nào</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Toàn bộ mã</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>Cài đặt, nạp, xóa, gửi ra ngoài đều đòi xác nhận. Phiên không có người KHÔNG được coi là người đã đồng ý. Không có cờ dòng lệnh nào bỏ qua được.</t>
-        </is>
-      </c>
-      <c r="G70" s="17" t="inlineStr">
-        <is>
-          <t>T2</t>
+          <t>Quét tự động mỗi lần commit: tên chip, tên thanh ghi, tên công cụ của một hãng không được nằm trong lõi. Thiếu năng lực thì mở rộng interface, không thêm nhánh rẽ.</t>
+        </is>
+      </c>
+      <c r="G70" s="15" t="inlineStr">
+        <is>
+          <t>T4</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>Xác nhận từng lần</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>Một cờ bỏ qua tồn tại là một cờ sẽ được dùng lúc vội</t>
+          <t>Mất ranh giới thì sản phẩm thành công cụ cho đúng một con chip</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>N-903</t>
+          <t>N-901</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -4138,22 +4138,22 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Nói rõ mức tin cậy của mọi điều mình nói</t>
+          <t>Bảo vệ khóa và bí mật</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Mỗi kết luận kèm nguồn hoặc kèm nhãn 'chưa chắc'</t>
+          <t>Khóa không lọt vào log, commit, prompt, thông báo lỗi</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Biến môi trường</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>Phân biệt ĐÃ KIỂM / SUY RA / GIẢ ĐỊNH ở mọi đầu ra. Không đọc được thì nói không đọc được, thay vì trả một câu trả lời trông giống như đã kiểm.</t>
+          <t>Khóa chỉ đọc từ biến môi trường; che ở mọi lối ra; test tự động kiểm điều này.</t>
         </is>
       </c>
       <c r="G71" s="15" t="inlineStr">
@@ -4168,14 +4168,14 @@
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>Một dòng 'không khớp' sai tệ hơn một dòng 'không nhận diện được' đúng</t>
+          <t>Khóa lọt vào kho Git là sự cố không thu hồi được</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>N-904</t>
+          <t>N-902</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -4185,44 +4185,44 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>Quản lý chi phí gọi mô hình</t>
+          <t>Không bao giờ hành động ngoài ý muốn người</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Số token và chi phí theo module, có trần</t>
+          <t>Mọi việc chạm vào máy hoặc thiết bị đều có xác nhận</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Nhật ký gọi mô hình</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>Kiểm ngân sách TRƯỚC khi gọi; ghi số token mỗi lần; cảnh báo khi một module ăn quá phần của nó.</t>
-        </is>
-      </c>
-      <c r="G72" s="16" t="inlineStr">
-        <is>
-          <t>T3</t>
+          <t>Cài đặt, nạp, xóa, gửi ra ngoài đều đòi xác nhận. Phiên không có người KHÔNG được coi là người đã đồng ý. Không có cờ dòng lệnh nào bỏ qua được.</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>Duyệt khi vượt trần</t>
+          <t>Xác nhận từng lần</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>Chi phí không đo được thì không tối ưu được, và dễ vượt ngoài dự tính</t>
+          <t>Một cờ bỏ qua tồn tại là một cờ sẽ được dùng lúc vội</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>N-905</t>
+          <t>N-903</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Ghi nhận mọi sai lệch so với thiết kế</t>
+          <t>Nói rõ mức tin cậy của mọi điều mình nói</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Nhật ký sai lệch: lệch gì, vì sao, ảnh hưởng gì</t>
+          <t>Mỗi kết luận kèm nguồn hoặc kèm nhãn 'chưa chắc'</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -4247,29 +4247,29 @@
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>Buộc phải lệch thì ghi lại ngay kèm lý do và cập nhật tài liệu tương ứng; không lệch ngầm.</t>
-        </is>
-      </c>
-      <c r="G73" s="16" t="inlineStr">
-        <is>
-          <t>T3</t>
+          <t>Phân biệt ĐÃ KIỂM / SUY RA / GIẢ ĐỊNH ở mọi đầu ra. Không đọc được thì nói không đọc được, thay vì trả một câu trả lời trông giống như đã kiểm.</t>
+        </is>
+      </c>
+      <c r="G73" s="15" t="inlineStr">
+        <is>
+          <t>T4</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>Duyệt sai lệch lớn</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>Lệch ngầm làm tài liệu và mã kể hai câu chuyện khác nhau</t>
+          <t>Một dòng 'không khớp' sai tệ hơn một dòng 'không nhận diện được' đúng</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>N-906</t>
+          <t>N-904</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -4279,44 +4279,44 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Tự đánh giá và cải tiến quy trình</t>
+          <t>Quản lý chi phí gọi mô hình</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Chỉ số theo thời gian: tỉ lệ qua cổng, số lần tự sửa, lỗi bịa</t>
+          <t>Số token và chi phí theo module, có trần</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Nhật ký các vòng chạy</t>
+          <t>Nhật ký gọi mô hình</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>Tổng hợp chỉ số qua các module; chỉ ra khâu nào hay hỏng nhất; đề xuất sửa prompt hoặc sửa quy tắc.</t>
-        </is>
-      </c>
-      <c r="G74" s="14" t="inlineStr">
-        <is>
-          <t>T1</t>
+          <t>Kiểm ngân sách TRƯỚC khi gọi; ghi số token mỗi lần; cảnh báo khi một module ăn quá phần của nó.</t>
+        </is>
+      </c>
+      <c r="G74" s="16" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>Quyết định thay đổi quy trình</t>
+          <t>Duyệt khi vượt trần</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>Không đo thì mọi cải tiến chỉ là cảm giác</t>
+          <t>Chi phí không đo được thì không tối ưu được, và dễ vượt ngoài dự tính</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>N-907</t>
+          <t>N-905</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -4326,44 +4326,44 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Khôi phục sau gián đoạn</t>
+          <t>Ghi nhận mọi sai lệch so với thiết kế</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Phiên tiếp tục đúng chỗ đã dừng</t>
+          <t>Nhật ký sai lệch: lệch gì, vì sao, ảnh hưởng gì</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Trạng thái dự án</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>Ghi trạng thái nguyên tử, sống sót qua treo máy; khi mở lại thì nói rõ đang ở đâu và bước kế tiếp là gì.</t>
-        </is>
-      </c>
-      <c r="G75" s="15" t="inlineStr">
-        <is>
-          <t>T4</t>
+          <t>Buộc phải lệch thì ghi lại ngay kèm lý do và cập nhật tài liệu tương ứng; không lệch ngầm.</t>
+        </is>
+      </c>
+      <c r="G75" s="16" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Duyệt sai lệch lớn</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>Mất trạng thái giữa chừng làm hỏng cả chuỗi dấu vết</t>
+          <t>Lệch ngầm làm tài liệu và mã kể hai câu chuyện khác nhau</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>N-908</t>
+          <t>N-906</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
@@ -4373,22 +4373,22 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Phân biệt 'mã tôi sai' với 'bài kiểm tôi sai'</t>
+          <t>Tự đánh giá và cải tiến quy trình</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>Khi cổng đỏ: một phán đoán có lý lẽ về việc nên sửa mã hay nên sửa bài kiểm</t>
+          <t>Chỉ số theo thời gian: tỉ lệ qua cổng, số lần tự sửa, lỗi bịa</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Đầu ra cổng + mã + bài kiểm</t>
+          <t>Nhật ký các vòng chạy</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>Trước khi vá: đối chiếu con số bài kiểm đòi với con số suy ra từ vật lý/toán của bài toán. Lệch thì bài kiểm là nghi phạm, không phải mã. Mọi lần vá chạm vào HẰNG SỐ của bài kiểm phải nêu lý do bằng đại lượng vật lý, không bằng 'để bài kiểm xanh'.</t>
+          <t>Tổng hợp chỉ số qua các module; chỉ ra khâu nào hay hỏng nhất; đề xuất sửa prompt hoặc sửa quy tắc.</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -4398,19 +4398,19 @@
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>Phân xử khi hai bên không khớp</t>
+          <t>Quyết định thay đổi quy trình</t>
         </is>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>Ba trong 12 lần từ chối G3 là mã tự chỉnh cho vừa đồ đo của chính nó, và cả ba qua sạch bốn cổng</t>
+          <t>Không đo thì mọi cải tiến chỉ là cảm giác</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>N-909</t>
+          <t>N-907</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -4420,44 +4420,44 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Phát hiện bài kiểm KHÔNG chứng minh điều nó nhận là mình chứng minh</t>
+          <t>Khôi phục sau gián đoạn</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Danh sách bài kiểm 'rỗng': xanh cả với mã sai</t>
+          <t>Phiên tiếp tục đúng chỗ đã dừng</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Bài kiểm mới sinh + mã nó canh</t>
+          <t>Trạng thái dự án</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>Với mỗi bài kiểm mới: tính xem đầu vào của nó có đủ ĐẨY hệ tới chỗ lỗi sẽ hiện ra không (đủ số vòng, đủ biên độ, đúng trạng thái khởi động). Đưa phép tính ấy vào hồ sơ G3 chứ không chỉ đưa màu của bài kiểm.</t>
-        </is>
-      </c>
-      <c r="G77" s="17" t="inlineStr">
-        <is>
-          <t>T2</t>
+          <t>Ghi trạng thái nguyên tử, sống sót qua treo máy; khi mở lại thì nói rõ đang ở đâu và bước kế tiếp là gì.</t>
+        </is>
+      </c>
+      <c r="G77" s="15" t="inlineStr">
+        <is>
+          <t>T4</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>Đọc lại phép tính ở G3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>Bài kiểm đỏ đúng lúc rồi xanh đúng lúc — vì một lý do khác — nguy hiểm hơn bài kiểm đỏ, vì lần sau không ai đọc lại nó nữa (§3.8)</t>
+          <t>Mất trạng thái giữa chừng làm hỏng cả chuỗi dấu vết</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>N-910</t>
+          <t>N-914</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -4467,44 +4467,44 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Canh thoái lui giữa các lượt sinh của cùng một module</t>
+          <t>Người chọn mô hình, hệ không tự chọn</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Cảnh báo khi lượt sinh mới đánh mất thứ lượt trước đã có</t>
+          <t>Danh mục mã model đã kiểm, kèm chỗ mạnh chỗ yếu; mã đang dùng ghim trong Project State</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Mã trên main + mã vừa sinh</t>
+          <t>Khóa API, danh mục</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>So khai báo hàm (đã có: eaa/contract.py, SL-163) VÀ so tập lời gọi khởi tạo trong hàm vào (app_init, main) — mất một lời gọi là mất im lặng, không cổng nào đỏ.</t>
-        </is>
-      </c>
-      <c r="G78" s="15" t="inlineStr">
-        <is>
-          <t>T4</t>
+          <t>In ra những mã ĐÃ KIỂM với API nhà cung cấp, mỗi mã kèm ngày kiểm. Nhận cả mã ngoài danh mục — nhà cung cấp ra model mới nhanh hơn tài liệu — nhưng lúc ấy nói rõ là CHƯA KIỂM. Không có cơ chế nào tự đổi model giữa chừng.</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Chọn model, và trả tiền cho lựa chọn ấy</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>app_init() mất bốn lời gọi khởi tạo driver sau một vòng vá → firmware câm, 33 bài kiểm vẫn xanh</t>
+          <t>Tự đổi model giữa chừng phá tính tái lập: hai lần chạy cùng một lệnh rơi vào hai model, và lúc kết quả lệch thì không biết lệch vì model hay vì đầu vào</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>N-911</t>
+          <t>N-915</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -4514,22 +4514,22 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
+          <t>Hoán đổi nhà cung cấp mô hình mà hành vi không đổi</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Cảnh báo khi một phép chia trong chú thích ghép hai đại lượng khác thứ nguyên</t>
+          <t>Cùng một vòng lặp chạy được trên mô hình thật, mô hình giả, và bản phát lại</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Mã sinh ra + bảng đại lượng của dự án</t>
+          <t>Một adapter khai đúng giao diện</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>Rút các biểu thức số trong chú thích `// a / b = c`, tra đơn vị của a và b trong hồ sơ phần cứng, báo khi phép chia không ra đơn vị nó nhận.</t>
+          <t>Vòng lặp chỉ gọi qua giao diện chung; đổi adapter chỉ đổi trường ghi trong chỉ số, không đổi một nhánh xử lý nào. Bản phát lại đọc nhật ký lời gọi đã ghi và CỐ Ý không bịa phản hồi khi trượt băm — một lượt phát lại tự sinh nội dung là bằng chứng giả.</t>
         </is>
       </c>
       <c r="G79" s="15" t="inlineStr">
@@ -4544,14 +4544,14 @@
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>'4ms per step / 0.000031s per sample = 129' chia chu kỳ cho một hệ số ĐỘ TRÊN LSB. Con số vô nghĩa, chú thích nghe hợp lý, và nó là nguyên nhân robot không lấy đủ mẫu</t>
+          <t>Khóa vào một nhà cung cấp là đặt cả đề án vào tay một bảng giá và một lịch ngừng dịch vụ</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>N-912</t>
+          <t>N-908</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
@@ -4561,22 +4561,22 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
+          <t>Phân biệt 'mã tôi sai' với 'bài kiểm tôi sai'</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Mỗi module có ít nhất một đường báo lỗi ra ngoài mà người quan sát được</t>
+          <t>Khi cổng đỏ: một phán đoán có lý lẽ về việc nên sửa mã hay nên sửa bài kiểm</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Bản phân rã module + phương tiện báo có trên bo (LED, còi, UART)</t>
+          <t>Đầu ra cổng + mã + bài kiểm</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>Khi phân rã: mỗi module khai một 'dấu hiệu sống' và một 'dấu hiệu hỏng' quan sát được mà không cần máy đo. Đưa vào tiêu chí nghiệm thu của module, không để thành việc thêm sau.</t>
+          <t>Trước khi vá: đối chiếu con số bài kiểm đòi với con số suy ra từ vật lý/toán của bài toán. Lệch thì bài kiểm là nghi phạm, không phải mã. Mọi lần vá chạm vào HẰNG SỐ của bài kiểm phải nêu lý do bằng đại lượng vật lý, không bằng 'để bài kiểm xanh'.</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -4586,64 +4586,252 @@
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>Chốt dấu hiệu nào đủ rõ trên bo cụ thể</t>
+          <t>Phân xử khi hai bên không khớp</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>Ba lượt nạp đầu robot chỉ 'im' hoặc 'ngã', không phân biệt được với chip chết. Mọi cải tiến quan sát — nhịp bíp, nút thoát, watchdog mất mẫu — đều do người thêm</t>
+          <t>Ba trong 12 lần từ chối G3 là mã tự chỉnh cho vừa đồ đo của chính nó, và cả ba qua sạch bốn cổng</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
+          <t>N-909</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Phát hiện bài kiểm KHÔNG chứng minh điều nó nhận là mình chứng minh</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Danh sách bài kiểm 'rỗng': xanh cả với mã sai</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>Bài kiểm mới sinh + mã nó canh</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>Với mỗi bài kiểm mới: tính xem đầu vào của nó có đủ ĐẨY hệ tới chỗ lỗi sẽ hiện ra không (đủ số vòng, đủ biên độ, đúng trạng thái khởi động). Đưa phép tính ấy vào hồ sơ G3 chứ không chỉ đưa màu của bài kiểm.</t>
+        </is>
+      </c>
+      <c r="G81" s="17" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>Đọc lại phép tính ở G3</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>Bài kiểm đỏ đúng lúc rồi xanh đúng lúc — vì một lý do khác — nguy hiểm hơn bài kiểm đỏ, vì lần sau không ai đọc lại nó nữa (§3.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>N-910</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Canh thoái lui giữa các lượt sinh của cùng một module</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Cảnh báo khi lượt sinh mới đánh mất thứ lượt trước đã có</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>Mã trên main + mã vừa sinh</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>So khai báo hàm (đã có: eaa/contract.py, SL-163) VÀ so tập lời gọi khởi tạo trong hàm vào (app_init, main) — mất một lời gọi là mất im lặng, không cổng nào đỏ.</t>
+        </is>
+      </c>
+      <c r="G82" s="15" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>app_init() mất bốn lời gọi khởi tạo driver sau một vòng vá → firmware câm, 33 bài kiểm vẫn xanh</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>N-911</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Cảnh báo khi một phép chia trong chú thích ghép hai đại lượng khác thứ nguyên</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>Mã sinh ra + bảng đại lượng của dự án</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>Rút các biểu thức số trong chú thích `// a / b = c`, tra đơn vị của a và b trong hồ sơ phần cứng, báo khi phép chia không ra đơn vị nó nhận.</t>
+        </is>
+      </c>
+      <c r="G83" s="15" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>'4ms per step / 0.000031s per sample = 129' chia chu kỳ cho một hệ số ĐỘ TRÊN LSB. Con số vô nghĩa, chú thích nghe hợp lý, và nó là nguyên nhân robot không lấy đủ mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>N-912</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Mỗi module có ít nhất một đường báo lỗi ra ngoài mà người quan sát được</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>Bản phân rã module + phương tiện báo có trên bo (LED, còi, UART)</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>Khi phân rã: mỗi module khai một 'dấu hiệu sống' và một 'dấu hiệu hỏng' quan sát được mà không cần máy đo. Đưa vào tiêu chí nghiệm thu của module, không để thành việc thêm sau.</t>
+        </is>
+      </c>
+      <c r="G84" s="14" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>Chốt dấu hiệu nào đủ rõ trên bo cụ thể</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>Ba lượt nạp đầu robot chỉ 'im' hoặc 'ngã', không phân biệt được với chip chết. Mọi cải tiến quan sát — nhịp bíp, nút thoát, watchdog mất mẫu — đều do người thêm</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="inlineStr">
+        <is>
           <t>N-913</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>XS · Xuyên suốt</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>Đưa số đo từ phần cứng ngược vào prompt</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>Lớp ngữ cảnh chứa số đo thật của bo, không chỉ số trong tài liệu</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E85" s="6" t="inlineStr">
         <is>
           <t>measurements.jsonl + kết quả chẩn đoán DS-xx</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>Thêm một lớp vào bộ ghép prompt: số đo đã duyệt của chính bo này (trôi con quay, mốc gia tốc, tốc độ bootloader, nhịp đo được). Số đo phải qua gate mới vào, cùng đường với tri thức.</t>
         </is>
       </c>
-      <c r="G81" s="16" t="inlineStr">
+      <c r="G85" s="16" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="H85" s="6" t="inlineStr">
         <is>
           <t>Duyệt số đo nào được coi là đã chốt</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
+      <c r="I85" s="6" t="inlineStr">
         <is>
           <t>Bài học từ bo hiện chỉ tới mô hình qua LÝ DO TỪ CHỐI kỹ sư gõ tay — mất là mất hẳn</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I81"/>
+  <autoFilter ref="A1:I85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5120,7 +5308,7 @@
         </is>
       </c>
       <c r="B6" s="20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="20" t="n">
         <v>0</v>
@@ -5135,7 +5323,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -5270,7 +5458,7 @@
         </is>
       </c>
       <c r="B12" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="20" t="n">
         <v>0</v>
@@ -5279,7 +5467,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="20" t="n">
         <v>2</v>
@@ -5320,13 +5508,13 @@
         </is>
       </c>
       <c r="B14" s="20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C14" s="20" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="20" t="n">
         <v>2</v>
@@ -5335,7 +5523,7 @@
         <v>3</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -5345,22 +5533,22 @@
         </is>
       </c>
       <c r="B15" s="21" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C15" s="21" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15" s="21" t="n">
         <v>21</v>
       </c>
       <c r="G15" s="21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -5504,10 +5692,10 @@
         </is>
       </c>
       <c r="B22" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" s="22" t="n">
         <v>8</v>
-      </c>
-      <c r="C22" s="22" t="n">
-        <v>7</v>
       </c>
       <c r="D22" s="22" t="n">
         <v>1</v>
@@ -5654,10 +5842,10 @@
         </is>
       </c>
       <c r="B28" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" s="22" t="n">
         <v>0</v>
@@ -5704,22 +5892,22 @@
         </is>
       </c>
       <c r="B30" s="22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C30" s="22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D30" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F30" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -5729,22 +5917,22 @@
         </is>
       </c>
       <c r="B31" s="25" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5758,7 +5946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5903,7 +6091,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>eaa/brief.py probe_hardware · TC-49a</t>
+          <t>eaa/brief.py probe_hardware + eaa/usbdev.py (hỏi BO ĐÃ LÊN BUS CHƯA, khác hẳn câu có cổng nối tiếp không) + eaa/serialport.py · TC-49a, TC-85</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr"/>
@@ -5989,7 +6177,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>eaa/docplan.py plan_documents · TC-55a,b</t>
+          <t>eaa/docplan.py plan_documents + eaa/archive.py (nhận cả một kho nén hồ sơ: giải nén, phân loại, giữ nguyên bản gốc) · TC-55a,b</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr"/>
@@ -6720,7 +6908,7 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>eaa/ingest.py → G2 · TC-22</t>
+          <t>eaa/ingest.py → G2, đọc PDF qua eaa/pdftext.py — bọc pypdf và NÓI RA chỗ nó đọc không được thay vì trả về chuỗi rỗng · TC-22</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr"/>
@@ -6990,17 +7178,17 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>N-040</t>
+          <t>N-038</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>GĐ4 · Thiết kế &amp; phân rã</t>
+          <t>GĐ3 · Tri thức phần cứng</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Phân rã bài toán thành module</t>
+          <t>Trả lời câu hỏi kỹ thuật từ kho tri thức ĐÃ DUYỆT</t>
         </is>
       </c>
       <c r="D29" s="26" t="inlineStr">
@@ -7008,14 +7196,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E29" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
+      <c r="E29" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F29" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
         </is>
       </c>
       <c r="G29" s="28" t="inlineStr">
@@ -7025,7 +7213,7 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>eaa/decompose.py + eaa plan propose · TC-50 (32 test)</t>
+          <t>eaa/rag.py search_chunks (đồ thị trước, BM25 sau) + lệnh eaa recall + mục recall trong TOOLBOX; chất lượng truy xuất đo bằng eaa/goldenset.py — precision@k trên bộ chuẩn, eaa report retrieval · SL-166, TC-126, TC-20</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr"/>
@@ -7033,7 +7221,7 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>N-041</t>
+          <t>N-040</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -7043,7 +7231,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Định nghĩa giao diện giữa module</t>
+          <t>Phân rã bài toán thành module</t>
         </is>
       </c>
       <c r="D30" s="26" t="inlineStr">
@@ -7051,14 +7239,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E30" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="F30" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
+      <c r="E30" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="G30" s="28" t="inlineStr">
@@ -7068,7 +7256,7 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>eaa/interfaces.py + khuôn interfaces của pack · TC-56a..e</t>
+          <t>eaa/decompose.py + eaa plan propose · TC-50 (32 test)</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr"/>
@@ -7076,7 +7264,7 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>N-042</t>
+          <t>N-041</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -7086,7 +7274,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Xếp thứ tự làm theo phụ thuộc</t>
+          <t>Định nghĩa giao diện giữa module</t>
         </is>
       </c>
       <c r="D31" s="26" t="inlineStr">
@@ -7094,14 +7282,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E31" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="F31" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F31" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="G31" s="28" t="inlineStr">
@@ -7111,7 +7299,7 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>decompose.order()/parallel_groups() · TC-50b</t>
+          <t>eaa/interfaces.py + khuôn interfaces của pack · TC-56a..e</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr"/>
@@ -7119,7 +7307,7 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>N-043</t>
+          <t>N-042</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -7129,7 +7317,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Thiết kế lịch chạy</t>
+          <t>Xếp thứ tự làm theo phụ thuộc</t>
         </is>
       </c>
       <c r="D32" s="26" t="inlineStr">
@@ -7137,14 +7325,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E32" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="F32" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
+      <c r="E32" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F32" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="G32" s="28" t="inlineStr">
@@ -7154,7 +7342,7 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>decompose: chu kỳ + tải CPU + 3 phép kiểm · TC-50c</t>
+          <t>decompose.order()/parallel_groups() · TC-50b</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr"/>
@@ -7162,17 +7350,17 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>N-050</t>
+          <t>N-043</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>GĐ5 · Sinh mã &amp; kiểm chứng tĩnh</t>
+          <t>GĐ4 · Thiết kế &amp; phân rã</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Sinh mã một module</t>
+          <t>Thiết kế lịch chạy</t>
         </is>
       </c>
       <c r="D33" s="26" t="inlineStr">
@@ -7180,14 +7368,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E33" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="F33" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
+      <c r="E33" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="G33" s="28" t="inlineStr">
@@ -7197,7 +7385,7 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>eaa/composer.py + orchestrator · TC-04, TC-17</t>
+          <t>decompose: chu kỳ + tải CPU + 3 phép kiểm · TC-50c</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr"/>
@@ -7205,7 +7393,7 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>N-051</t>
+          <t>N-050</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -7215,7 +7403,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Biên dịch</t>
+          <t>Sinh mã một module</t>
         </is>
       </c>
       <c r="D34" s="26" t="inlineStr">
@@ -7223,14 +7411,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E34" s="29" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="F34" s="29" t="inlineStr">
-        <is>
-          <t>T4</t>
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F34" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="G34" s="28" t="inlineStr">
@@ -7240,7 +7428,7 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>eaa/tools/compile.py CompileGate · TC-40</t>
+          <t>eaa/composer.py + orchestrator · TC-04, TC-17</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr"/>
@@ -7248,7 +7436,7 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>N-052</t>
+          <t>N-051</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -7258,7 +7446,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Phân tích tĩnh theo ràng buộc dự án</t>
+          <t>Biên dịch</t>
         </is>
       </c>
       <c r="D35" s="26" t="inlineStr">
@@ -7283,7 +7471,7 @@
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>eaa/tools/static.py · TC-07</t>
+          <t>eaa/tools/compile.py CompileGate · TC-40</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr"/>
@@ -7291,7 +7479,7 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>N-053</t>
+          <t>N-052</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -7301,7 +7489,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Kiểm thử đơn vị trên máy chủ</t>
+          <t>Phân tích tĩnh theo ràng buộc dự án</t>
         </is>
       </c>
       <c r="D36" s="26" t="inlineStr">
@@ -7326,7 +7514,7 @@
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>eaa/tools/unittests.py host_gaps · TC-56f,g</t>
+          <t>eaa/tools/static.py · TC-07</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr"/>
@@ -7334,7 +7522,7 @@
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>N-054</t>
+          <t>N-053</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -7344,7 +7532,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Đo chiếm dụng bộ nhớ</t>
+          <t>Kiểm thử đơn vị trên máy chủ</t>
         </is>
       </c>
       <c r="D37" s="26" t="inlineStr">
@@ -7369,7 +7557,7 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>eaa/tools/compile.py SizeGate + size_scope · TC-40d</t>
+          <t>eaa/tools/unittests.py host_gaps · TC-56f,g</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr"/>
@@ -7377,7 +7565,7 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>N-055</t>
+          <t>N-054</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -7387,7 +7575,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Vòng tự sửa khi cổng không đạt</t>
+          <t>Đo chiếm dụng bộ nhớ</t>
         </is>
       </c>
       <c r="D38" s="26" t="inlineStr">
@@ -7395,14 +7583,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E38" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="F38" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
+      <c r="E38" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F38" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
         </is>
       </c>
       <c r="G38" s="28" t="inlineStr">
@@ -7412,7 +7600,7 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>eaa/orchestrator.py · TC-06, TC-19</t>
+          <t>eaa/tools/compile.py SizeGate + size_scope · TC-40d</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr"/>
@@ -7420,7 +7608,7 @@
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>N-056</t>
+          <t>N-055</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -7430,7 +7618,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Review và hợp nhất</t>
+          <t>Vòng tự sửa khi cổng không đạt</t>
         </is>
       </c>
       <c r="D39" s="26" t="inlineStr">
@@ -7438,14 +7626,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E39" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="F39" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
+      <c r="E39" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F39" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="G39" s="28" t="inlineStr">
@@ -7455,7 +7643,7 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>eaa/gates.py + vcs.py content_digest · TC-01</t>
+          <t>eaa/orchestrator.py · TC-06, TC-19</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr"/>
@@ -7463,7 +7651,7 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>N-057</t>
+          <t>N-056</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -7473,7 +7661,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Ghi nhận lỗi mô hình bịa ra</t>
+          <t>Review và hợp nhất</t>
         </is>
       </c>
       <c r="D40" s="26" t="inlineStr">
@@ -7481,14 +7669,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E40" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="F40" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
+      <c r="E40" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F40" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="G40" s="28" t="inlineStr">
@@ -7498,7 +7686,7 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>eaa/ledger.py · TC-10</t>
+          <t>eaa/gates.py + vcs.py content_digest · TC-01</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr"/>
@@ -7506,17 +7694,17 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>N-060</t>
+          <t>N-057</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>GĐ6 · Mô phỏng</t>
+          <t>GĐ5 · Sinh mã &amp; kiểm chứng tĩnh</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Dựng mô hình đối tượng điều khiển</t>
+          <t>Ghi nhận lỗi mô hình bịa ra</t>
         </is>
       </c>
       <c r="D41" s="26" t="inlineStr">
@@ -7524,14 +7712,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E41" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="F41" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
+      <c r="E41" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F41" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="G41" s="28" t="inlineStr">
@@ -7541,7 +7729,7 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>eaa/propose.py PlantModelProposal · TC-57f,g</t>
+          <t>eaa/ledger.py · TC-10</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr"/>
@@ -7549,7 +7737,7 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>N-061</t>
+          <t>N-060</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -7559,7 +7747,7 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Chạy mô phỏng vòng kín</t>
+          <t>Dựng mô hình đối tượng điều khiển</t>
         </is>
       </c>
       <c r="D42" s="26" t="inlineStr">
@@ -7567,14 +7755,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E42" s="29" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="F42" s="29" t="inlineStr">
-        <is>
-          <t>T4</t>
+      <c r="E42" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F42" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="G42" s="28" t="inlineStr">
@@ -7584,7 +7772,7 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>eaa/tools/sim.py, sim_runner.py · TC-12</t>
+          <t>eaa/propose.py PlantModelProposal · TC-57f,g</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr"/>
@@ -7592,7 +7780,7 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>N-062</t>
+          <t>N-061</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
@@ -7602,7 +7790,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Quét tham số và đề xuất bộ tham số</t>
+          <t>Chạy mô phỏng vòng kín</t>
         </is>
       </c>
       <c r="D43" s="26" t="inlineStr">
@@ -7610,14 +7798,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E43" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="F43" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
+      <c r="E43" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F43" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
         </is>
       </c>
       <c r="G43" s="28" t="inlineStr">
@@ -7627,7 +7815,7 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>eaa sim --sweep · TC-12</t>
+          <t>eaa/tools/sim.py, sim_runner.py · TC-12</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr"/>
@@ -7635,7 +7823,7 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>N-063</t>
+          <t>N-062</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -7645,7 +7833,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Tiêm lỗi trong mô phỏng</t>
+          <t>Quét tham số và đề xuất bộ tham số</t>
         </is>
       </c>
       <c r="D44" s="26" t="inlineStr">
@@ -7653,14 +7841,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E44" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="F44" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
+      <c r="E44" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="G44" s="28" t="inlineStr">
@@ -7670,7 +7858,7 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>sim_runner FaultSpec + require_safe_state · TC-57a..e</t>
+          <t>eaa sim --sweep · TC-12</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr"/>
@@ -7678,7 +7866,7 @@
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>N-064</t>
+          <t>N-063</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -7688,12 +7876,12 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Chạy chính mã C sinh ra trong mô phỏng</t>
-        </is>
-      </c>
-      <c r="D45" s="33" t="inlineStr">
-        <is>
-          <t>Cố ý không làm</t>
+          <t>Tiêm lỗi trong mô phỏng</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E45" s="30" t="inlineStr">
@@ -7701,74 +7889,74 @@
           <t>T3</t>
         </is>
       </c>
-      <c r="F45" s="34" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="G45" s="35" t="inlineStr">
-        <is>
-          <t>−3</t>
+      <c r="F45" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G45" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>Cố ý để ngoài chuỗi tự động: nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì.</t>
-        </is>
-      </c>
+          <t>sim_runner FaultSpec + require_safe_state · TC-57a..e</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>N-070</t>
+          <t>N-064</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>GĐ7 · Ráp &amp; nạp</t>
+          <t>GĐ6 · Mô phỏng</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Ráp firmware hoàn chỉnh</t>
-        </is>
-      </c>
-      <c r="D46" s="26" t="inlineStr">
-        <is>
-          <t>Đủ</t>
-        </is>
-      </c>
-      <c r="E46" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="F46" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="G46" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Chạy chính mã C sinh ra trong mô phỏng</t>
+        </is>
+      </c>
+      <c r="D46" s="33" t="inlineStr">
+        <is>
+          <t>Cố ý không làm</t>
+        </is>
+      </c>
+      <c r="E46" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F46" s="34" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G46" s="35" t="inlineStr">
+        <is>
+          <t>−3</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>eaa/firmware.py + eaa build · TC-41</t>
-        </is>
-      </c>
-      <c r="I46" s="6" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>Cố ý để ngoài chuỗi tự động: nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>N-071</t>
+          <t>N-070</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
@@ -7778,7 +7966,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Kiểm bộ nhớ ở tầm firmware</t>
+          <t>Ráp firmware hoàn chỉnh</t>
         </is>
       </c>
       <c r="D47" s="26" t="inlineStr">
@@ -7786,14 +7974,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E47" s="29" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="F47" s="29" t="inlineStr">
-        <is>
-          <t>T4</t>
+      <c r="E47" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F47" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="G47" s="28" t="inlineStr">
@@ -7803,7 +7991,7 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>budget.derived + stack_headroom_bytes_min · TC-53d</t>
+          <t>eaa/firmware.py + eaa build · TC-41</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr"/>
@@ -7811,7 +7999,7 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>N-072</t>
+          <t>N-071</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -7821,7 +8009,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Kiểm trước khi nạp</t>
+          <t>Kiểm bộ nhớ ở tầm firmware</t>
         </is>
       </c>
       <c r="D48" s="26" t="inlineStr">
@@ -7829,14 +8017,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E48" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="F48" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
+      <c r="E48" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F48" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
         </is>
       </c>
       <c r="G48" s="28" t="inlineStr">
@@ -7846,7 +8034,7 @@
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>eaa/flash.py preflight · TC-42b</t>
+          <t>budget.derived + stack_headroom_bytes_min · TC-53d</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr"/>
@@ -7854,7 +8042,7 @@
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>N-073</t>
+          <t>N-072</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
@@ -7864,7 +8052,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Chọn đúng thiết bị để nạp</t>
+          <t>Kiểm trước khi nạp</t>
         </is>
       </c>
       <c r="D49" s="26" t="inlineStr">
@@ -7872,14 +8060,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E49" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="F49" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
+      <c r="E49" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F49" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="G49" s="28" t="inlineStr">
@@ -7889,7 +8077,7 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>eaa/serialport.py match_confirmed · TC-47d</t>
+          <t>eaa/flash.py preflight · TC-42b</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr"/>
@@ -7897,7 +8085,7 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>N-074</t>
+          <t>N-073</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
@@ -7907,7 +8095,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Nạp và ghi nhật ký</t>
+          <t>Chọn đúng thiết bị để nạp</t>
         </is>
       </c>
       <c r="D50" s="26" t="inlineStr">
@@ -7915,14 +8103,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E50" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="F50" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
+      <c r="E50" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F50" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="G50" s="28" t="inlineStr">
@@ -7932,7 +8120,7 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>eaa/flash.py + FlashLog · TC-42d</t>
+          <t>eaa/serialport.py match_confirmed · TC-47d</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr"/>
@@ -7940,7 +8128,7 @@
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>N-075</t>
+          <t>N-074</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -7950,7 +8138,7 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Kiểm sau khi nạp</t>
+          <t>Nạp và ghi nhật ký</t>
         </is>
       </c>
       <c r="D51" s="26" t="inlineStr">
@@ -7958,14 +8146,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E51" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="F51" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
+      <c r="E51" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F51" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="G51" s="28" t="inlineStr">
@@ -7975,7 +8163,7 @@
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>eaa/flash.py VerifyResult + năng lực flash_verify · TC-52</t>
+          <t>eaa/flash.py + FlashLog · TC-42d</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr"/>
@@ -7983,17 +8171,17 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>N-080</t>
+          <t>N-075</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>GĐ8 · Đưa lên mạch &amp; đo</t>
+          <t>GĐ7 · Ráp &amp; nạp</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Thiết lập kênh đo</t>
+          <t>Kiểm sau khi nạp</t>
         </is>
       </c>
       <c r="D52" s="26" t="inlineStr">
@@ -8018,7 +8206,7 @@
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>eaa/telemetry.py + eaa telemetry · TC-43</t>
+          <t>eaa/flash.py VerifyResult + năng lực flash_verify · TC-52</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr"/>
@@ -8026,7 +8214,7 @@
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>N-081</t>
+          <t>N-080</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -8036,7 +8224,7 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Sinh firmware đo cho từng kịch bản chẩn đoán</t>
+          <t>Thiết lập kênh đo</t>
         </is>
       </c>
       <c r="D53" s="26" t="inlineStr">
@@ -8044,14 +8232,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E53" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="F53" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
+      <c r="E53" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F53" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="G53" s="28" t="inlineStr">
@@ -8061,7 +8249,7 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>đủ 6 kịch bản khai firmware_template · TC-58a</t>
+          <t>eaa/telemetry.py + eaa telemetry · TC-43</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr"/>
@@ -8069,7 +8257,7 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>N-082</t>
+          <t>N-081</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -8079,7 +8267,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Chẩn đoán hai kênh</t>
+          <t>Sinh firmware đo cho từng kịch bản chẩn đoán</t>
         </is>
       </c>
       <c r="D54" s="26" t="inlineStr">
@@ -8087,14 +8275,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E54" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="F54" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
+      <c r="E54" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F54" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="G54" s="28" t="inlineStr">
@@ -8104,7 +8292,7 @@
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>eaa/diagnostics.py · TC-27</t>
+          <t>đủ 6 kịch bản khai firmware_template · TC-58a</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr"/>
@@ -8112,7 +8300,7 @@
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
-          <t>N-083</t>
+          <t>N-082</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
@@ -8122,7 +8310,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Đo đặc tính thời gian thực</t>
+          <t>Chẩn đoán hai kênh</t>
         </is>
       </c>
       <c r="D55" s="26" t="inlineStr">
@@ -8130,14 +8318,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E55" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="F55" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
+      <c r="E55" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F55" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="G55" s="28" t="inlineStr">
@@ -8147,7 +8335,7 @@
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>DS-06 đo cả trường hợp xấu nhất và tải CPU · TC-58b</t>
+          <t>eaa/diagnostics.py · TC-27</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr"/>
@@ -8155,7 +8343,7 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>N-084</t>
+          <t>N-083</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -8165,7 +8353,7 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Đo điện và nhiệt</t>
+          <t>Đo đặc tính thời gian thực</t>
         </is>
       </c>
       <c r="D56" s="26" t="inlineStr">
@@ -8173,14 +8361,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E56" s="34" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="F56" s="34" t="inlineStr">
-        <is>
-          <t>T0</t>
+      <c r="E56" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F56" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="G56" s="28" t="inlineStr">
@@ -8190,7 +8378,7 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>ManualMeasurement + eaa diagnose measure · TC-58c,d</t>
+          <t>DS-06 đo cả trường hợp xấu nhất và tải CPU · TC-58b</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr"/>
@@ -8198,7 +8386,7 @@
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
-          <t>N-085</t>
+          <t>N-084</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
@@ -8208,7 +8396,7 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Chẩn đoán sâu bằng công cụ gỡ lỗi</t>
+          <t>Đo điện và nhiệt</t>
         </is>
       </c>
       <c r="D57" s="26" t="inlineStr">
@@ -8216,9 +8404,9 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E57" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
+      <c r="E57" s="34" t="inlineStr">
+        <is>
+          <t>T0</t>
         </is>
       </c>
       <c r="F57" s="34" t="inlineStr">
@@ -8226,26 +8414,22 @@
           <t>T0</t>
         </is>
       </c>
-      <c r="G57" s="35" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="G57" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>eaa/debugsession.py + eaa debug plan/log/record · TC-75</t>
-        </is>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>Đủ Ở ĐÚNG MỨC T0 — 'người làm, Agent ghi vết'. Agent dò mạch gỡ lỗi, dựng kế hoạch phiên từ tiêu chí kịch bản đã duyệt (mỗi bước khai trước hai nhánh kết luận), và ghi lại ai làm gì. Nó KHÔNG chạy phiên gỡ lỗi — việc ấy đòi mạch cắm vào bo thật và vẫn ngoài phạm vi đề án. Tên trình gỡ lỗi nằm ở packs/*/pack.yaml, không ở engine.</t>
-        </is>
-      </c>
+          <t>ManualMeasurement + eaa diagnose measure · TC-58c,d</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>N-086</t>
+          <t>N-085</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -8255,7 +8439,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Kiểm độ bền dài hạn</t>
+          <t>Chẩn đoán sâu bằng công cụ gỡ lỗi</t>
         </is>
       </c>
       <c r="D58" s="26" t="inlineStr">
@@ -8263,42 +8447,46 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E58" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="F58" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G58" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E58" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F58" s="34" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="G58" s="35" t="inlineStr">
+        <is>
+          <t>−1</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>eaa/endurance.py + eaa endurance · TC-58e,f,g</t>
-        </is>
-      </c>
-      <c r="I58" s="6" t="inlineStr"/>
+          <t>eaa/debugsession.py + eaa debug plan/log/record · TC-75</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>Đủ Ở ĐÚNG MỨC T0 — 'người làm, Agent ghi vết'. Agent dò mạch gỡ lỗi, dựng kế hoạch phiên từ tiêu chí kịch bản đã duyệt (mỗi bước khai trước hai nhánh kết luận), và ghi lại ai làm gì. Nó KHÔNG chạy phiên gỡ lỗi — việc ấy đòi mạch cắm vào bo thật và vẫn ngoài phạm vi đề án. Tên trình gỡ lỗi nằm ở packs/*/pack.yaml, không ở engine.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>N-090</t>
+          <t>N-086</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>GĐ9 · Nghiệm thu &amp; phát hành</t>
+          <t>GĐ8 · Đưa lên mạch &amp; đo</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Đối chiếu tiêu chí nghiệm thu</t>
+          <t>Kiểm độ bền dài hạn</t>
         </is>
       </c>
       <c r="D59" s="26" t="inlineStr">
@@ -8306,14 +8494,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E59" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="F59" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
+      <c r="E59" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F59" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="G59" s="28" t="inlineStr">
@@ -8323,7 +8511,7 @@
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>eaa/acceptance.py · TC-45</t>
+          <t>eaa/endurance.py + eaa endurance · TC-58e,f,g</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr"/>
@@ -8331,7 +8519,7 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>N-091</t>
+          <t>N-090</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
@@ -8341,7 +8529,7 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Phong hạng chất lượng bản mã</t>
+          <t>Đối chiếu tiêu chí nghiệm thu</t>
         </is>
       </c>
       <c r="D60" s="26" t="inlineStr">
@@ -8366,7 +8554,7 @@
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>eaa/versions.py + check_device_commit · TC-30, TC-45a</t>
+          <t>eaa/acceptance.py · TC-45</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr"/>
@@ -8374,7 +8562,7 @@
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>N-092</t>
+          <t>N-091</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -8384,7 +8572,7 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Giữ bản chạy tốt và quay lui</t>
+          <t>Phong hạng chất lượng bản mã</t>
         </is>
       </c>
       <c r="D61" s="26" t="inlineStr">
@@ -8392,14 +8580,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E61" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="F61" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
+      <c r="E61" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F61" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="G61" s="28" t="inlineStr">
@@ -8409,7 +8597,7 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>eaa/versions.py + eaa rollback · TC-30</t>
+          <t>eaa/versions.py + check_device_commit · TC-30, TC-45a</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr"/>
@@ -8417,7 +8605,7 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>N-093</t>
+          <t>N-092</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
@@ -8427,7 +8615,7 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Xuất báo cáo và dấu vết</t>
+          <t>Giữ bản chạy tốt và quay lui</t>
         </is>
       </c>
       <c r="D62" s="26" t="inlineStr">
@@ -8452,7 +8640,7 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>eaa/kpi.py + llm/calllog.py + registry.py · TC-09, TC-15</t>
+          <t>eaa/versions.py + eaa rollback · TC-30</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr"/>
@@ -8460,7 +8648,7 @@
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>N-094</t>
+          <t>N-093</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -8470,7 +8658,7 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Bàn giao tài liệu vận hành</t>
+          <t>Xuất báo cáo và dấu vết</t>
         </is>
       </c>
       <c r="D63" s="26" t="inlineStr">
@@ -8478,14 +8666,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E63" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="F63" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
+      <c r="E63" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F63" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="G63" s="28" t="inlineStr">
@@ -8495,7 +8683,7 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>eaa/handover.py OperationsHandbook · TC-59a,b</t>
+          <t>eaa/kpi.py + llm/calllog.py + registry.py · TC-09, TC-15</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr"/>
@@ -8503,22 +8691,22 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>N-100</t>
+          <t>N-094</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>GĐ10 · Vận hành &amp; bảo trì</t>
+          <t>GĐ9 · Nghiệm thu &amp; phát hành</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
-        </is>
-      </c>
-      <c r="D64" s="32" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+          <t>Bàn giao tài liệu vận hành</t>
+        </is>
+      </c>
+      <c r="D64" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E64" s="27" t="inlineStr">
@@ -8538,29 +8726,25 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>eaa/lifecycle.py StaleSet · TC-29</t>
-        </is>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>Cùng gốc với N-036: sửa một datasheet hiện KHÔNG có lệnh nào trả lời 'mã nào bị ảnh hưởng'. Cần một lệnh (vd `eaa knowledge stale`) nối StaleSet vào đường người dùng</t>
-        </is>
-      </c>
+          <t>eaa/handover.py OperationsHandbook · TC-59a,b</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>N-101</t>
+          <t>N-095</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>GĐ10 · Vận hành &amp; bảo trì</t>
+          <t>GĐ9 · Nghiệm thu &amp; phát hành</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Đánh giá ảnh hưởng khi linh kiện đổi</t>
+          <t>Sinh tài liệu thiết kế của chính dự án</t>
         </is>
       </c>
       <c r="D65" s="26" t="inlineStr">
@@ -8568,14 +8752,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E65" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="F65" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
+      <c r="E65" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F65" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="G65" s="28" t="inlineStr">
@@ -8585,7 +8769,7 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>eaa/handover.py SwapAnalysis · TC-59c,d</t>
+          <t>eaa/docmodel.py (một bản vẽ, nhiều định dạng) + eaa/designdoc.py (URD/SRS/SDD, chức năng, luồng, rút TỪ HỒ SƠ chứ không hỏi mô hình) + eaa/office.py (docx/pptx/xlsx/md/pdf, không thêm phụ thuộc) + lệnh eaa design list/gen · SL-105, TC-82</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr"/>
@@ -8593,7 +8777,7 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>N-102</t>
+          <t>N-100</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -8603,12 +8787,12 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Chẩn đoán sự cố ngoài hiện trường</t>
-        </is>
-      </c>
-      <c r="D66" s="26" t="inlineStr">
-        <is>
-          <t>Đủ</t>
+          <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
+        </is>
+      </c>
+      <c r="D66" s="32" t="inlineStr">
+        <is>
+          <t>Một phần</t>
         </is>
       </c>
       <c r="E66" s="27" t="inlineStr">
@@ -8628,15 +8812,19 @@
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>eaa/diagnostics.py FieldCase · TC-59e,f</t>
-        </is>
-      </c>
-      <c r="I66" s="6" t="inlineStr"/>
+          <t>eaa/lifecycle.py StaleSet · TC-29</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>Cùng gốc với N-036: sửa một datasheet hiện KHÔNG có lệnh nào trả lời 'mã nào bị ảnh hưởng'. Cần một lệnh (vd `eaa knowledge stale`) nối StaleSet vào đường người dùng</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>N-103</t>
+          <t>N-101</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -8646,7 +8834,7 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Cập nhật firmware cho thiết bị đã triển khai</t>
+          <t>Đánh giá ảnh hưởng khi linh kiện đổi</t>
         </is>
       </c>
       <c r="D67" s="26" t="inlineStr">
@@ -8654,14 +8842,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E67" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="F67" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
+      <c r="E67" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F67" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="G67" s="28" t="inlineStr">
@@ -8671,7 +8859,7 @@
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>eaa/handover.py RolloutPlan · TC-59g,h</t>
+          <t>eaa/handover.py SwapAnalysis · TC-59c,d</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr"/>
@@ -8679,17 +8867,17 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>N-900</t>
+          <t>N-102</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>XS · Xuyên suốt</t>
+          <t>GĐ10 · Vận hành &amp; bảo trì</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Giữ ranh giới tổng quát / nền tảng / dự án</t>
+          <t>Chẩn đoán sự cố ngoài hiện trường</t>
         </is>
       </c>
       <c r="D68" s="26" t="inlineStr">
@@ -8697,14 +8885,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E68" s="29" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="F68" s="29" t="inlineStr">
-        <is>
-          <t>T4</t>
+      <c r="E68" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F68" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="G68" s="28" t="inlineStr">
@@ -8714,7 +8902,7 @@
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>TC-38 (quét mỗi commit) + TC-47a (không rẽ nhánh theo pack)</t>
+          <t>eaa/diagnostics.py FieldCase · TC-59e,f</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr"/>
@@ -8722,17 +8910,17 @@
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>N-901</t>
+          <t>N-103</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>XS · Xuyên suốt</t>
+          <t>GĐ10 · Vận hành &amp; bảo trì</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Bảo vệ khóa và bí mật</t>
+          <t>Cập nhật firmware cho thiết bị đã triển khai</t>
         </is>
       </c>
       <c r="D69" s="26" t="inlineStr">
@@ -8740,14 +8928,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E69" s="29" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="F69" s="29" t="inlineStr">
-        <is>
-          <t>T4</t>
+      <c r="E69" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F69" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="G69" s="28" t="inlineStr">
@@ -8757,7 +8945,7 @@
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>eaa/llm/base.py mask_secrets · TC-14 + tests/conftest.py</t>
+          <t>eaa/handover.py RolloutPlan · TC-59g,h</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr"/>
@@ -8765,7 +8953,7 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>N-902</t>
+          <t>N-900</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -8775,7 +8963,7 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Không bao giờ hành động ngoài ý muốn người</t>
+          <t>Giữ ranh giới tổng quát / nền tảng / dự án</t>
         </is>
       </c>
       <c r="D70" s="26" t="inlineStr">
@@ -8783,14 +8971,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E70" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="F70" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
+      <c r="E70" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F70" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
         </is>
       </c>
       <c r="G70" s="28" t="inlineStr">
@@ -8800,7 +8988,7 @@
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>eaa/gates.py, doctor, flash — không cờ bỏ qua · TC-01, TC-42c</t>
+          <t>eaa/platform.py là interface DUY NHẤT engine gọi toolchain qua đó (FR-PLT-02, ADR-09) · TC-38 (quét mỗi commit) + TC-47a (không rẽ nhánh theo pack)</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr"/>
@@ -8808,7 +8996,7 @@
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>N-903</t>
+          <t>N-901</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -8818,7 +9006,7 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Nói rõ mức tin cậy của mọi điều mình nói</t>
+          <t>Bảo vệ khóa và bí mật</t>
         </is>
       </c>
       <c r="D71" s="26" t="inlineStr">
@@ -8831,19 +9019,19 @@
           <t>T4</t>
         </is>
       </c>
-      <c r="F71" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G71" s="35" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F71" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G71" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>eaa/confidence.py + Judged · TC-60a-c, TC-63a-e</t>
+          <t>eaa/llm/base.py mask_secrets · TC-14 + tests/conftest.py</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr"/>
@@ -8851,7 +9039,7 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>N-904</t>
+          <t>N-902</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
@@ -8861,7 +9049,7 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>Quản lý chi phí gọi mô hình</t>
+          <t>Không bao giờ hành động ngoài ý muốn người</t>
         </is>
       </c>
       <c r="D72" s="26" t="inlineStr">
@@ -8869,14 +9057,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E72" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="F72" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
+      <c r="E72" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F72" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="G72" s="28" t="inlineStr">
@@ -8886,7 +9074,7 @@
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>eaa/budget.py TokenBudget · TC-53e,f</t>
+          <t>eaa/gates.py, doctor, flash — không cờ bỏ qua · TC-01, TC-42c</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr"/>
@@ -8894,7 +9082,7 @@
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>N-905</t>
+          <t>N-903</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -8904,7 +9092,7 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Ghi nhận mọi sai lệch so với thiết kế</t>
+          <t>Nói rõ mức tin cậy của mọi điều mình nói</t>
         </is>
       </c>
       <c r="D73" s="26" t="inlineStr">
@@ -8912,24 +9100,24 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E73" s="30" t="inlineStr">
+      <c r="E73" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F73" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F73" s="30" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G73" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="G73" s="35" t="inlineStr">
+        <is>
+          <t>−1</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>eaa/deviation.py + eaa deviations · TC-60d,e,f</t>
+          <t>eaa/confidence.py + Judged · TC-60a-c, TC-63a-e</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr"/>
@@ -8937,7 +9125,7 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>N-906</t>
+          <t>N-904</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
@@ -8947,7 +9135,7 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Tự đánh giá và cải tiến quy trình</t>
+          <t>Quản lý chi phí gọi mô hình</t>
         </is>
       </c>
       <c r="D74" s="26" t="inlineStr">
@@ -8955,14 +9143,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E74" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="F74" s="27" t="inlineStr">
-        <is>
-          <t>T1</t>
+      <c r="E74" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F74" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="G74" s="28" t="inlineStr">
@@ -8972,7 +9160,7 @@
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>kpi.weak_points + eaa report review · TC-60g,h,i</t>
+          <t>eaa/budget.py TokenBudget · TC-53e,f</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr"/>
@@ -8980,7 +9168,7 @@
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>N-907</t>
+          <t>N-905</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
@@ -8990,7 +9178,7 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Khôi phục sau gián đoạn</t>
+          <t>Ghi nhận mọi sai lệch so với thiết kế</t>
         </is>
       </c>
       <c r="D75" s="26" t="inlineStr">
@@ -8998,14 +9186,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E75" s="29" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="F75" s="29" t="inlineStr">
-        <is>
-          <t>T4</t>
+      <c r="E75" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F75" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="G75" s="28" t="inlineStr">
@@ -9015,7 +9203,7 @@
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>eaa/state.py ghi nguyên tử + eaa resume · TC-03</t>
+          <t>eaa/deviation.py + eaa deviations · TC-60d,e,f</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr"/>
@@ -9023,7 +9211,7 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>N-908</t>
+          <t>N-906</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
@@ -9033,12 +9221,12 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Phân biệt 'mã tôi sai' với 'bài kiểm tôi sai'</t>
-        </is>
-      </c>
-      <c r="D76" s="36" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
+          <t>Tự đánh giá và cải tiến quy trình</t>
+        </is>
+      </c>
+      <c r="D76" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E76" s="27" t="inlineStr">
@@ -9046,31 +9234,27 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="35" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F76" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G76" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có gì. Bốn cổng đo mã CÓ CHẠY KHÔNG, không đo mã có ĐANG ĐO ĐÚNG THỨ nó nhận không. Bằng chứng: 3/12 lần từ chối G3 (drv_imu, logic_pid, app_balance) · §3.1</t>
-        </is>
-      </c>
+          <t>kpi.weak_points + eaa report review · TC-60g,h,i</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>N-909</t>
+          <t>N-907</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -9080,44 +9264,40 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Phát hiện bài kiểm KHÔNG chứng minh điều nó nhận là mình chứng minh</t>
-        </is>
-      </c>
-      <c r="D77" s="36" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
-        </is>
-      </c>
-      <c r="E77" s="31" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="35" t="inlineStr">
-        <is>
-          <t>−2</t>
+          <t>Khôi phục sau gián đoạn</t>
+        </is>
+      </c>
+      <c r="D77" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E77" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F77" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G77" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có gì. Cần một phép kiểm ĐỘ NHẠY: chạy lại bài kiểm mới trên bản mã SAI đã biết, xanh thì bài kiểm ấy rỗng. Bằng chứng: test_deadband_keeps_setpoint_steady · §3.3, §3.8</t>
-        </is>
-      </c>
+          <t>eaa/state.py ghi nguyên tử + eaa resume · TC-03</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>N-910</t>
+          <t>N-914</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -9127,7 +9307,7 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Canh thoái lui giữa các lượt sinh của cùng một module</t>
+          <t>Người chọn mô hình, hệ không tự chọn</t>
         </is>
       </c>
       <c r="D78" s="26" t="inlineStr">
@@ -9135,14 +9315,14 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E78" s="29" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="F78" s="29" t="inlineStr">
-        <is>
-          <t>T4</t>
+      <c r="E78" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F78" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="G78" s="28" t="inlineStr">
@@ -9152,7 +9332,7 @@
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>eaa/contract.py: pha_vo_hop_dong so chữ ký header (SL-163, TC-124) + mat_loi_goi so tập lời gọi LIÊN MODULE của tệp .c với bản đã merge (SL-167, TC-127, 33 bài)</t>
+          <t>eaa/llm/catalog.py CATALOG + KHUYEN_NGHI (là LỜI KHUYÊN in ra, không có mã nào đọc nó để quyết định) + lệnh eaa models; mặc định ghim trong Project State, cờ --model đổi tại chỗ dùng · SL-103, SL-170, TC-80, TC-130</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr"/>
@@ -9160,7 +9340,7 @@
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>N-911</t>
+          <t>N-915</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
@@ -9170,12 +9350,12 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
-        </is>
-      </c>
-      <c r="D79" s="36" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
+          <t>Hoán đổi nhà cung cấp mô hình mà hành vi không đổi</t>
+        </is>
+      </c>
+      <c r="D79" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E79" s="29" t="inlineStr">
@@ -9183,31 +9363,27 @@
           <t>T4</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="35" t="inlineStr">
-        <is>
-          <t>−4</t>
+      <c r="F79" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G79" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có gì. Hồ sơ phần cứng đã khai đơn vị của từng đại lượng, nên dữ liệu để làm thì có sẵn. Bằng chứng: chú thích '4ms / 0.000031s = 129' · §3.4</t>
-        </is>
-      </c>
+          <t>eaa/llm/base.py là giao diện chung; ba adapter eaa/llm/gemini.py, mock.py và ReplayClient trong calllog.py — bản phát lại cố ý KHÔNG bịa phản hồi khi trượt băm · TC-11, TC-15</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>N-912</t>
+          <t>N-908</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
@@ -9217,7 +9393,7 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
+          <t>Phân biệt 'mã tôi sai' với 'bài kiểm tôi sai'</t>
         </is>
       </c>
       <c r="D80" s="36" t="inlineStr">
@@ -9247,59 +9423,243 @@
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>Chưa có gì. eaa/decompose.py chưa đòi module khai dấu hiệu sống/hỏng; eaa/propose.py AcceptanceProposal chưa sinh tiêu chí quan sát được bằng mắt/tai · §3.6</t>
+          <t>Chưa có gì. Bốn cổng đo mã CÓ CHẠY KHÔNG, không đo mã có ĐANG ĐO ĐÚNG THỨ nó nhận không. Bằng chứng: 3/12 lần từ chối G3 (drv_imu, logic_pid, app_balance) · §3.1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
+          <t>N-909</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Phát hiện bài kiểm KHÔNG chứng minh điều nó nhận là mình chứng minh</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>Một phần</t>
+        </is>
+      </c>
+      <c r="E81" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F81" s="31" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="G81" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>eaa/sensitivity.py chạy bộ kiểm MỚI trên mã CŨ trong bản sao tạm; kết quả vào nhật ký, KPI test_sensitivity, và đầu checklist G3 (SL-168, TC-128, 28 bài)</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>Bắt được hạng NHẸ HƠN hạng đã sinh ra nó: bài kiểm không phân biệt được gì. Ca deadband vẫn đỏ trên mã cũ vì lý do khác nên vẫn QUA được phép đo — phần ấy còn cần người đọc ở G3</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>N-910</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Canh thoái lui giữa các lượt sinh của cùng một module</t>
+        </is>
+      </c>
+      <c r="D82" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
+        </is>
+      </c>
+      <c r="E82" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F82" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G82" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>eaa/contract.py: pha_vo_hop_dong so chữ ký header (SL-163, TC-124) + mat_loi_goi so tập lời gọi LIÊN MODULE của tệp .c với bản đã merge (SL-167, TC-127, 33 bài)</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>N-911</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
+        </is>
+      </c>
+      <c r="D83" s="36" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E83" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="35" t="inlineStr">
+        <is>
+          <t>−4</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có gì. Hồ sơ phần cứng đã khai đơn vị của từng đại lượng, nên dữ liệu để làm thì có sẵn. Bằng chứng: chú thích '4ms / 0.000031s = 129' · §3.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>N-912</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
+        </is>
+      </c>
+      <c r="D84" s="36" t="inlineStr">
+        <is>
+          <t>Chưa có</t>
+        </is>
+      </c>
+      <c r="E84" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="35" t="inlineStr">
+        <is>
+          <t>−1</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có gì. eaa/decompose.py chưa đòi module khai dấu hiệu sống/hỏng; eaa/propose.py AcceptanceProposal chưa sinh tiêu chí quan sát được bằng mắt/tai · §3.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="inlineStr">
+        <is>
           <t>N-913</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>XS · Xuyên suốt</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>Đưa số đo từ phần cứng ngược vào prompt</t>
         </is>
       </c>
-      <c r="D81" s="36" t="inlineStr">
+      <c r="D85" s="36" t="inlineStr">
         <is>
           <t>Chưa có</t>
         </is>
       </c>
-      <c r="E81" s="30" t="inlineStr">
+      <c r="E85" s="30" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="35" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G85" s="35" t="inlineStr">
         <is>
           <t>−3</t>
         </is>
       </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
         <is>
           <t>Chưa có gì. measurements.jsonl và kết quả DS-xx nằm NGOÀI eaa/composer.py. Đây là mục đắt nhất trong sáu mục, vì nó đụng vào bộ ghép prompt và vào gate tri thức · §3.7</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I81"/>
+  <autoFilter ref="A1:I85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/EAA_Nghiep_vu_Agent.xlsx
+++ b/docs/EAA_Nghiep_vu_Agent.xlsx
@@ -5898,16 +5898,16 @@
         <v>11</v>
       </c>
       <c r="D30" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -5923,16 +5923,16 @@
         <v>76</v>
       </c>
       <c r="D31" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" s="25" t="n">
         <v>3</v>
-      </c>
-      <c r="E31" s="25" t="n">
-        <v>4</v>
       </c>
       <c r="F31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -9396,9 +9396,9 @@
           <t>Phân biệt 'mã tôi sai' với 'bài kiểm tôi sai'</t>
         </is>
       </c>
-      <c r="D80" s="36" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>Một phần</t>
         </is>
       </c>
       <c r="E80" s="27" t="inlineStr">
@@ -9406,24 +9406,24 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="35" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F80" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G80" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>eaa/instrument.py dò ba DẤU VẾT trên mỗi bản vá: hằng số trong hàm mang // ref: bị đổi; mã vừa mọc nhánh nhận đúng con số của bài kiểm; chú thích tự khai. Thấy dấu vết thì DỪNG vòng vá và đưa câu hỏi về cho người (SL-171, TC-131, 25 bài)</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>Chưa có gì. Bốn cổng đo mã CÓ CHẠY KHÔNG, không đo mã có ĐANG ĐO ĐÚNG THỨ nó nhận không. Bằng chứng: 3/12 lần từ chối G3 (drv_imu, logic_pid, app_balance) · §3.1</t>
+          <t>Dò DẤU VẾT, không kiểm vật lý. Câu 'con số nào mới đúng' đòi biết bài toán, và chỗ ấy vẫn là người phân xử — đúng mức tự chủ T1 mà nghiệp vụ này khai</t>
         </is>
       </c>
     </row>

--- a/docs/EAA_Nghiep_vu_Agent.xlsx
+++ b/docs/EAA_Nghiep_vu_Agent.xlsx
@@ -62,15 +62,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C5700"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001F4E79"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="009C0006"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C5700"/>
     </font>
   </fonts>
   <fills count="13">
@@ -122,12 +122,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -246,16 +246,16 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5695,10 +5695,10 @@
         <v>9</v>
       </c>
       <c r="C22" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="22" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>4</v>
       </c>
       <c r="C29" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="22" t="n">
         <v>0</v>
@@ -5920,10 +5920,10 @@
         <v>84</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" s="25" t="n">
         <v>3</v>
@@ -7101,9 +7101,9 @@
           <t>Quản lý vòng đời tri thức</t>
         </is>
       </c>
-      <c r="D27" s="32" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E27" s="30" t="inlineStr">
@@ -7123,14 +7123,10 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>eaa/lifecycle.py KnowledgeLifecycle (3 đường truy ngược) · TC-29</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>Rà soát 04/09: KHÔNG module nào trong eaa/ import lifecycle, và không lệnh CLI nào gọi tới. `eaa docs regen` đi qua registry, không qua vòng đời tri thức. Cơ chế đúng, đường chạy chưa có</t>
-        </is>
-      </c>
+          <t>eaa/lifecycle.py KnowledgeLifecycle (3 đường truy ngược) + lệnh eaa knowledge supersede/deprecate — đòi quyết định G2, hạ module xuống 'stale' trong cùng lệnh, KHÔNG tự mở vòng sinh lại · TC-29, SL-172, TC-132</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -7922,7 +7918,7 @@
           <t>Chạy chính mã C sinh ra trong mô phỏng</t>
         </is>
       </c>
-      <c r="D46" s="33" t="inlineStr">
+      <c r="D46" s="32" t="inlineStr">
         <is>
           <t>Cố ý không làm</t>
         </is>
@@ -7932,12 +7928,12 @@
           <t>T3</t>
         </is>
       </c>
-      <c r="F46" s="34" t="inlineStr">
+      <c r="F46" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G46" s="35" t="inlineStr">
+      <c r="G46" s="34" t="inlineStr">
         <is>
           <t>−3</t>
         </is>
@@ -8404,12 +8400,12 @@
           <t>Đủ</t>
         </is>
       </c>
-      <c r="E57" s="34" t="inlineStr">
+      <c r="E57" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="F57" s="34" t="inlineStr">
+      <c r="F57" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
@@ -8452,12 +8448,12 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F58" s="34" t="inlineStr">
+      <c r="F58" s="33" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
       </c>
-      <c r="G58" s="35" t="inlineStr">
+      <c r="G58" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -8790,9 +8786,9 @@
           <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
         </is>
       </c>
-      <c r="D66" s="32" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+      <c r="D66" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E66" s="27" t="inlineStr">
@@ -8812,14 +8808,10 @@
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>eaa/lifecycle.py StaleSet · TC-29</t>
-        </is>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>Cùng gốc với N-036: sửa một datasheet hiện KHÔNG có lệnh nào trả lời 'mã nào bị ảnh hưởng'. Cần một lệnh (vd `eaa knowledge stale`) nối StaleSet vào đường người dùng</t>
-        </is>
-      </c>
+          <t>eaa knowledge stale &lt;chunk&gt; — CHỈ ĐỌC, hợp ba đường (đồ thị · trích dẫn // ref: trong mã · chunk-ids của commit), gắn nhãn SUY RA vì đường đồ thị mù khi khai báo uses thiếu. Có trong TOOLBOX ở nhóm chỉ đọc · SL-172, TC-132</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
@@ -9110,7 +9102,7 @@
           <t>T3</t>
         </is>
       </c>
-      <c r="G73" s="35" t="inlineStr">
+      <c r="G73" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -9396,7 +9388,7 @@
           <t>Phân biệt 'mã tôi sai' với 'bài kiểm tôi sai'</t>
         </is>
       </c>
-      <c r="D80" s="32" t="inlineStr">
+      <c r="D80" s="35" t="inlineStr">
         <is>
           <t>Một phần</t>
         </is>
@@ -9443,7 +9435,7 @@
           <t>Phát hiện bài kiểm KHÔNG chứng minh điều nó nhận là mình chứng minh</t>
         </is>
       </c>
-      <c r="D81" s="32" t="inlineStr">
+      <c r="D81" s="35" t="inlineStr">
         <is>
           <t>Một phần</t>
         </is>
@@ -9548,7 +9540,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G83" s="35" t="inlineStr">
+      <c r="G83" s="34" t="inlineStr">
         <is>
           <t>−4</t>
         </is>
@@ -9595,7 +9587,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G84" s="35" t="inlineStr">
+      <c r="G84" s="34" t="inlineStr">
         <is>
           <t>−1</t>
         </is>
@@ -9642,7 +9634,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G85" s="35" t="inlineStr">
+      <c r="G85" s="34" t="inlineStr">
         <is>
           <t>−3</t>
         </is>

--- a/docs/EAA_Nghiep_vu_Agent.xlsx
+++ b/docs/EAA_Nghiep_vu_Agent.xlsx
@@ -5895,19 +5895,19 @@
         <v>16</v>
       </c>
       <c r="C30" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D30" s="22" t="n">
         <v>2</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -5920,19 +5920,19 @@
         <v>84</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D31" s="25" t="n">
         <v>2</v>
       </c>
       <c r="E31" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -9619,9 +9619,9 @@
           <t>Đưa số đo từ phần cứng ngược vào prompt</t>
         </is>
       </c>
-      <c r="D85" s="36" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
+      <c r="D85" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E85" s="30" t="inlineStr">
@@ -9629,26 +9629,22 @@
           <t>T3</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G85" s="34" t="inlineStr">
-        <is>
-          <t>−3</t>
+      <c r="F85" s="30" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G85" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I85" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có gì. measurements.jsonl và kết quả DS-xx nằm NGOÀI eaa/composer.py. Đây là mục đắt nhất trong sáu mục, vì nó đụng vào bộ ghép prompt và vào gate tri thức · §3.7</t>
-        </is>
-      </c>
+          <t>eaa/measured.py — sổ nối tiếp board_facts.jsonl + lớp ngữ cảnh K8 board_facts trong eaa/composer.py (đứng TRƯỚC lớp trích đoạn tài liệu) + lệnh eaa measured list/add/approve. Agent đề xuất, người chốt; chỉ số ĐÃ DUYỆT mới vào prompt · SL-173, TC-133, 21 bài</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I85"/>

--- a/docs/EAA_Nghiep_vu_Agent.xlsx
+++ b/docs/EAA_Nghiep_vu_Agent.xlsx
@@ -5895,19 +5895,19 @@
         <v>16</v>
       </c>
       <c r="C30" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D30" s="22" t="n">
         <v>2</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -5920,19 +5920,19 @@
         <v>84</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D31" s="25" t="n">
         <v>2</v>
       </c>
       <c r="E31" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -9525,9 +9525,9 @@
           <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
         </is>
       </c>
-      <c r="D83" s="36" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
+      <c r="D83" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E83" s="29" t="inlineStr">
@@ -9535,26 +9535,22 @@
           <t>T4</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="34" t="inlineStr">
-        <is>
-          <t>−4</t>
+      <c r="F83" s="29" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G83" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có gì. Hồ sơ phần cứng đã khai đơn vị của từng đại lượng, nên dữ liệu để làm thì có sẵn. Bằng chứng: chú thích '4ms / 0.000031s = 129' · §3.4</t>
-        </is>
-      </c>
+          <t>eaa/dimension.py, nối vào StaticGate ở mức CẢNH BÁO. Hai phép soi: đơn vị khai trong chú thích chọi với đơn vị trong sổ số đo (cần N-913), và phép tính không ra kết quả nó khai (tự chứa, có quy đổi tiền tố) · SL-174, TC-134, 20 bài</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="13" t="inlineStr">

--- a/docs/EAA_Nghiep_vu_Agent.xlsx
+++ b/docs/EAA_Nghiep_vu_Agent.xlsx
@@ -73,7 +73,7 @@
       <color rgb="009C5700"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -130,11 +130,6 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -162,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -253,9 +248,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5895,19 +5887,19 @@
         <v>16</v>
       </c>
       <c r="C30" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D30" s="22" t="n">
         <v>2</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -5920,19 +5912,19 @@
         <v>84</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D31" s="25" t="n">
         <v>2</v>
       </c>
       <c r="E31" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -9568,9 +9560,9 @@
           <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
         </is>
       </c>
-      <c r="D84" s="36" t="inlineStr">
-        <is>
-          <t>Chưa có</t>
+      <c r="D84" s="26" t="inlineStr">
+        <is>
+          <t>Đủ</t>
         </is>
       </c>
       <c r="E84" s="27" t="inlineStr">
@@ -9578,26 +9570,22 @@
           <t>T1</t>
         </is>
       </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G84" s="34" t="inlineStr">
-        <is>
-          <t>−1</t>
+      <c r="F84" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G84" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>Chưa có gì. eaa/decompose.py chưa đòi module khai dấu hiệu sống/hỏng; eaa/propose.py AcceptanceProposal chưa sinh tiêu chí quan sát được bằng mắt/tai · §3.6</t>
-        </is>
-      </c>
+          <t>eaa/observability.py + hai trường dau_hieu_song/dau_hieu_hong trong mục backlog + lệnh eaa observe (báo cáo) và observe set (khai) + một dòng checklist ở hồ sơ G3. Kênh quan sát đọc từ cờ observable của hồ sơ dự án — engine coi là chuỗi mờ · SL-175, TC-135, 23 bài</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="13" t="inlineStr">
